--- a/test-automation/EN301549v4.1.1-ListOfCriteria.xlsx
+++ b/test-automation/EN301549v4.1.1-ListOfCriteria.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\a11y-best-practices\test-automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A185A5F-D008-4027-BA2E-2BD0CD676C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFAD18E3-4677-4D81-B058-CF1AA7F71595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4110" yWindow="-21795" windowWidth="51990" windowHeight="21990" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20685" yWindow="-21600" windowWidth="26010" windowHeight="21705" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Anmerkungen" sheetId="16" r:id="rId1"/>
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Alle Kriterien'!$A$1:$AF$456</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -2913,7 +2913,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1365" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1365" uniqueCount="593">
   <si>
     <t>(1) Struktur und Semantik klar vorgeben</t>
   </si>
@@ -4662,9 +4662,6 @@
   </si>
   <si>
     <t>English titles v4.1.1 2026-09</t>
-  </si>
-  <si>
-    <t>5.1.6.1 Closed functionality (keyboard)</t>
   </si>
   <si>
     <t>6.5.6 Indication of all active communication participants</t>
@@ -5052,7 +5049,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -5318,37 +5315,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5376,7 +5349,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5654,12 +5626,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A1" s="37" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A2" s="114" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="28.5" x14ac:dyDescent="0.45">
@@ -5683,11 +5655,10 @@
     <col min="3" max="3" width="46.86328125" customWidth="1"/>
     <col min="4" max="4" width="7" customWidth="1"/>
     <col min="5" max="7" width="6.3984375" customWidth="1"/>
-    <col min="8" max="15" width="6.3984375" style="1" customWidth="1"/>
-    <col min="16" max="16" width="6.3984375" style="123" customWidth="1"/>
+    <col min="8" max="16" width="6.3984375" style="1" customWidth="1"/>
     <col min="17" max="30" width="5.86328125" style="1" customWidth="1"/>
     <col min="31" max="31" width="6.796875" style="2" customWidth="1"/>
-    <col min="32" max="32" width="7.06640625" style="135" customWidth="1"/>
+    <col min="32" max="32" width="7.06640625" style="10" customWidth="1"/>
     <col min="33" max="40" width="6.86328125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5702,16 +5673,16 @@
         <v>582</v>
       </c>
       <c r="D1" s="113" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E1" s="105" t="s">
         <v>399</v>
       </c>
       <c r="F1" s="109" t="s">
+        <v>586</v>
+      </c>
+      <c r="G1" s="107" t="s">
         <v>587</v>
-      </c>
-      <c r="G1" s="107" t="s">
-        <v>588</v>
       </c>
       <c r="H1" s="61" t="s">
         <v>533</v>
@@ -5777,10 +5748,10 @@
         <v>540</v>
       </c>
       <c r="AC1" s="56" t="s">
+        <v>591</v>
+      </c>
+      <c r="AD1" s="57" t="s">
         <v>592</v>
-      </c>
-      <c r="AD1" s="57" t="s">
-        <v>593</v>
       </c>
       <c r="AE1" s="4" t="s">
         <v>9</v>
@@ -5840,10 +5811,10 @@
       <c r="Z2" s="89"/>
       <c r="AA2" s="89"/>
       <c r="AB2" s="89"/>
-      <c r="AC2" s="115"/>
+      <c r="AC2" s="89"/>
       <c r="AD2" s="103"/>
       <c r="AE2" s="89" t="str">
-        <f>IF(SUM(Q2:AD2)&gt;0,SUM(Q2:AD2),"")</f>
+        <f t="shared" ref="AE2:AE65" si="0">IF(SUM(Q2:AD2)&gt;0,SUM(Q2:AD2),"")</f>
         <v/>
       </c>
       <c r="AF2" s="77" t="str">
@@ -5902,14 +5873,14 @@
       <c r="Z3" s="89"/>
       <c r="AA3" s="89"/>
       <c r="AB3" s="89"/>
-      <c r="AC3" s="115"/>
+      <c r="AC3" s="89"/>
       <c r="AD3" s="103"/>
       <c r="AE3" s="89" t="str">
-        <f>IF(SUM(Q3:AD3)&gt;0,SUM(Q3:AD3),"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="AF3" s="77" t="str">
-        <f t="shared" ref="AF3:AF66" si="0">IF(SUM(Q3:AD3)&lt;1,"",Q3*1+R3*2+S3*3+T3*4+U3*5+V3*6+W3*7+X3*8+Y3*9+Z3*10+AA3*11+AB3*12+AC3*13+AD3*14)</f>
+        <f t="shared" ref="AF3:AF66" si="1">IF(SUM(Q3:AD3)&lt;1,"",Q3*1+R3*2+S3*3+T3*4+U3*5+V3*6+W3*7+X3*8+Y3*9+Z3*10+AA3*11+AB3*12+AC3*13+AD3*14)</f>
         <v/>
       </c>
     </row>
@@ -5955,14 +5926,14 @@
       <c r="T4" s="53">
         <v>1</v>
       </c>
-      <c r="AC4" s="116"/>
+      <c r="AC4" s="115"/>
       <c r="AD4" s="7"/>
       <c r="AE4" s="2">
-        <f>IF(SUM(Q4:AD4)&gt;0,SUM(Q4:AD4),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF4" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -6008,14 +5979,14 @@
       <c r="AB5" s="53">
         <v>1</v>
       </c>
-      <c r="AC5" s="116"/>
+      <c r="AC5" s="115"/>
       <c r="AD5" s="7"/>
       <c r="AE5" s="2">
-        <f>IF(SUM(Q5:AD5)&gt;0,SUM(Q5:AD5),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF5" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
     </row>
@@ -6061,14 +6032,14 @@
       <c r="T6" s="53">
         <v>1</v>
       </c>
-      <c r="AC6" s="116"/>
+      <c r="AC6" s="115"/>
       <c r="AD6" s="7"/>
       <c r="AE6" s="2">
-        <f>IF(SUM(Q6:AD6)&gt;0,SUM(Q6:AD6),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF6" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -6114,14 +6085,14 @@
       <c r="T7" s="53">
         <v>1</v>
       </c>
-      <c r="AC7" s="116"/>
+      <c r="AC7" s="115"/>
       <c r="AD7" s="7"/>
       <c r="AE7" s="2">
-        <f>IF(SUM(Q7:AD7)&gt;0,SUM(Q7:AD7),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF7" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -6167,14 +6138,14 @@
       <c r="T8" s="53">
         <v>1</v>
       </c>
-      <c r="AC8" s="116"/>
+      <c r="AC8" s="115"/>
       <c r="AD8" s="7"/>
       <c r="AE8" s="2">
-        <f>IF(SUM(Q8:AD8)&gt;0,SUM(Q8:AD8),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF8" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -6220,14 +6191,14 @@
       <c r="T9" s="53">
         <v>1</v>
       </c>
-      <c r="AC9" s="116"/>
+      <c r="AC9" s="115"/>
       <c r="AD9" s="7"/>
       <c r="AE9" s="2">
-        <f>IF(SUM(Q9:AD9)&gt;0,SUM(Q9:AD9),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF9" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -6273,14 +6244,14 @@
       <c r="U10" s="53">
         <v>1</v>
       </c>
-      <c r="AC10" s="116"/>
+      <c r="AC10" s="115"/>
       <c r="AD10" s="7"/>
       <c r="AE10" s="2">
-        <f>IF(SUM(Q10:AD10)&gt;0,SUM(Q10:AD10),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF10" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
     </row>
@@ -6326,14 +6297,14 @@
       <c r="T11" s="53">
         <v>1</v>
       </c>
-      <c r="AC11" s="116"/>
+      <c r="AC11" s="115"/>
       <c r="AD11" s="7"/>
       <c r="AE11" s="2">
-        <f>IF(SUM(Q11:AD11)&gt;0,SUM(Q11:AD11),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF11" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -6376,16 +6347,16 @@
       <c r="P12" s="58">
         <v>1</v>
       </c>
-      <c r="AC12" s="117">
+      <c r="AC12" s="53">
         <v>1</v>
       </c>
       <c r="AD12" s="7"/>
       <c r="AE12" s="2">
-        <f>IF(SUM(Q12:AD12)&gt;0,SUM(Q12:AD12),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF12" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
     </row>
@@ -6431,14 +6402,14 @@
       <c r="W13" s="53">
         <v>1</v>
       </c>
-      <c r="AC13" s="116"/>
+      <c r="AC13" s="115"/>
       <c r="AD13" s="7"/>
       <c r="AE13" s="2">
-        <f>IF(SUM(Q13:AD13)&gt;0,SUM(Q13:AD13),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF13" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
     </row>
@@ -6484,14 +6455,14 @@
       <c r="T14" s="53">
         <v>1</v>
       </c>
-      <c r="AC14" s="116"/>
+      <c r="AC14" s="115"/>
       <c r="AD14" s="7"/>
       <c r="AE14" s="2">
-        <f>IF(SUM(Q14:AD14)&gt;0,SUM(Q14:AD14),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF14" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -6537,14 +6508,14 @@
       <c r="T15" s="53">
         <v>1</v>
       </c>
-      <c r="AC15" s="116"/>
+      <c r="AC15" s="115"/>
       <c r="AD15" s="7"/>
       <c r="AE15" s="2">
-        <f>IF(SUM(Q15:AD15)&gt;0,SUM(Q15:AD15),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF15" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -6590,14 +6561,14 @@
       <c r="T16" s="53">
         <v>1</v>
       </c>
-      <c r="AC16" s="116"/>
+      <c r="AC16" s="115"/>
       <c r="AD16" s="7"/>
       <c r="AE16" s="2">
-        <f>IF(SUM(Q16:AD16)&gt;0,SUM(Q16:AD16),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF16" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -6643,14 +6614,14 @@
       <c r="Q17" s="53">
         <v>1</v>
       </c>
-      <c r="AC17" s="116"/>
+      <c r="AC17" s="115"/>
       <c r="AD17" s="7"/>
       <c r="AE17" s="2">
-        <f>IF(SUM(Q17:AD17)&gt;0,SUM(Q17:AD17),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF17" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -6696,14 +6667,14 @@
       <c r="X18" s="53">
         <v>1</v>
       </c>
-      <c r="AC18" s="116"/>
+      <c r="AC18" s="115"/>
       <c r="AD18" s="7"/>
       <c r="AE18" s="2">
-        <f>IF(SUM(Q18:AD18)&gt;0,SUM(Q18:AD18),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF18" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
     </row>
@@ -6749,14 +6720,14 @@
       <c r="T19" s="53">
         <v>1</v>
       </c>
-      <c r="AC19" s="116"/>
+      <c r="AC19" s="115"/>
       <c r="AD19" s="7"/>
       <c r="AE19" s="2">
-        <f>IF(SUM(Q19:AD19)&gt;0,SUM(Q19:AD19),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF19" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -6802,14 +6773,14 @@
       <c r="V20" s="53">
         <v>1</v>
       </c>
-      <c r="AC20" s="116"/>
+      <c r="AC20" s="115"/>
       <c r="AD20" s="7"/>
       <c r="AE20" s="2">
-        <f>IF(SUM(Q20:AD20)&gt;0,SUM(Q20:AD20),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF20" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
     </row>
@@ -6855,14 +6826,14 @@
       <c r="U21" s="53">
         <v>1</v>
       </c>
-      <c r="AC21" s="116"/>
+      <c r="AC21" s="115"/>
       <c r="AD21" s="7"/>
       <c r="AE21" s="2">
-        <f>IF(SUM(Q21:AD21)&gt;0,SUM(Q21:AD21),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF21" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
     </row>
@@ -6871,7 +6842,7 @@
         <v>231</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>583</v>
+        <v>231</v>
       </c>
       <c r="D22" s="32" t="s">
         <v>11</v>
@@ -6909,14 +6880,14 @@
       <c r="S22" s="53">
         <v>1</v>
       </c>
-      <c r="AC22" s="116"/>
+      <c r="AC22" s="115"/>
       <c r="AD22" s="7"/>
       <c r="AE22" s="2">
-        <f>IF(SUM(Q22:AD22)&gt;0,SUM(Q22:AD22),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF22" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -6963,14 +6934,14 @@
       <c r="S23" s="53">
         <v>1</v>
       </c>
-      <c r="AC23" s="116"/>
+      <c r="AC23" s="115"/>
       <c r="AD23" s="7"/>
       <c r="AE23" s="2">
-        <f>IF(SUM(Q23:AD23)&gt;0,SUM(Q23:AD23),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF23" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -7017,14 +6988,14 @@
       <c r="Z24" s="53">
         <v>1</v>
       </c>
-      <c r="AC24" s="116"/>
+      <c r="AC24" s="115"/>
       <c r="AD24" s="7"/>
       <c r="AE24" s="2">
-        <f>IF(SUM(Q24:AD24)&gt;0,SUM(Q24:AD24),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF24" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -7070,14 +7041,14 @@
       <c r="Q25" s="53">
         <v>1</v>
       </c>
-      <c r="AC25" s="116"/>
+      <c r="AC25" s="115"/>
       <c r="AD25" s="7"/>
       <c r="AE25" s="2">
-        <f>IF(SUM(Q25:AD25)&gt;0,SUM(Q25:AD25),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF25" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -7123,14 +7094,14 @@
       <c r="R26" s="53">
         <v>1</v>
       </c>
-      <c r="AC26" s="116"/>
+      <c r="AC26" s="115"/>
       <c r="AD26" s="7"/>
       <c r="AE26" s="2">
-        <f>IF(SUM(Q26:AD26)&gt;0,SUM(Q26:AD26),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF26" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
@@ -7182,14 +7153,14 @@
       <c r="Y27" s="53">
         <v>1</v>
       </c>
-      <c r="AC27" s="116"/>
+      <c r="AC27" s="115"/>
       <c r="AD27" s="7"/>
       <c r="AE27" s="2">
-        <f>IF(SUM(Q27:AD27)&gt;0,SUM(Q27:AD27),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF27" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
     </row>
@@ -7240,14 +7211,14 @@
       <c r="AA28" s="53">
         <v>1</v>
       </c>
-      <c r="AC28" s="116"/>
+      <c r="AC28" s="115"/>
       <c r="AD28" s="7"/>
       <c r="AE28" s="2">
-        <f>IF(SUM(Q28:AD28)&gt;0,SUM(Q28:AD28),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF28" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
     </row>
@@ -7264,14 +7235,14 @@
       <c r="I29" s="86"/>
       <c r="K29" s="86"/>
       <c r="P29" s="58"/>
-      <c r="AC29" s="116"/>
+      <c r="AC29" s="115"/>
       <c r="AD29" s="7"/>
       <c r="AE29" s="2" t="str">
-        <f>IF(SUM(Q29:AD29)&gt;0,SUM(Q29:AD29),"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="AF29" s="77" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -7314,14 +7285,14 @@
       <c r="S30" s="53">
         <v>1</v>
       </c>
-      <c r="AC30" s="116"/>
+      <c r="AC30" s="115"/>
       <c r="AD30" s="7"/>
       <c r="AE30" s="2">
-        <f>IF(SUM(Q30:AD30)&gt;0,SUM(Q30:AD30),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF30" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -7372,14 +7343,14 @@
       <c r="S31" s="53">
         <v>1</v>
       </c>
-      <c r="AC31" s="116"/>
+      <c r="AC31" s="115"/>
       <c r="AD31" s="7"/>
       <c r="AE31" s="2">
-        <f>IF(SUM(Q31:AD31)&gt;0,SUM(Q31:AD31),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF31" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -7430,14 +7401,14 @@
       <c r="S32" s="53">
         <v>1</v>
       </c>
-      <c r="AC32" s="116"/>
+      <c r="AC32" s="115"/>
       <c r="AD32" s="7"/>
       <c r="AE32" s="2">
-        <f>IF(SUM(Q32:AD32)&gt;0,SUM(Q32:AD32),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF32" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -7489,14 +7460,14 @@
       <c r="S33" s="53">
         <v>1</v>
       </c>
-      <c r="AC33" s="116"/>
+      <c r="AC33" s="115"/>
       <c r="AD33" s="7"/>
       <c r="AE33" s="2">
-        <f>IF(SUM(Q33:AD33)&gt;0,SUM(Q33:AD33),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF33" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -7548,14 +7519,14 @@
       <c r="S34" s="53">
         <v>1</v>
       </c>
-      <c r="AC34" s="116"/>
+      <c r="AC34" s="115"/>
       <c r="AD34" s="7"/>
       <c r="AE34" s="2">
-        <f>IF(SUM(Q34:AD34)&gt;0,SUM(Q34:AD34),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF34" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -7607,14 +7578,14 @@
       <c r="S35" s="53">
         <v>1</v>
       </c>
-      <c r="AC35" s="116"/>
+      <c r="AC35" s="115"/>
       <c r="AD35" s="7"/>
       <c r="AE35" s="2">
-        <f>IF(SUM(Q35:AD35)&gt;0,SUM(Q35:AD35),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF35" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -7653,14 +7624,14 @@
       <c r="AA36" s="53">
         <v>1</v>
       </c>
-      <c r="AC36" s="116"/>
+      <c r="AC36" s="115"/>
       <c r="AD36" s="7"/>
       <c r="AE36" s="2">
-        <f>IF(SUM(Q36:AD36)&gt;0,SUM(Q36:AD36),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF36" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
     </row>
@@ -7699,14 +7670,14 @@
       <c r="AA37" s="53">
         <v>1</v>
       </c>
-      <c r="AC37" s="116"/>
+      <c r="AC37" s="115"/>
       <c r="AD37" s="7"/>
       <c r="AE37" s="2">
-        <f>IF(SUM(Q37:AD37)&gt;0,SUM(Q37:AD37),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF37" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
     </row>
@@ -7745,14 +7716,14 @@
       <c r="AA38" s="53">
         <v>1</v>
       </c>
-      <c r="AC38" s="116"/>
+      <c r="AC38" s="115"/>
       <c r="AD38" s="7"/>
       <c r="AE38" s="2">
-        <f>IF(SUM(Q38:AD38)&gt;0,SUM(Q38:AD38),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF38" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
     </row>
@@ -7791,14 +7762,14 @@
       <c r="AA39" s="53">
         <v>1</v>
       </c>
-      <c r="AC39" s="116"/>
+      <c r="AC39" s="115"/>
       <c r="AD39" s="7"/>
       <c r="AE39" s="2">
-        <f>IF(SUM(Q39:AD39)&gt;0,SUM(Q39:AD39),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF39" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
     </row>
@@ -7837,14 +7808,14 @@
       <c r="AA40" s="53">
         <v>1</v>
       </c>
-      <c r="AC40" s="116"/>
+      <c r="AC40" s="115"/>
       <c r="AD40" s="7"/>
       <c r="AE40" s="2">
-        <f>IF(SUM(Q40:AD40)&gt;0,SUM(Q40:AD40),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF40" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
     </row>
@@ -7876,14 +7847,14 @@
       <c r="Z41" s="53">
         <v>1</v>
       </c>
-      <c r="AC41" s="116"/>
+      <c r="AC41" s="115"/>
       <c r="AD41" s="7"/>
       <c r="AE41" s="2">
-        <f>IF(SUM(Q41:AD41)&gt;0,SUM(Q41:AD41),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF41" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -7933,14 +7904,14 @@
       </c>
       <c r="AA42" s="9"/>
       <c r="AB42" s="9"/>
-      <c r="AC42" s="116"/>
+      <c r="AC42" s="115"/>
       <c r="AD42" s="7"/>
       <c r="AE42" s="2">
-        <f>IF(SUM(Q42:AD42)&gt;0,SUM(Q42:AD42),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF42" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -7990,14 +7961,14 @@
       </c>
       <c r="AA43" s="9"/>
       <c r="AB43" s="9"/>
-      <c r="AC43" s="116"/>
+      <c r="AC43" s="115"/>
       <c r="AD43" s="7"/>
       <c r="AE43" s="2">
-        <f>IF(SUM(Q43:AD43)&gt;0,SUM(Q43:AD43),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF43" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -8047,14 +8018,14 @@
       </c>
       <c r="AA44" s="9"/>
       <c r="AB44" s="9"/>
-      <c r="AC44" s="116"/>
+      <c r="AC44" s="115"/>
       <c r="AD44" s="7"/>
       <c r="AE44" s="2">
-        <f>IF(SUM(Q44:AD44)&gt;0,SUM(Q44:AD44),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF44" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -8086,14 +8057,14 @@
       <c r="Z45" s="53">
         <v>1</v>
       </c>
-      <c r="AC45" s="116"/>
+      <c r="AC45" s="115"/>
       <c r="AD45" s="7"/>
       <c r="AE45" s="2">
-        <f>IF(SUM(Q45:AD45)&gt;0,SUM(Q45:AD45),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF45" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -8125,14 +8096,14 @@
       <c r="Z46" s="53">
         <v>1</v>
       </c>
-      <c r="AC46" s="116"/>
+      <c r="AC46" s="115"/>
       <c r="AD46" s="7"/>
       <c r="AE46" s="2">
-        <f>IF(SUM(Q46:AD46)&gt;0,SUM(Q46:AD46),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF46" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -8164,14 +8135,14 @@
       <c r="Z47" s="53">
         <v>1</v>
       </c>
-      <c r="AC47" s="116"/>
+      <c r="AC47" s="115"/>
       <c r="AD47" s="7"/>
       <c r="AE47" s="2">
-        <f>IF(SUM(Q47:AD47)&gt;0,SUM(Q47:AD47),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF47" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -8207,14 +8178,14 @@
       <c r="Z48" s="53">
         <v>1</v>
       </c>
-      <c r="AC48" s="116"/>
+      <c r="AC48" s="115"/>
       <c r="AD48" s="7"/>
       <c r="AE48" s="2">
-        <f>IF(SUM(Q48:AD48)&gt;0,SUM(Q48:AD48),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF48" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -8248,14 +8219,14 @@
       <c r="Z49" s="53">
         <v>1</v>
       </c>
-      <c r="AC49" s="116"/>
+      <c r="AC49" s="115"/>
       <c r="AD49" s="7"/>
       <c r="AE49" s="2">
-        <f>IF(SUM(Q49:AD49)&gt;0,SUM(Q49:AD49),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF49" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -8300,14 +8271,14 @@
       <c r="Z50" s="53">
         <v>1</v>
       </c>
-      <c r="AC50" s="116"/>
+      <c r="AC50" s="115"/>
       <c r="AD50" s="7"/>
       <c r="AE50" s="2">
-        <f>IF(SUM(Q50:AD50)&gt;0,SUM(Q50:AD50),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF50" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -8345,14 +8316,14 @@
       <c r="Z51" s="53">
         <v>1</v>
       </c>
-      <c r="AC51" s="116"/>
+      <c r="AC51" s="115"/>
       <c r="AD51" s="7"/>
       <c r="AE51" s="2">
-        <f>IF(SUM(Q51:AD51)&gt;0,SUM(Q51:AD51),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF51" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -8381,14 +8352,14 @@
       <c r="Z52" s="53">
         <v>1</v>
       </c>
-      <c r="AC52" s="116"/>
+      <c r="AC52" s="115"/>
       <c r="AD52" s="7"/>
       <c r="AE52" s="2">
-        <f>IF(SUM(Q52:AD52)&gt;0,SUM(Q52:AD52),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF52" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -8435,14 +8406,14 @@
       <c r="Z53" s="53">
         <v>1</v>
       </c>
-      <c r="AC53" s="116"/>
+      <c r="AC53" s="115"/>
       <c r="AD53" s="7"/>
       <c r="AE53" s="2">
-        <f>IF(SUM(Q53:AD53)&gt;0,SUM(Q53:AD53),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF53" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -8503,14 +8474,14 @@
       </c>
       <c r="AA54" s="9"/>
       <c r="AB54" s="9"/>
-      <c r="AC54" s="116"/>
+      <c r="AC54" s="115"/>
       <c r="AD54" s="7"/>
       <c r="AE54" s="2">
-        <f>IF(SUM(Q54:AD54)&gt;0,SUM(Q54:AD54),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF54" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -8552,14 +8523,14 @@
       <c r="Z55" s="53">
         <v>1</v>
       </c>
-      <c r="AC55" s="116"/>
+      <c r="AC55" s="115"/>
       <c r="AD55" s="7"/>
       <c r="AE55" s="2">
-        <f>IF(SUM(Q55:AD55)&gt;0,SUM(Q55:AD55),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF55" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -8603,14 +8574,14 @@
       <c r="Z56" s="53">
         <v>1</v>
       </c>
-      <c r="AC56" s="116"/>
+      <c r="AC56" s="115"/>
       <c r="AD56" s="7"/>
       <c r="AE56" s="2">
-        <f>IF(SUM(Q56:AD56)&gt;0,SUM(Q56:AD56),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF56" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -8627,14 +8598,14 @@
       <c r="P57" s="58" t="s">
         <v>576</v>
       </c>
-      <c r="AC57" s="116"/>
+      <c r="AC57" s="115"/>
       <c r="AD57" s="7"/>
       <c r="AE57" s="2" t="str">
-        <f>IF(SUM(Q57:AD57)&gt;0,SUM(Q57:AD57),"")</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="AF57" s="77" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
     </row>
@@ -8678,14 +8649,14 @@
       <c r="Z58" s="53">
         <v>1</v>
       </c>
-      <c r="AC58" s="116"/>
+      <c r="AC58" s="115"/>
       <c r="AD58" s="7"/>
       <c r="AE58" s="2">
-        <f>IF(SUM(Q58:AD58)&gt;0,SUM(Q58:AD58),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF58" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -8732,14 +8703,14 @@
       <c r="Z59" s="53">
         <v>1</v>
       </c>
-      <c r="AC59" s="116"/>
+      <c r="AC59" s="115"/>
       <c r="AD59" s="7"/>
       <c r="AE59" s="2">
-        <f>IF(SUM(Q59:AD59)&gt;0,SUM(Q59:AD59),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF59" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -8797,14 +8768,14 @@
       </c>
       <c r="AA60" s="9"/>
       <c r="AB60" s="9"/>
-      <c r="AC60" s="116"/>
+      <c r="AC60" s="115"/>
       <c r="AD60" s="7"/>
       <c r="AE60" s="2">
-        <f>IF(SUM(Q60:AD60)&gt;0,SUM(Q60:AD60),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF60" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -8864,14 +8835,14 @@
       </c>
       <c r="AA61" s="9"/>
       <c r="AB61" s="9"/>
-      <c r="AC61" s="116"/>
+      <c r="AC61" s="115"/>
       <c r="AD61" s="7"/>
       <c r="AE61" s="2">
-        <f>IF(SUM(Q61:AD61)&gt;0,SUM(Q61:AD61),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF61" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -8927,14 +8898,14 @@
       </c>
       <c r="AA62" s="9"/>
       <c r="AB62" s="9"/>
-      <c r="AC62" s="116"/>
+      <c r="AC62" s="115"/>
       <c r="AD62" s="7"/>
       <c r="AE62" s="2">
-        <f>IF(SUM(Q62:AD62)&gt;0,SUM(Q62:AD62),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF62" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -8994,14 +8965,14 @@
       </c>
       <c r="AA63" s="9"/>
       <c r="AB63" s="9"/>
-      <c r="AC63" s="116"/>
+      <c r="AC63" s="115"/>
       <c r="AD63" s="7"/>
       <c r="AE63" s="2">
-        <f>IF(SUM(Q63:AD63)&gt;0,SUM(Q63:AD63),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF63" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -9056,14 +9027,14 @@
       </c>
       <c r="AA64" s="9"/>
       <c r="AB64" s="9"/>
-      <c r="AC64" s="116"/>
+      <c r="AC64" s="115"/>
       <c r="AD64" s="7"/>
       <c r="AE64" s="2">
-        <f>IF(SUM(Q64:AD64)&gt;0,SUM(Q64:AD64),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF64" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -9118,14 +9089,14 @@
       </c>
       <c r="AA65" s="9"/>
       <c r="AB65" s="9"/>
-      <c r="AC65" s="116"/>
+      <c r="AC65" s="115"/>
       <c r="AD65" s="7"/>
       <c r="AE65" s="2">
-        <f>IF(SUM(Q65:AD65)&gt;0,SUM(Q65:AD65),"")</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AF65" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -9180,14 +9151,14 @@
       </c>
       <c r="AA66" s="9"/>
       <c r="AB66" s="9"/>
-      <c r="AC66" s="116"/>
+      <c r="AC66" s="115"/>
       <c r="AD66" s="7"/>
       <c r="AE66" s="2">
-        <f>IF(SUM(Q66:AD66)&gt;0,SUM(Q66:AD66),"")</f>
+        <f t="shared" ref="AE66:AE129" si="2">IF(SUM(Q66:AD66)&gt;0,SUM(Q66:AD66),"")</f>
         <v>1</v>
       </c>
       <c r="AF66" s="77">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
     </row>
@@ -9242,14 +9213,14 @@
       </c>
       <c r="AA67" s="9"/>
       <c r="AB67" s="9"/>
-      <c r="AC67" s="116"/>
+      <c r="AC67" s="115"/>
       <c r="AD67" s="7"/>
       <c r="AE67" s="2">
-        <f>IF(SUM(Q67:AD67)&gt;0,SUM(Q67:AD67),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF67" s="77">
-        <f t="shared" ref="AF67:AF130" si="1">IF(SUM(Q67:AD67)&lt;1,"",Q67*1+R67*2+S67*3+T67*4+U67*5+V67*6+W67*7+X67*8+Y67*9+Z67*10+AA67*11+AB67*12+AC67*13+AD67*14)</f>
+        <f t="shared" ref="AF67:AF130" si="3">IF(SUM(Q67:AD67)&lt;1,"",Q67*1+R67*2+S67*3+T67*4+U67*5+V67*6+W67*7+X67*8+Y67*9+Z67*10+AA67*11+AB67*12+AC67*13+AD67*14)</f>
         <v>10</v>
       </c>
     </row>
@@ -9304,14 +9275,14 @@
       </c>
       <c r="AA68" s="9"/>
       <c r="AB68" s="9"/>
-      <c r="AC68" s="116"/>
+      <c r="AC68" s="115"/>
       <c r="AD68" s="7"/>
       <c r="AE68" s="2">
-        <f>IF(SUM(Q68:AD68)&gt;0,SUM(Q68:AD68),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF68" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
     </row>
@@ -9369,14 +9340,14 @@
       </c>
       <c r="AA69" s="9"/>
       <c r="AB69" s="9"/>
-      <c r="AC69" s="116"/>
+      <c r="AC69" s="115"/>
       <c r="AD69" s="7"/>
       <c r="AE69" s="2">
-        <f>IF(SUM(Q69:AD69)&gt;0,SUM(Q69:AD69),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF69" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
     </row>
@@ -9430,14 +9401,14 @@
       </c>
       <c r="AA70" s="9"/>
       <c r="AB70" s="9"/>
-      <c r="AC70" s="116"/>
+      <c r="AC70" s="115"/>
       <c r="AD70" s="7"/>
       <c r="AE70" s="2">
-        <f>IF(SUM(Q70:AD70)&gt;0,SUM(Q70:AD70),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF70" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
     </row>
@@ -9497,14 +9468,14 @@
       </c>
       <c r="AA71" s="9"/>
       <c r="AB71" s="9"/>
-      <c r="AC71" s="116"/>
+      <c r="AC71" s="115"/>
       <c r="AD71" s="7"/>
       <c r="AE71" s="2">
-        <f>IF(SUM(Q71:AD71)&gt;0,SUM(Q71:AD71),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF71" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
     </row>
@@ -9558,14 +9529,14 @@
       </c>
       <c r="AA72" s="9"/>
       <c r="AB72" s="9"/>
-      <c r="AC72" s="116"/>
+      <c r="AC72" s="115"/>
       <c r="AD72" s="7"/>
       <c r="AE72" s="2">
-        <f>IF(SUM(Q72:AD72)&gt;0,SUM(Q72:AD72),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF72" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
     </row>
@@ -9619,14 +9590,14 @@
       </c>
       <c r="AA73" s="9"/>
       <c r="AB73" s="9"/>
-      <c r="AC73" s="116"/>
+      <c r="AC73" s="115"/>
       <c r="AD73" s="7"/>
       <c r="AE73" s="2">
-        <f>IF(SUM(Q73:AD73)&gt;0,SUM(Q73:AD73),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF73" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
     </row>
@@ -9680,14 +9651,14 @@
       </c>
       <c r="AA74" s="9"/>
       <c r="AB74" s="9"/>
-      <c r="AC74" s="116"/>
+      <c r="AC74" s="115"/>
       <c r="AD74" s="7"/>
       <c r="AE74" s="2">
-        <f>IF(SUM(Q74:AD74)&gt;0,SUM(Q74:AD74),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF74" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
     </row>
@@ -9747,14 +9718,14 @@
       </c>
       <c r="AA75" s="9"/>
       <c r="AB75" s="9"/>
-      <c r="AC75" s="116"/>
+      <c r="AC75" s="115"/>
       <c r="AD75" s="7"/>
       <c r="AE75" s="2">
-        <f>IF(SUM(Q75:AD75)&gt;0,SUM(Q75:AD75),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF75" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
     </row>
@@ -9766,7 +9737,7 @@
         <v>50</v>
       </c>
       <c r="C76" s="15" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D76" s="67" t="s">
         <v>11</v>
@@ -9808,14 +9779,14 @@
       </c>
       <c r="AA76" s="9"/>
       <c r="AB76" s="9"/>
-      <c r="AC76" s="116"/>
+      <c r="AC76" s="115"/>
       <c r="AD76" s="7"/>
       <c r="AE76" s="2">
-        <f>IF(SUM(Q76:AD76)&gt;0,SUM(Q76:AD76),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF76" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
     </row>
@@ -9869,14 +9840,14 @@
       </c>
       <c r="AA77" s="9"/>
       <c r="AB77" s="9"/>
-      <c r="AC77" s="116"/>
+      <c r="AC77" s="115"/>
       <c r="AD77" s="7"/>
       <c r="AE77" s="2">
-        <f>IF(SUM(Q77:AD77)&gt;0,SUM(Q77:AD77),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF77" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
     </row>
@@ -9931,14 +9902,14 @@
       </c>
       <c r="AA78" s="9"/>
       <c r="AB78" s="9"/>
-      <c r="AC78" s="116"/>
+      <c r="AC78" s="115"/>
       <c r="AD78" s="7"/>
       <c r="AE78" s="2">
-        <f>IF(SUM(Q78:AD78)&gt;0,SUM(Q78:AD78),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF78" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
     </row>
@@ -9993,14 +9964,14 @@
       </c>
       <c r="AA79" s="9"/>
       <c r="AB79" s="9"/>
-      <c r="AC79" s="116"/>
+      <c r="AC79" s="115"/>
       <c r="AD79" s="7"/>
       <c r="AE79" s="2">
-        <f>IF(SUM(Q79:AD79)&gt;0,SUM(Q79:AD79),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF79" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
     </row>
@@ -10058,14 +10029,14 @@
       <c r="Z80" s="9"/>
       <c r="AA80" s="9"/>
       <c r="AB80" s="9"/>
-      <c r="AC80" s="116"/>
+      <c r="AC80" s="115"/>
       <c r="AD80" s="7"/>
       <c r="AE80" s="2">
-        <f>IF(SUM(Q80:AD80)&gt;0,SUM(Q80:AD80),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF80" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
     </row>
@@ -10123,14 +10094,14 @@
       <c r="Z81" s="9"/>
       <c r="AA81" s="9"/>
       <c r="AB81" s="9"/>
-      <c r="AC81" s="116"/>
+      <c r="AC81" s="115"/>
       <c r="AD81" s="7"/>
       <c r="AE81" s="2">
-        <f>IF(SUM(Q81:AD81)&gt;0,SUM(Q81:AD81),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF81" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
     </row>
@@ -10188,14 +10159,14 @@
       <c r="Z82" s="9"/>
       <c r="AA82" s="9"/>
       <c r="AB82" s="9"/>
-      <c r="AC82" s="116"/>
+      <c r="AC82" s="115"/>
       <c r="AD82" s="7"/>
       <c r="AE82" s="2">
-        <f>IF(SUM(Q82:AD82)&gt;0,SUM(Q82:AD82),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF82" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
     </row>
@@ -10253,14 +10224,14 @@
       <c r="Z83" s="9"/>
       <c r="AA83" s="9"/>
       <c r="AB83" s="9"/>
-      <c r="AC83" s="116"/>
+      <c r="AC83" s="115"/>
       <c r="AD83" s="7"/>
       <c r="AE83" s="2">
-        <f>IF(SUM(Q83:AD83)&gt;0,SUM(Q83:AD83),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF83" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
     </row>
@@ -10318,14 +10289,14 @@
       <c r="Z84" s="9"/>
       <c r="AA84" s="9"/>
       <c r="AB84" s="9"/>
-      <c r="AC84" s="116"/>
+      <c r="AC84" s="115"/>
       <c r="AD84" s="7"/>
       <c r="AE84" s="2">
-        <f>IF(SUM(Q84:AD84)&gt;0,SUM(Q84:AD84),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF84" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
     </row>
@@ -10377,14 +10348,14 @@
       <c r="Z85" s="9"/>
       <c r="AA85" s="9"/>
       <c r="AB85" s="9"/>
-      <c r="AC85" s="116"/>
+      <c r="AC85" s="115"/>
       <c r="AD85" s="7"/>
       <c r="AE85" s="2">
-        <f>IF(SUM(Q85:AD85)&gt;0,SUM(Q85:AD85),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF85" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
     </row>
@@ -10436,14 +10407,14 @@
       <c r="Z86" s="9"/>
       <c r="AA86" s="9"/>
       <c r="AB86" s="9"/>
-      <c r="AC86" s="116"/>
+      <c r="AC86" s="115"/>
       <c r="AD86" s="7"/>
       <c r="AE86" s="2">
-        <f>IF(SUM(Q86:AD86)&gt;0,SUM(Q86:AD86),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF86" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
     </row>
@@ -10495,14 +10466,14 @@
       <c r="Z87" s="9"/>
       <c r="AA87" s="9"/>
       <c r="AB87" s="9"/>
-      <c r="AC87" s="116"/>
+      <c r="AC87" s="115"/>
       <c r="AD87" s="7"/>
       <c r="AE87" s="2">
-        <f>IF(SUM(Q87:AD87)&gt;0,SUM(Q87:AD87),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF87" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
     </row>
@@ -10560,14 +10531,14 @@
       <c r="Z88" s="9"/>
       <c r="AA88" s="9"/>
       <c r="AB88" s="9"/>
-      <c r="AC88" s="116"/>
+      <c r="AC88" s="115"/>
       <c r="AD88" s="7"/>
       <c r="AE88" s="2">
-        <f>IF(SUM(Q88:AD88)&gt;0,SUM(Q88:AD88),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF88" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
     </row>
@@ -10619,14 +10590,14 @@
       <c r="Z89" s="9"/>
       <c r="AA89" s="9"/>
       <c r="AB89" s="9"/>
-      <c r="AC89" s="116"/>
+      <c r="AC89" s="115"/>
       <c r="AD89" s="7"/>
       <c r="AE89" s="2">
-        <f>IF(SUM(Q89:AD89)&gt;0,SUM(Q89:AD89),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF89" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
     </row>
@@ -10678,14 +10649,14 @@
       <c r="Z90" s="9"/>
       <c r="AA90" s="9"/>
       <c r="AB90" s="9"/>
-      <c r="AC90" s="116"/>
+      <c r="AC90" s="115"/>
       <c r="AD90" s="7"/>
       <c r="AE90" s="2">
-        <f>IF(SUM(Q90:AD90)&gt;0,SUM(Q90:AD90),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF90" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
     </row>
@@ -10737,14 +10708,14 @@
       <c r="Z91" s="9"/>
       <c r="AA91" s="9"/>
       <c r="AB91" s="9"/>
-      <c r="AC91" s="116"/>
+      <c r="AC91" s="115"/>
       <c r="AD91" s="7"/>
       <c r="AE91" s="2">
-        <f>IF(SUM(Q91:AD91)&gt;0,SUM(Q91:AD91),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF91" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
     </row>
@@ -10796,14 +10767,14 @@
       <c r="Z92" s="9"/>
       <c r="AA92" s="9"/>
       <c r="AB92" s="9"/>
-      <c r="AC92" s="116"/>
+      <c r="AC92" s="115"/>
       <c r="AD92" s="7"/>
       <c r="AE92" s="2">
-        <f>IF(SUM(Q92:AD92)&gt;0,SUM(Q92:AD92),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF92" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
     </row>
@@ -10853,16 +10824,16 @@
       <c r="Z93" s="9"/>
       <c r="AA93" s="9"/>
       <c r="AB93" s="9"/>
-      <c r="AC93" s="116"/>
+      <c r="AC93" s="115"/>
       <c r="AD93" s="54">
         <v>1</v>
       </c>
       <c r="AE93" s="2">
-        <f>IF(SUM(Q93:AD93)&gt;0,SUM(Q93:AD93),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF93" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
     </row>
@@ -10909,16 +10880,16 @@
       <c r="Z94" s="9"/>
       <c r="AA94" s="9"/>
       <c r="AB94" s="9"/>
-      <c r="AC94" s="116"/>
+      <c r="AC94" s="115"/>
       <c r="AD94" s="54">
         <v>1</v>
       </c>
       <c r="AE94" s="2">
-        <f>IF(SUM(Q94:AD94)&gt;0,SUM(Q94:AD94),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF94" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
     </row>
@@ -10965,16 +10936,16 @@
       <c r="Z95" s="9"/>
       <c r="AA95" s="9"/>
       <c r="AB95" s="9"/>
-      <c r="AC95" s="116"/>
+      <c r="AC95" s="115"/>
       <c r="AD95" s="54">
         <v>1</v>
       </c>
       <c r="AE95" s="2">
-        <f>IF(SUM(Q95:AD95)&gt;0,SUM(Q95:AD95),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF95" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
     </row>
@@ -11021,16 +10992,16 @@
       <c r="Z96" s="9"/>
       <c r="AA96" s="9"/>
       <c r="AB96" s="9"/>
-      <c r="AC96" s="116"/>
+      <c r="AC96" s="115"/>
       <c r="AD96" s="54">
         <v>1</v>
       </c>
       <c r="AE96" s="2">
-        <f>IF(SUM(Q96:AD96)&gt;0,SUM(Q96:AD96),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF96" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
     </row>
@@ -11077,16 +11048,16 @@
       <c r="Z97" s="9"/>
       <c r="AA97" s="9"/>
       <c r="AB97" s="9"/>
-      <c r="AC97" s="116"/>
+      <c r="AC97" s="115"/>
       <c r="AD97" s="54">
         <v>1</v>
       </c>
       <c r="AE97" s="2">
-        <f>IF(SUM(Q97:AD97)&gt;0,SUM(Q97:AD97),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF97" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
     </row>
@@ -11133,16 +11104,16 @@
       <c r="Z98" s="9"/>
       <c r="AA98" s="9"/>
       <c r="AB98" s="9"/>
-      <c r="AC98" s="116"/>
+      <c r="AC98" s="115"/>
       <c r="AD98" s="54">
         <v>1</v>
       </c>
       <c r="AE98" s="2">
-        <f>IF(SUM(Q98:AD98)&gt;0,SUM(Q98:AD98),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF98" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
     </row>
@@ -11189,16 +11160,16 @@
       <c r="Z99" s="9"/>
       <c r="AA99" s="9"/>
       <c r="AB99" s="9"/>
-      <c r="AC99" s="116"/>
+      <c r="AC99" s="115"/>
       <c r="AD99" s="54">
         <v>1</v>
       </c>
       <c r="AE99" s="2">
-        <f>IF(SUM(Q99:AD99)&gt;0,SUM(Q99:AD99),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF99" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
     </row>
@@ -11245,16 +11216,16 @@
       <c r="Z100" s="9"/>
       <c r="AA100" s="9"/>
       <c r="AB100" s="9"/>
-      <c r="AC100" s="116"/>
+      <c r="AC100" s="115"/>
       <c r="AD100" s="54">
         <v>1</v>
       </c>
       <c r="AE100" s="2">
-        <f>IF(SUM(Q100:AD100)&gt;0,SUM(Q100:AD100),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF100" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
     </row>
@@ -11288,14 +11259,14 @@
       <c r="Z101" s="9"/>
       <c r="AA101" s="9"/>
       <c r="AB101" s="9"/>
-      <c r="AC101" s="116"/>
-      <c r="AD101" s="126"/>
+      <c r="AC101" s="115"/>
+      <c r="AD101" s="118"/>
       <c r="AE101" s="2" t="str">
-        <f>IF(SUM(Q101:AD101)&gt;0,SUM(Q101:AD101),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AF101" s="77" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -11329,14 +11300,14 @@
       <c r="Z102" s="9"/>
       <c r="AA102" s="9"/>
       <c r="AB102" s="9"/>
-      <c r="AC102" s="116"/>
-      <c r="AD102" s="126"/>
+      <c r="AC102" s="115"/>
+      <c r="AD102" s="118"/>
       <c r="AE102" s="2" t="str">
-        <f>IF(SUM(Q102:AD102)&gt;0,SUM(Q102:AD102),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AF102" s="77" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -11371,14 +11342,14 @@
       <c r="Z103" s="9"/>
       <c r="AA103" s="9"/>
       <c r="AB103" s="9"/>
-      <c r="AC103" s="116"/>
+      <c r="AC103" s="115"/>
       <c r="AD103" s="7"/>
       <c r="AE103" s="2" t="str">
-        <f>IF(SUM(Q103:AD103)&gt;0,SUM(Q103:AD103),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AF103" s="77" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -11413,14 +11384,14 @@
       <c r="Z104" s="9"/>
       <c r="AA104" s="9"/>
       <c r="AB104" s="9"/>
-      <c r="AC104" s="116"/>
+      <c r="AC104" s="115"/>
       <c r="AD104" s="7"/>
       <c r="AE104" s="2" t="str">
-        <f>IF(SUM(Q104:AD104)&gt;0,SUM(Q104:AD104),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AF104" s="77" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -11470,16 +11441,16 @@
       <c r="Z105" s="9"/>
       <c r="AA105" s="9"/>
       <c r="AB105" s="9"/>
-      <c r="AC105" s="116"/>
+      <c r="AC105" s="115"/>
       <c r="AD105" s="54">
         <v>1</v>
       </c>
       <c r="AE105" s="2">
-        <f>IF(SUM(Q105:AD105)&gt;0,SUM(Q105:AD105),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF105" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
     </row>
@@ -11529,16 +11500,16 @@
       <c r="Z106" s="9"/>
       <c r="AA106" s="9"/>
       <c r="AB106" s="9"/>
-      <c r="AC106" s="116"/>
+      <c r="AC106" s="115"/>
       <c r="AD106" s="54">
         <v>1</v>
       </c>
       <c r="AE106" s="2">
-        <f>IF(SUM(Q106:AD106)&gt;0,SUM(Q106:AD106),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF106" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
     </row>
@@ -11572,14 +11543,14 @@
       <c r="Z107" s="9"/>
       <c r="AA107" s="9"/>
       <c r="AB107" s="9"/>
-      <c r="AC107" s="116"/>
+      <c r="AC107" s="115"/>
       <c r="AD107" s="7"/>
       <c r="AE107" s="2" t="str">
-        <f>IF(SUM(Q107:AD107)&gt;0,SUM(Q107:AD107),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AF107" s="77" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -11614,14 +11585,14 @@
       <c r="Z108" s="9"/>
       <c r="AA108" s="9"/>
       <c r="AB108" s="9"/>
-      <c r="AC108" s="116"/>
+      <c r="AC108" s="115"/>
       <c r="AD108" s="7"/>
       <c r="AE108" s="2" t="str">
-        <f>IF(SUM(Q108:AD108)&gt;0,SUM(Q108:AD108),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AF108" s="77" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -11631,7 +11602,7 @@
       </c>
       <c r="B109" s="12"/>
       <c r="C109" s="101" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D109" s="67" t="s">
         <v>11</v>
@@ -11671,16 +11642,16 @@
       <c r="Z109" s="9"/>
       <c r="AA109" s="9"/>
       <c r="AB109" s="9"/>
-      <c r="AC109" s="116"/>
+      <c r="AC109" s="115"/>
       <c r="AD109" s="54">
         <v>1</v>
       </c>
       <c r="AE109" s="2">
-        <f>IF(SUM(Q109:AD109)&gt;0,SUM(Q109:AD109),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF109" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
     </row>
@@ -11690,7 +11661,7 @@
       </c>
       <c r="B110" s="12"/>
       <c r="C110" s="24" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D110" s="67" t="s">
         <v>11</v>
@@ -11730,16 +11701,16 @@
       <c r="Z110" s="9"/>
       <c r="AA110" s="9"/>
       <c r="AB110" s="9"/>
-      <c r="AC110" s="116"/>
+      <c r="AC110" s="115"/>
       <c r="AD110" s="54">
         <v>1</v>
       </c>
       <c r="AE110" s="2">
-        <f>IF(SUM(Q110:AD110)&gt;0,SUM(Q110:AD110),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF110" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
     </row>
@@ -11789,16 +11760,16 @@
       <c r="Z111" s="9"/>
       <c r="AA111" s="9"/>
       <c r="AB111" s="9"/>
-      <c r="AC111" s="116"/>
+      <c r="AC111" s="115"/>
       <c r="AD111" s="54">
         <v>1</v>
       </c>
       <c r="AE111" s="2">
-        <f>IF(SUM(Q111:AD111)&gt;0,SUM(Q111:AD111),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF111" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
     </row>
@@ -11848,16 +11819,16 @@
       <c r="Z112" s="9"/>
       <c r="AA112" s="9"/>
       <c r="AB112" s="9"/>
-      <c r="AC112" s="116"/>
+      <c r="AC112" s="115"/>
       <c r="AD112" s="54">
         <v>1</v>
       </c>
       <c r="AE112" s="2">
-        <f>IF(SUM(Q112:AD112)&gt;0,SUM(Q112:AD112),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF112" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
     </row>
@@ -11892,14 +11863,14 @@
       <c r="Z113" s="9"/>
       <c r="AA113" s="9"/>
       <c r="AB113" s="9"/>
-      <c r="AC113" s="116"/>
+      <c r="AC113" s="115"/>
       <c r="AD113" s="7"/>
       <c r="AE113" s="2" t="str">
-        <f>IF(SUM(Q113:AD113)&gt;0,SUM(Q113:AD113),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AF113" s="77" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -11934,14 +11905,14 @@
       <c r="Z114" s="9"/>
       <c r="AA114" s="9"/>
       <c r="AB114" s="9"/>
-      <c r="AC114" s="116"/>
+      <c r="AC114" s="115"/>
       <c r="AD114" s="7"/>
       <c r="AE114" s="2" t="str">
-        <f>IF(SUM(Q114:AD114)&gt;0,SUM(Q114:AD114),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AF114" s="77" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -11977,14 +11948,14 @@
       <c r="Z115" s="9"/>
       <c r="AA115" s="9"/>
       <c r="AB115" s="9"/>
-      <c r="AC115" s="116"/>
+      <c r="AC115" s="115"/>
       <c r="AD115" s="7"/>
       <c r="AE115" s="2" t="str">
-        <f>IF(SUM(Q115:AD115)&gt;0,SUM(Q115:AD115),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AF115" s="77" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -12020,14 +11991,14 @@
       <c r="Z116" s="9"/>
       <c r="AA116" s="9"/>
       <c r="AB116" s="9"/>
-      <c r="AC116" s="116"/>
+      <c r="AC116" s="115"/>
       <c r="AD116" s="7"/>
       <c r="AE116" s="2" t="str">
-        <f>IF(SUM(Q116:AD116)&gt;0,SUM(Q116:AD116),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AF116" s="77" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -12063,14 +12034,14 @@
       <c r="Z117" s="9"/>
       <c r="AA117" s="9"/>
       <c r="AB117" s="9"/>
-      <c r="AC117" s="116"/>
+      <c r="AC117" s="115"/>
       <c r="AD117" s="7"/>
       <c r="AE117" s="2" t="str">
-        <f>IF(SUM(Q117:AD117)&gt;0,SUM(Q117:AD117),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AF117" s="77" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -12106,14 +12077,14 @@
       <c r="Z118" s="9"/>
       <c r="AA118" s="9"/>
       <c r="AB118" s="9"/>
-      <c r="AC118" s="116"/>
+      <c r="AC118" s="115"/>
       <c r="AD118" s="7"/>
       <c r="AE118" s="2" t="str">
-        <f>IF(SUM(Q118:AD118)&gt;0,SUM(Q118:AD118),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="AF118" s="77" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -12165,14 +12136,14 @@
         <v>1</v>
       </c>
       <c r="AB119" s="9"/>
-      <c r="AC119" s="116"/>
+      <c r="AC119" s="115"/>
       <c r="AD119" s="7"/>
       <c r="AE119" s="2">
-        <f>IF(SUM(Q119:AD119)&gt;0,SUM(Q119:AD119),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF119" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>11</v>
       </c>
     </row>
@@ -12224,14 +12195,14 @@
       <c r="Z120" s="9"/>
       <c r="AA120" s="9"/>
       <c r="AB120" s="9"/>
-      <c r="AC120" s="116"/>
+      <c r="AC120" s="115"/>
       <c r="AD120" s="7"/>
       <c r="AE120" s="2">
-        <f>IF(SUM(Q120:AD120)&gt;0,SUM(Q120:AD120),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF120" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
@@ -12281,16 +12252,16 @@
       <c r="Z121" s="9"/>
       <c r="AA121" s="9"/>
       <c r="AB121" s="9"/>
-      <c r="AC121" s="116"/>
+      <c r="AC121" s="115"/>
       <c r="AD121" s="54">
         <v>1</v>
       </c>
       <c r="AE121" s="2">
-        <f>IF(SUM(Q121:AD121)&gt;0,SUM(Q121:AD121),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF121" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
     </row>
@@ -12340,16 +12311,16 @@
       <c r="Z122" s="9"/>
       <c r="AA122" s="9"/>
       <c r="AB122" s="9"/>
-      <c r="AC122" s="116"/>
+      <c r="AC122" s="115"/>
       <c r="AD122" s="54">
         <v>1</v>
       </c>
       <c r="AE122" s="2">
-        <f>IF(SUM(Q122:AD122)&gt;0,SUM(Q122:AD122),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF122" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
     </row>
@@ -12395,14 +12366,14 @@
       <c r="Z123" s="9"/>
       <c r="AA123" s="9"/>
       <c r="AB123" s="9"/>
-      <c r="AC123" s="116"/>
+      <c r="AC123" s="115"/>
       <c r="AD123" s="7"/>
       <c r="AE123" s="2">
-        <f>IF(SUM(Q123:AD123)&gt;0,SUM(Q123:AD123),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF123" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
     </row>
@@ -12454,14 +12425,14 @@
       <c r="Z124" s="9"/>
       <c r="AA124" s="9"/>
       <c r="AB124" s="9"/>
-      <c r="AC124" s="116"/>
+      <c r="AC124" s="115"/>
       <c r="AD124" s="7"/>
       <c r="AE124" s="2">
-        <f>IF(SUM(Q124:AD124)&gt;0,SUM(Q124:AD124),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF124" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
     </row>
@@ -12513,14 +12484,14 @@
       <c r="AB125" s="53">
         <v>1</v>
       </c>
-      <c r="AC125" s="116"/>
+      <c r="AC125" s="115"/>
       <c r="AD125" s="7"/>
       <c r="AE125" s="2">
-        <f>IF(SUM(Q125:AD125)&gt;0,SUM(Q125:AD125),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF125" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12</v>
       </c>
     </row>
@@ -12573,14 +12544,14 @@
       <c r="Z126" s="9"/>
       <c r="AA126" s="9"/>
       <c r="AB126" s="9"/>
-      <c r="AC126" s="116"/>
+      <c r="AC126" s="115"/>
       <c r="AD126" s="7"/>
       <c r="AE126" s="2">
-        <f>IF(SUM(Q126:AD126)&gt;0,SUM(Q126:AD126),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF126" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
     </row>
@@ -12631,14 +12602,14 @@
       <c r="Z127" s="9"/>
       <c r="AA127" s="9"/>
       <c r="AB127" s="9"/>
-      <c r="AC127" s="116"/>
+      <c r="AC127" s="115"/>
       <c r="AD127" s="7"/>
       <c r="AE127" s="2">
-        <f>IF(SUM(Q127:AD127)&gt;0,SUM(Q127:AD127),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF127" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
     </row>
@@ -12692,14 +12663,14 @@
       <c r="Z128" s="9"/>
       <c r="AA128" s="9"/>
       <c r="AB128" s="9"/>
-      <c r="AC128" s="116"/>
+      <c r="AC128" s="115"/>
       <c r="AD128" s="7"/>
       <c r="AE128" s="2">
-        <f>IF(SUM(Q128:AD128)&gt;0,SUM(Q128:AD128),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF128" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
     </row>
@@ -12753,14 +12724,14 @@
       <c r="Z129" s="9"/>
       <c r="AA129" s="9"/>
       <c r="AB129" s="9"/>
-      <c r="AC129" s="116"/>
+      <c r="AC129" s="115"/>
       <c r="AD129" s="7"/>
       <c r="AE129" s="2">
-        <f>IF(SUM(Q129:AD129)&gt;0,SUM(Q129:AD129),"")</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AF129" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
     </row>
@@ -12814,14 +12785,14 @@
       <c r="Z130" s="9"/>
       <c r="AA130" s="9"/>
       <c r="AB130" s="9"/>
-      <c r="AC130" s="116"/>
+      <c r="AC130" s="115"/>
       <c r="AD130" s="7"/>
       <c r="AE130" s="2">
-        <f>IF(SUM(Q130:AD130)&gt;0,SUM(Q130:AD130),"")</f>
+        <f t="shared" ref="AE130:AE193" si="4">IF(SUM(Q130:AD130)&gt;0,SUM(Q130:AD130),"")</f>
         <v>1</v>
       </c>
       <c r="AF130" s="77">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
     </row>
@@ -12875,14 +12846,14 @@
       <c r="Z131" s="9"/>
       <c r="AA131" s="9"/>
       <c r="AB131" s="9"/>
-      <c r="AC131" s="116"/>
+      <c r="AC131" s="115"/>
       <c r="AD131" s="7"/>
       <c r="AE131" s="2">
-        <f>IF(SUM(Q131:AD131)&gt;0,SUM(Q131:AD131),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF131" s="77">
-        <f t="shared" ref="AF131:AF194" si="2">IF(SUM(Q131:AD131)&lt;1,"",Q131*1+R131*2+S131*3+T131*4+U131*5+V131*6+W131*7+X131*8+Y131*9+Z131*10+AA131*11+AB131*12+AC131*13+AD131*14)</f>
+        <f t="shared" ref="AF131:AF194" si="5">IF(SUM(Q131:AD131)&lt;1,"",Q131*1+R131*2+S131*3+T131*4+U131*5+V131*6+W131*7+X131*8+Y131*9+Z131*10+AA131*11+AB131*12+AC131*13+AD131*14)</f>
         <v>5</v>
       </c>
     </row>
@@ -12934,14 +12905,14 @@
       <c r="Z132" s="9"/>
       <c r="AA132" s="9"/>
       <c r="AB132" s="9"/>
-      <c r="AC132" s="116"/>
+      <c r="AC132" s="115"/>
       <c r="AD132" s="7"/>
       <c r="AE132" s="2">
-        <f>IF(SUM(Q132:AD132)&gt;0,SUM(Q132:AD132),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF132" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
     </row>
@@ -12995,14 +12966,14 @@
       <c r="Z133" s="9"/>
       <c r="AA133" s="9"/>
       <c r="AB133" s="9"/>
-      <c r="AC133" s="116"/>
+      <c r="AC133" s="115"/>
       <c r="AD133" s="7"/>
       <c r="AE133" s="2">
-        <f>IF(SUM(Q133:AD133)&gt;0,SUM(Q133:AD133),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF133" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
     </row>
@@ -13054,14 +13025,14 @@
       <c r="Z134" s="9"/>
       <c r="AA134" s="9"/>
       <c r="AB134" s="9"/>
-      <c r="AC134" s="116"/>
+      <c r="AC134" s="115"/>
       <c r="AD134" s="7"/>
       <c r="AE134" s="2">
-        <f>IF(SUM(Q134:AD134)&gt;0,SUM(Q134:AD134),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF134" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
     </row>
@@ -13113,14 +13084,14 @@
       <c r="Z135" s="9"/>
       <c r="AA135" s="9"/>
       <c r="AB135" s="9"/>
-      <c r="AC135" s="116"/>
+      <c r="AC135" s="115"/>
       <c r="AD135" s="7"/>
       <c r="AE135" s="2">
-        <f>IF(SUM(Q135:AD135)&gt;0,SUM(Q135:AD135),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF135" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
     </row>
@@ -13172,14 +13143,14 @@
       <c r="Z136" s="9"/>
       <c r="AA136" s="9"/>
       <c r="AB136" s="9"/>
-      <c r="AC136" s="116"/>
+      <c r="AC136" s="115"/>
       <c r="AD136" s="7"/>
       <c r="AE136" s="2">
-        <f>IF(SUM(Q136:AD136)&gt;0,SUM(Q136:AD136),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF136" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
     </row>
@@ -13231,14 +13202,14 @@
       <c r="Z137" s="9"/>
       <c r="AA137" s="9"/>
       <c r="AB137" s="9"/>
-      <c r="AC137" s="116"/>
+      <c r="AC137" s="115"/>
       <c r="AD137" s="7"/>
       <c r="AE137" s="2">
-        <f>IF(SUM(Q137:AD137)&gt;0,SUM(Q137:AD137),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF137" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
     </row>
@@ -13292,14 +13263,14 @@
       <c r="Z138" s="9"/>
       <c r="AA138" s="9"/>
       <c r="AB138" s="9"/>
-      <c r="AC138" s="116"/>
+      <c r="AC138" s="115"/>
       <c r="AD138" s="7"/>
       <c r="AE138" s="2">
-        <f>IF(SUM(Q138:AD138)&gt;0,SUM(Q138:AD138),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF138" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
@@ -13353,14 +13324,14 @@
       <c r="Z139" s="9"/>
       <c r="AA139" s="9"/>
       <c r="AB139" s="9"/>
-      <c r="AC139" s="116"/>
+      <c r="AC139" s="115"/>
       <c r="AD139" s="7"/>
       <c r="AE139" s="2">
-        <f>IF(SUM(Q139:AD139)&gt;0,SUM(Q139:AD139),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF139" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
@@ -13414,14 +13385,14 @@
       <c r="Z140" s="9"/>
       <c r="AA140" s="9"/>
       <c r="AB140" s="9"/>
-      <c r="AC140" s="116"/>
+      <c r="AC140" s="115"/>
       <c r="AD140" s="7"/>
       <c r="AE140" s="2">
-        <f>IF(SUM(Q140:AD140)&gt;0,SUM(Q140:AD140),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF140" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
@@ -13475,14 +13446,14 @@
       <c r="Z141" s="9"/>
       <c r="AA141" s="9"/>
       <c r="AB141" s="9"/>
-      <c r="AC141" s="116"/>
+      <c r="AC141" s="115"/>
       <c r="AD141" s="7"/>
       <c r="AE141" s="2">
-        <f>IF(SUM(Q141:AD141)&gt;0,SUM(Q141:AD141),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF141" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
     </row>
@@ -13536,14 +13507,14 @@
       <c r="Z142" s="9"/>
       <c r="AA142" s="9"/>
       <c r="AB142" s="9"/>
-      <c r="AC142" s="116"/>
+      <c r="AC142" s="115"/>
       <c r="AD142" s="7"/>
       <c r="AE142" s="2">
-        <f>IF(SUM(Q142:AD142)&gt;0,SUM(Q142:AD142),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF142" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
     </row>
@@ -13595,14 +13566,14 @@
       <c r="Z143" s="9"/>
       <c r="AA143" s="9"/>
       <c r="AB143" s="9"/>
-      <c r="AC143" s="116"/>
+      <c r="AC143" s="115"/>
       <c r="AD143" s="7"/>
       <c r="AE143" s="2">
-        <f>IF(SUM(Q143:AD143)&gt;0,SUM(Q143:AD143),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF143" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
     </row>
@@ -13657,14 +13628,14 @@
       <c r="Z144" s="9"/>
       <c r="AA144" s="9"/>
       <c r="AB144" s="9"/>
-      <c r="AC144" s="116"/>
+      <c r="AC144" s="115"/>
       <c r="AD144" s="7"/>
       <c r="AE144" s="2">
-        <f>IF(SUM(Q144:AD144)&gt;0,SUM(Q144:AD144),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF144" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
     </row>
@@ -13718,14 +13689,14 @@
       <c r="Z145" s="9"/>
       <c r="AA145" s="9"/>
       <c r="AB145" s="9"/>
-      <c r="AC145" s="116"/>
+      <c r="AC145" s="115"/>
       <c r="AD145" s="7"/>
       <c r="AE145" s="2">
-        <f>IF(SUM(Q145:AD145)&gt;0,SUM(Q145:AD145),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF145" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
     </row>
@@ -13780,14 +13751,14 @@
       <c r="Z146" s="9"/>
       <c r="AA146" s="9"/>
       <c r="AB146" s="9"/>
-      <c r="AC146" s="116"/>
+      <c r="AC146" s="115"/>
       <c r="AD146" s="7"/>
       <c r="AE146" s="2">
-        <f>IF(SUM(Q146:AD146)&gt;0,SUM(Q146:AD146),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF146" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
     </row>
@@ -13842,14 +13813,14 @@
       <c r="Z147" s="9"/>
       <c r="AA147" s="9"/>
       <c r="AB147" s="9"/>
-      <c r="AC147" s="116"/>
+      <c r="AC147" s="115"/>
       <c r="AD147" s="7"/>
       <c r="AE147" s="2">
-        <f>IF(SUM(Q147:AD147)&gt;0,SUM(Q147:AD147),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF147" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
     </row>
@@ -13904,14 +13875,14 @@
       <c r="Z148" s="9"/>
       <c r="AA148" s="9"/>
       <c r="AB148" s="9"/>
-      <c r="AC148" s="116"/>
+      <c r="AC148" s="115"/>
       <c r="AD148" s="7"/>
       <c r="AE148" s="2">
-        <f>IF(SUM(Q148:AD148)&gt;0,SUM(Q148:AD148),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF148" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
     </row>
@@ -13964,14 +13935,14 @@
       <c r="Z149" s="9"/>
       <c r="AA149" s="9"/>
       <c r="AB149" s="9"/>
-      <c r="AC149" s="116"/>
+      <c r="AC149" s="115"/>
       <c r="AD149" s="7"/>
       <c r="AE149" s="2">
-        <f>IF(SUM(Q149:AD149)&gt;0,SUM(Q149:AD149),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF149" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
     </row>
@@ -14023,14 +13994,14 @@
       <c r="Z150" s="9"/>
       <c r="AA150" s="9"/>
       <c r="AB150" s="9"/>
-      <c r="AC150" s="116"/>
+      <c r="AC150" s="115"/>
       <c r="AD150" s="7"/>
       <c r="AE150" s="2">
-        <f>IF(SUM(Q150:AD150)&gt;0,SUM(Q150:AD150),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF150" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
     </row>
@@ -14083,14 +14054,14 @@
       <c r="Z151" s="9"/>
       <c r="AA151" s="9"/>
       <c r="AB151" s="9"/>
-      <c r="AC151" s="116"/>
+      <c r="AC151" s="115"/>
       <c r="AD151" s="7"/>
       <c r="AE151" s="2">
-        <f>IF(SUM(Q151:AD151)&gt;0,SUM(Q151:AD151),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF151" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
     </row>
@@ -14143,14 +14114,14 @@
       <c r="Z152" s="9"/>
       <c r="AA152" s="9"/>
       <c r="AB152" s="9"/>
-      <c r="AC152" s="116"/>
+      <c r="AC152" s="115"/>
       <c r="AD152" s="7"/>
       <c r="AE152" s="2">
-        <f>IF(SUM(Q152:AD152)&gt;0,SUM(Q152:AD152),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF152" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
     </row>
@@ -14205,14 +14176,14 @@
       <c r="Z153" s="9"/>
       <c r="AA153" s="9"/>
       <c r="AB153" s="9"/>
-      <c r="AC153" s="116"/>
+      <c r="AC153" s="115"/>
       <c r="AD153" s="7"/>
       <c r="AE153" s="2">
-        <f>IF(SUM(Q153:AD153)&gt;0,SUM(Q153:AD153),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF153" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
     </row>
@@ -14267,14 +14238,14 @@
       <c r="Z154" s="9"/>
       <c r="AA154" s="9"/>
       <c r="AB154" s="9"/>
-      <c r="AC154" s="116"/>
+      <c r="AC154" s="115"/>
       <c r="AD154" s="7"/>
       <c r="AE154" s="2">
-        <f>IF(SUM(Q154:AD154)&gt;0,SUM(Q154:AD154),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF154" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
     </row>
@@ -14329,14 +14300,14 @@
       <c r="Z155" s="9"/>
       <c r="AA155" s="9"/>
       <c r="AB155" s="9"/>
-      <c r="AC155" s="116"/>
+      <c r="AC155" s="115"/>
       <c r="AD155" s="7"/>
       <c r="AE155" s="2">
-        <f>IF(SUM(Q155:AD155)&gt;0,SUM(Q155:AD155),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF155" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
     </row>
@@ -14390,14 +14361,14 @@
       <c r="Z156" s="9"/>
       <c r="AA156" s="9"/>
       <c r="AB156" s="9"/>
-      <c r="AC156" s="116"/>
+      <c r="AC156" s="115"/>
       <c r="AD156" s="7"/>
       <c r="AE156" s="2">
-        <f>IF(SUM(Q156:AD156)&gt;0,SUM(Q156:AD156),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF156" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
     </row>
@@ -14451,14 +14422,14 @@
       <c r="Z157" s="9"/>
       <c r="AA157" s="9"/>
       <c r="AB157" s="9"/>
-      <c r="AC157" s="116"/>
+      <c r="AC157" s="115"/>
       <c r="AD157" s="7"/>
       <c r="AE157" s="2">
-        <f>IF(SUM(Q157:AD157)&gt;0,SUM(Q157:AD157),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF157" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
@@ -14512,14 +14483,14 @@
       <c r="Z158" s="9"/>
       <c r="AA158" s="9"/>
       <c r="AB158" s="9"/>
-      <c r="AC158" s="116"/>
+      <c r="AC158" s="115"/>
       <c r="AD158" s="7"/>
       <c r="AE158" s="2">
-        <f>IF(SUM(Q158:AD158)&gt;0,SUM(Q158:AD158),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF158" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
@@ -14571,14 +14542,14 @@
       <c r="Z159" s="9"/>
       <c r="AA159" s="9"/>
       <c r="AB159" s="9"/>
-      <c r="AC159" s="116"/>
+      <c r="AC159" s="115"/>
       <c r="AD159" s="7"/>
       <c r="AE159" s="2">
-        <f>IF(SUM(Q159:AD159)&gt;0,SUM(Q159:AD159),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF159" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
@@ -14632,14 +14603,14 @@
       <c r="Z160" s="9"/>
       <c r="AA160" s="9"/>
       <c r="AB160" s="9"/>
-      <c r="AC160" s="116"/>
+      <c r="AC160" s="115"/>
       <c r="AD160" s="7"/>
       <c r="AE160" s="2">
-        <f>IF(SUM(Q160:AD160)&gt;0,SUM(Q160:AD160),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF160" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
@@ -14693,14 +14664,14 @@
       <c r="Z161" s="9"/>
       <c r="AA161" s="9"/>
       <c r="AB161" s="9"/>
-      <c r="AC161" s="116"/>
+      <c r="AC161" s="115"/>
       <c r="AD161" s="7"/>
       <c r="AE161" s="2">
-        <f>IF(SUM(Q161:AD161)&gt;0,SUM(Q161:AD161),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF161" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
     </row>
@@ -14754,14 +14725,14 @@
       <c r="Z162" s="9"/>
       <c r="AA162" s="9"/>
       <c r="AB162" s="9"/>
-      <c r="AC162" s="116"/>
+      <c r="AC162" s="115"/>
       <c r="AD162" s="7"/>
       <c r="AE162" s="2">
-        <f>IF(SUM(Q162:AD162)&gt;0,SUM(Q162:AD162),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF162" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
     </row>
@@ -14813,14 +14784,14 @@
       <c r="Z163" s="9"/>
       <c r="AA163" s="9"/>
       <c r="AB163" s="9"/>
-      <c r="AC163" s="116"/>
+      <c r="AC163" s="115"/>
       <c r="AD163" s="7"/>
       <c r="AE163" s="2">
-        <f>IF(SUM(Q163:AD163)&gt;0,SUM(Q163:AD163),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF163" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
     </row>
@@ -14872,14 +14843,14 @@
       <c r="Z164" s="9"/>
       <c r="AA164" s="9"/>
       <c r="AB164" s="9"/>
-      <c r="AC164" s="116"/>
+      <c r="AC164" s="115"/>
       <c r="AD164" s="7"/>
       <c r="AE164" s="2">
-        <f>IF(SUM(Q164:AD164)&gt;0,SUM(Q164:AD164),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF164" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
     </row>
@@ -14931,14 +14902,14 @@
       <c r="Z165" s="9"/>
       <c r="AA165" s="9"/>
       <c r="AB165" s="9"/>
-      <c r="AC165" s="116"/>
+      <c r="AC165" s="115"/>
       <c r="AD165" s="7"/>
       <c r="AE165" s="2">
-        <f>IF(SUM(Q165:AD165)&gt;0,SUM(Q165:AD165),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF165" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
     </row>
@@ -14990,14 +14961,14 @@
       <c r="Z166" s="9"/>
       <c r="AA166" s="9"/>
       <c r="AB166" s="9"/>
-      <c r="AC166" s="116"/>
+      <c r="AC166" s="115"/>
       <c r="AD166" s="7"/>
       <c r="AE166" s="2">
-        <f>IF(SUM(Q166:AD166)&gt;0,SUM(Q166:AD166),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF166" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
     </row>
@@ -15051,14 +15022,14 @@
       <c r="Z167" s="9"/>
       <c r="AA167" s="9"/>
       <c r="AB167" s="9"/>
-      <c r="AC167" s="116"/>
+      <c r="AC167" s="115"/>
       <c r="AD167" s="7"/>
       <c r="AE167" s="2">
-        <f>IF(SUM(Q167:AD167)&gt;0,SUM(Q167:AD167),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF167" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
     </row>
@@ -15110,14 +15081,14 @@
       <c r="Z168" s="9"/>
       <c r="AA168" s="9"/>
       <c r="AB168" s="9"/>
-      <c r="AC168" s="116"/>
+      <c r="AC168" s="115"/>
       <c r="AD168" s="7"/>
       <c r="AE168" s="2">
-        <f>IF(SUM(Q168:AD168)&gt;0,SUM(Q168:AD168),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF168" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
     </row>
@@ -15169,14 +15140,14 @@
       <c r="Z169" s="9"/>
       <c r="AA169" s="9"/>
       <c r="AB169" s="9"/>
-      <c r="AC169" s="116"/>
+      <c r="AC169" s="115"/>
       <c r="AD169" s="7"/>
       <c r="AE169" s="2">
-        <f>IF(SUM(Q169:AD169)&gt;0,SUM(Q169:AD169),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF169" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
     </row>
@@ -15230,14 +15201,14 @@
       <c r="Z170" s="9"/>
       <c r="AA170" s="9"/>
       <c r="AB170" s="9"/>
-      <c r="AC170" s="116"/>
+      <c r="AC170" s="115"/>
       <c r="AD170" s="7"/>
       <c r="AE170" s="2">
-        <f>IF(SUM(Q170:AD170)&gt;0,SUM(Q170:AD170),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF170" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
@@ -15291,14 +15262,14 @@
       <c r="Z171" s="9"/>
       <c r="AA171" s="9"/>
       <c r="AB171" s="9"/>
-      <c r="AC171" s="116"/>
+      <c r="AC171" s="115"/>
       <c r="AD171" s="7"/>
       <c r="AE171" s="2">
-        <f>IF(SUM(Q171:AD171)&gt;0,SUM(Q171:AD171),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF171" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
     </row>
@@ -15352,14 +15323,14 @@
       <c r="Z172" s="9"/>
       <c r="AA172" s="9"/>
       <c r="AB172" s="9"/>
-      <c r="AC172" s="116"/>
+      <c r="AC172" s="115"/>
       <c r="AD172" s="7"/>
       <c r="AE172" s="2">
-        <f>IF(SUM(Q172:AD172)&gt;0,SUM(Q172:AD172),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF172" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
@@ -15413,14 +15384,14 @@
       <c r="Z173" s="9"/>
       <c r="AA173" s="9"/>
       <c r="AB173" s="9"/>
-      <c r="AC173" s="116"/>
+      <c r="AC173" s="115"/>
       <c r="AD173" s="7"/>
       <c r="AE173" s="2">
-        <f>IF(SUM(Q173:AD173)&gt;0,SUM(Q173:AD173),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF173" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
     </row>
@@ -15474,14 +15445,14 @@
       <c r="Z174" s="9"/>
       <c r="AA174" s="9"/>
       <c r="AB174" s="9"/>
-      <c r="AC174" s="116"/>
+      <c r="AC174" s="115"/>
       <c r="AD174" s="7"/>
       <c r="AE174" s="2">
-        <f>IF(SUM(Q174:AD174)&gt;0,SUM(Q174:AD174),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF174" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
     </row>
@@ -15535,14 +15506,14 @@
       <c r="Z175" s="9"/>
       <c r="AA175" s="9"/>
       <c r="AB175" s="9"/>
-      <c r="AC175" s="116"/>
+      <c r="AC175" s="115"/>
       <c r="AD175" s="7"/>
       <c r="AE175" s="2">
-        <f>IF(SUM(Q175:AD175)&gt;0,SUM(Q175:AD175),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF175" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
     </row>
@@ -15596,14 +15567,14 @@
       <c r="Z176" s="9"/>
       <c r="AA176" s="9"/>
       <c r="AB176" s="9"/>
-      <c r="AC176" s="116"/>
+      <c r="AC176" s="115"/>
       <c r="AD176" s="7"/>
       <c r="AE176" s="2">
-        <f>IF(SUM(Q176:AD176)&gt;0,SUM(Q176:AD176),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF176" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
@@ -15655,14 +15626,14 @@
       <c r="Z177" s="9"/>
       <c r="AA177" s="9"/>
       <c r="AB177" s="9"/>
-      <c r="AC177" s="116"/>
+      <c r="AC177" s="115"/>
       <c r="AD177" s="7"/>
       <c r="AE177" s="2">
-        <f>IF(SUM(Q177:AD177)&gt;0,SUM(Q177:AD177),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF177" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
     </row>
@@ -15714,14 +15685,14 @@
       <c r="Z178" s="9"/>
       <c r="AA178" s="9"/>
       <c r="AB178" s="9"/>
-      <c r="AC178" s="116"/>
+      <c r="AC178" s="115"/>
       <c r="AD178" s="7"/>
       <c r="AE178" s="2">
-        <f>IF(SUM(Q178:AD178)&gt;0,SUM(Q178:AD178),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF178" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
     </row>
@@ -15773,14 +15744,14 @@
       <c r="Z179" s="9"/>
       <c r="AA179" s="9"/>
       <c r="AB179" s="9"/>
-      <c r="AC179" s="116"/>
+      <c r="AC179" s="115"/>
       <c r="AD179" s="7"/>
       <c r="AE179" s="2">
-        <f>IF(SUM(Q179:AD179)&gt;0,SUM(Q179:AD179),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF179" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
     </row>
@@ -15832,14 +15803,14 @@
       <c r="Z180" s="9"/>
       <c r="AA180" s="9"/>
       <c r="AB180" s="9"/>
-      <c r="AC180" s="116"/>
+      <c r="AC180" s="115"/>
       <c r="AD180" s="7"/>
       <c r="AE180" s="2">
-        <f>IF(SUM(Q180:AD180)&gt;0,SUM(Q180:AD180),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF180" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
@@ -15889,14 +15860,14 @@
       <c r="Z181" s="9"/>
       <c r="AA181" s="9"/>
       <c r="AB181" s="9"/>
-      <c r="AC181" s="116"/>
+      <c r="AC181" s="115"/>
       <c r="AD181" s="7"/>
       <c r="AE181" s="2">
-        <f>IF(SUM(Q181:AD181)&gt;0,SUM(Q181:AD181),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF181" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
@@ -15946,14 +15917,14 @@
       <c r="Z182" s="9"/>
       <c r="AA182" s="9"/>
       <c r="AB182" s="9"/>
-      <c r="AC182" s="116"/>
+      <c r="AC182" s="115"/>
       <c r="AD182" s="7"/>
       <c r="AE182" s="2">
-        <f>IF(SUM(Q182:AD182)&gt;0,SUM(Q182:AD182),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF182" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
@@ -16007,14 +15978,14 @@
       <c r="Z183" s="9"/>
       <c r="AA183" s="9"/>
       <c r="AB183" s="9"/>
-      <c r="AC183" s="116"/>
+      <c r="AC183" s="115"/>
       <c r="AD183" s="7"/>
       <c r="AE183" s="2">
-        <f>IF(SUM(Q183:AD183)&gt;0,SUM(Q183:AD183),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF183" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
     </row>
@@ -16068,14 +16039,14 @@
       <c r="Z184" s="9"/>
       <c r="AA184" s="9"/>
       <c r="AB184" s="9"/>
-      <c r="AC184" s="116"/>
+      <c r="AC184" s="115"/>
       <c r="AD184" s="7"/>
       <c r="AE184" s="2">
-        <f>IF(SUM(Q184:AD184)&gt;0,SUM(Q184:AD184),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF184" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
     </row>
@@ -16129,14 +16100,14 @@
       <c r="Z185" s="9"/>
       <c r="AA185" s="9"/>
       <c r="AB185" s="9"/>
-      <c r="AC185" s="116"/>
+      <c r="AC185" s="115"/>
       <c r="AD185" s="7"/>
       <c r="AE185" s="2">
-        <f>IF(SUM(Q185:AD185)&gt;0,SUM(Q185:AD185),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF185" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
@@ -16190,14 +16161,14 @@
       <c r="Z186" s="9"/>
       <c r="AA186" s="9"/>
       <c r="AB186" s="9"/>
-      <c r="AC186" s="116"/>
+      <c r="AC186" s="115"/>
       <c r="AD186" s="7"/>
       <c r="AE186" s="2">
-        <f>IF(SUM(Q186:AD186)&gt;0,SUM(Q186:AD186),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF186" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
     </row>
@@ -16249,14 +16220,14 @@
       <c r="Z187" s="9"/>
       <c r="AA187" s="9"/>
       <c r="AB187" s="9"/>
-      <c r="AC187" s="116"/>
+      <c r="AC187" s="115"/>
       <c r="AD187" s="7"/>
       <c r="AE187" s="2">
-        <f>IF(SUM(Q187:AD187)&gt;0,SUM(Q187:AD187),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF187" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
     </row>
@@ -16308,14 +16279,14 @@
       <c r="Z188" s="9"/>
       <c r="AA188" s="9"/>
       <c r="AB188" s="9"/>
-      <c r="AC188" s="116"/>
+      <c r="AC188" s="115"/>
       <c r="AD188" s="7"/>
       <c r="AE188" s="2">
-        <f>IF(SUM(Q188:AD188)&gt;0,SUM(Q188:AD188),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF188" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
     </row>
@@ -16367,14 +16338,14 @@
       <c r="Z189" s="9"/>
       <c r="AA189" s="9"/>
       <c r="AB189" s="9"/>
-      <c r="AC189" s="116"/>
+      <c r="AC189" s="115"/>
       <c r="AD189" s="7"/>
       <c r="AE189" s="2">
-        <f>IF(SUM(Q189:AD189)&gt;0,SUM(Q189:AD189),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF189" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
     </row>
@@ -16426,14 +16397,14 @@
       <c r="Z190" s="9"/>
       <c r="AA190" s="9"/>
       <c r="AB190" s="9"/>
-      <c r="AC190" s="116"/>
+      <c r="AC190" s="115"/>
       <c r="AD190" s="7"/>
       <c r="AE190" s="2">
-        <f>IF(SUM(Q190:AD190)&gt;0,SUM(Q190:AD190),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF190" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>9</v>
       </c>
     </row>
@@ -16479,14 +16450,14 @@
       <c r="Z191" s="9"/>
       <c r="AA191" s="9"/>
       <c r="AB191" s="9"/>
-      <c r="AC191" s="116"/>
+      <c r="AC191" s="115"/>
       <c r="AD191" s="7"/>
       <c r="AE191" s="2">
-        <f>IF(SUM(Q191:AD191)&gt;0,SUM(Q191:AD191),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF191" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
@@ -16532,14 +16503,14 @@
       <c r="Z192" s="9"/>
       <c r="AA192" s="9"/>
       <c r="AB192" s="9"/>
-      <c r="AC192" s="116"/>
+      <c r="AC192" s="115"/>
       <c r="AD192" s="7"/>
       <c r="AE192" s="2">
-        <f>IF(SUM(Q192:AD192)&gt;0,SUM(Q192:AD192),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF192" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
@@ -16584,14 +16555,14 @@
       <c r="Z193" s="9"/>
       <c r="AA193" s="9"/>
       <c r="AB193" s="9"/>
-      <c r="AC193" s="116"/>
+      <c r="AC193" s="115"/>
       <c r="AD193" s="7"/>
       <c r="AE193" s="2">
-        <f>IF(SUM(Q193:AD193)&gt;0,SUM(Q193:AD193),"")</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AF193" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
     </row>
@@ -16636,14 +16607,14 @@
       <c r="Z194" s="9"/>
       <c r="AA194" s="9"/>
       <c r="AB194" s="9"/>
-      <c r="AC194" s="116"/>
+      <c r="AC194" s="115"/>
       <c r="AD194" s="7"/>
       <c r="AE194" s="2">
-        <f>IF(SUM(Q194:AD194)&gt;0,SUM(Q194:AD194),"")</f>
+        <f t="shared" ref="AE194:AE257" si="6">IF(SUM(Q194:AD194)&gt;0,SUM(Q194:AD194),"")</f>
         <v>1</v>
       </c>
       <c r="AF194" s="77">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
     </row>
@@ -16688,14 +16659,14 @@
       <c r="Z195" s="9"/>
       <c r="AA195" s="9"/>
       <c r="AB195" s="9"/>
-      <c r="AC195" s="116"/>
+      <c r="AC195" s="115"/>
       <c r="AD195" s="7"/>
       <c r="AE195" s="2">
-        <f>IF(SUM(Q195:AD195)&gt;0,SUM(Q195:AD195),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF195" s="77">
-        <f t="shared" ref="AF195:AF258" si="3">IF(SUM(Q195:AD195)&lt;1,"",Q195*1+R195*2+S195*3+T195*4+U195*5+V195*6+W195*7+X195*8+Y195*9+Z195*10+AA195*11+AB195*12+AC195*13+AD195*14)</f>
+        <f t="shared" ref="AF195:AF258" si="7">IF(SUM(Q195:AD195)&lt;1,"",Q195*1+R195*2+S195*3+T195*4+U195*5+V195*6+W195*7+X195*8+Y195*9+Z195*10+AA195*11+AB195*12+AC195*13+AD195*14)</f>
         <v>6</v>
       </c>
     </row>
@@ -16740,14 +16711,14 @@
       <c r="Z196" s="9"/>
       <c r="AA196" s="9"/>
       <c r="AB196" s="9"/>
-      <c r="AC196" s="116"/>
+      <c r="AC196" s="115"/>
       <c r="AD196" s="7"/>
       <c r="AE196" s="2">
-        <f>IF(SUM(Q196:AD196)&gt;0,SUM(Q196:AD196),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF196" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
     </row>
@@ -16793,14 +16764,14 @@
       <c r="Z197" s="9"/>
       <c r="AA197" s="9"/>
       <c r="AB197" s="9"/>
-      <c r="AC197" s="116"/>
+      <c r="AC197" s="115"/>
       <c r="AD197" s="7"/>
       <c r="AE197" s="2">
-        <f>IF(SUM(Q197:AD197)&gt;0,SUM(Q197:AD197),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF197" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
     </row>
@@ -16846,14 +16817,14 @@
       <c r="Z198" s="9"/>
       <c r="AA198" s="9"/>
       <c r="AB198" s="9"/>
-      <c r="AC198" s="116"/>
+      <c r="AC198" s="115"/>
       <c r="AD198" s="7"/>
       <c r="AE198" s="2">
-        <f>IF(SUM(Q198:AD198)&gt;0,SUM(Q198:AD198),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF198" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
     </row>
@@ -16901,14 +16872,14 @@
       <c r="Z199" s="9"/>
       <c r="AA199" s="9"/>
       <c r="AB199" s="9"/>
-      <c r="AC199" s="116"/>
+      <c r="AC199" s="115"/>
       <c r="AD199" s="7"/>
       <c r="AE199" s="2">
-        <f>IF(SUM(Q199:AD199)&gt;0,SUM(Q199:AD199),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF199" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
@@ -16956,14 +16927,14 @@
       <c r="Z200" s="9"/>
       <c r="AA200" s="9"/>
       <c r="AB200" s="9"/>
-      <c r="AC200" s="116"/>
+      <c r="AC200" s="115"/>
       <c r="AD200" s="7"/>
       <c r="AE200" s="2">
-        <f>IF(SUM(Q200:AD200)&gt;0,SUM(Q200:AD200),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF200" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
@@ -17007,14 +16978,14 @@
       <c r="Z201" s="9"/>
       <c r="AA201" s="9"/>
       <c r="AB201" s="9"/>
-      <c r="AC201" s="116"/>
+      <c r="AC201" s="115"/>
       <c r="AD201" s="7"/>
       <c r="AE201" s="2">
-        <f>IF(SUM(Q201:AD201)&gt;0,SUM(Q201:AD201),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF201" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
     </row>
@@ -17058,14 +17029,14 @@
       <c r="Z202" s="9"/>
       <c r="AA202" s="9"/>
       <c r="AB202" s="9"/>
-      <c r="AC202" s="116"/>
+      <c r="AC202" s="115"/>
       <c r="AD202" s="7"/>
       <c r="AE202" s="2">
-        <f>IF(SUM(Q202:AD202)&gt;0,SUM(Q202:AD202),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF202" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
@@ -17111,14 +17082,14 @@
       <c r="Z203" s="9"/>
       <c r="AA203" s="9"/>
       <c r="AB203" s="9"/>
-      <c r="AC203" s="116"/>
+      <c r="AC203" s="115"/>
       <c r="AD203" s="7"/>
       <c r="AE203" s="2">
-        <f>IF(SUM(Q203:AD203)&gt;0,SUM(Q203:AD203),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF203" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
     </row>
@@ -17164,14 +17135,14 @@
       <c r="Z204" s="9"/>
       <c r="AA204" s="9"/>
       <c r="AB204" s="9"/>
-      <c r="AC204" s="116"/>
+      <c r="AC204" s="115"/>
       <c r="AD204" s="7"/>
       <c r="AE204" s="2">
-        <f>IF(SUM(Q204:AD204)&gt;0,SUM(Q204:AD204),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF204" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
     </row>
@@ -17217,14 +17188,14 @@
       <c r="Z205" s="9"/>
       <c r="AA205" s="9"/>
       <c r="AB205" s="9"/>
-      <c r="AC205" s="116"/>
+      <c r="AC205" s="115"/>
       <c r="AD205" s="7"/>
       <c r="AE205" s="2">
-        <f>IF(SUM(Q205:AD205)&gt;0,SUM(Q205:AD205),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF205" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
     </row>
@@ -17278,14 +17249,14 @@
       <c r="Z206" s="9"/>
       <c r="AA206" s="9"/>
       <c r="AB206" s="9"/>
-      <c r="AC206" s="116"/>
+      <c r="AC206" s="115"/>
       <c r="AD206" s="7"/>
       <c r="AE206" s="2">
-        <f>IF(SUM(Q206:AD206)&gt;0,SUM(Q206:AD206),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF206" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
     </row>
@@ -17329,14 +17300,14 @@
       <c r="Z207" s="9"/>
       <c r="AA207" s="9"/>
       <c r="AB207" s="9"/>
-      <c r="AC207" s="116"/>
+      <c r="AC207" s="115"/>
       <c r="AD207" s="7"/>
       <c r="AE207" s="2">
-        <f>IF(SUM(Q207:AD207)&gt;0,SUM(Q207:AD207),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF207" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
     </row>
@@ -17388,14 +17359,14 @@
       <c r="Z208" s="9"/>
       <c r="AA208" s="9"/>
       <c r="AB208" s="9"/>
-      <c r="AC208" s="116"/>
+      <c r="AC208" s="115"/>
       <c r="AD208" s="7"/>
       <c r="AE208" s="2">
-        <f>IF(SUM(Q208:AD208)&gt;0,SUM(Q208:AD208),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF208" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
     </row>
@@ -17447,14 +17418,14 @@
       <c r="Z209" s="9"/>
       <c r="AA209" s="9"/>
       <c r="AB209" s="9"/>
-      <c r="AC209" s="116"/>
+      <c r="AC209" s="115"/>
       <c r="AD209" s="7"/>
       <c r="AE209" s="2">
-        <f>IF(SUM(Q209:AD209)&gt;0,SUM(Q209:AD209),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF209" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
     </row>
@@ -17506,14 +17477,14 @@
       <c r="Z210" s="9"/>
       <c r="AA210" s="9"/>
       <c r="AB210" s="9"/>
-      <c r="AC210" s="116"/>
+      <c r="AC210" s="115"/>
       <c r="AD210" s="7"/>
       <c r="AE210" s="2">
-        <f>IF(SUM(Q210:AD210)&gt;0,SUM(Q210:AD210),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF210" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
     </row>
@@ -17563,14 +17534,14 @@
       <c r="Z211" s="9"/>
       <c r="AA211" s="9"/>
       <c r="AB211" s="9"/>
-      <c r="AC211" s="116"/>
+      <c r="AC211" s="115"/>
       <c r="AD211" s="7"/>
       <c r="AE211" s="2">
-        <f>IF(SUM(Q211:AD211)&gt;0,SUM(Q211:AD211),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF211" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
     </row>
@@ -17606,14 +17577,14 @@
       <c r="Z212" s="9"/>
       <c r="AA212" s="9"/>
       <c r="AB212" s="9"/>
-      <c r="AC212" s="116"/>
+      <c r="AC212" s="115"/>
       <c r="AD212" s="7"/>
       <c r="AE212" s="2" t="str">
-        <f>IF(SUM(Q212:AD212)&gt;0,SUM(Q212:AD212),"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AF212" s="77" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -17669,14 +17640,14 @@
       <c r="Z213" s="9"/>
       <c r="AA213" s="9"/>
       <c r="AB213" s="9"/>
-      <c r="AC213" s="116"/>
+      <c r="AC213" s="115"/>
       <c r="AD213" s="7"/>
       <c r="AE213" s="2">
-        <f>IF(SUM(Q213:AD213)&gt;0,SUM(Q213:AD213),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF213" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -17732,14 +17703,14 @@
       <c r="Z214" s="9"/>
       <c r="AA214" s="9"/>
       <c r="AB214" s="9"/>
-      <c r="AC214" s="116"/>
+      <c r="AC214" s="115"/>
       <c r="AD214" s="7"/>
       <c r="AE214" s="2">
-        <f>IF(SUM(Q214:AD214)&gt;0,SUM(Q214:AD214),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF214" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -17781,14 +17752,14 @@
       <c r="Z215" s="89"/>
       <c r="AA215" s="89"/>
       <c r="AB215" s="89"/>
-      <c r="AC215" s="115"/>
+      <c r="AC215" s="89"/>
       <c r="AD215" s="103"/>
       <c r="AE215" s="89" t="str">
-        <f>IF(SUM(Q215:AD215)&gt;0,SUM(Q215:AD215),"")</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AF215" s="77" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
     </row>
@@ -17832,14 +17803,14 @@
       <c r="AB216" s="53">
         <v>1</v>
       </c>
-      <c r="AC216" s="116"/>
+      <c r="AC216" s="115"/>
       <c r="AD216" s="7"/>
       <c r="AE216" s="2">
-        <f>IF(SUM(Q216:AD216)&gt;0,SUM(Q216:AD216),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF216" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>12</v>
       </c>
     </row>
@@ -17898,14 +17869,14 @@
       <c r="Z217" s="39"/>
       <c r="AA217" s="39"/>
       <c r="AB217" s="39"/>
-      <c r="AC217" s="118"/>
+      <c r="AC217" s="39"/>
       <c r="AD217" s="40"/>
       <c r="AE217" s="2">
-        <f>IF(SUM(Q217:AD217)&gt;0,SUM(Q217:AD217),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF217" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
     </row>
@@ -17964,14 +17935,14 @@
       <c r="Z218" s="39"/>
       <c r="AA218" s="39"/>
       <c r="AB218" s="39"/>
-      <c r="AC218" s="118"/>
+      <c r="AC218" s="39"/>
       <c r="AD218" s="40"/>
       <c r="AE218" s="2">
-        <f>IF(SUM(Q218:AD218)&gt;0,SUM(Q218:AD218),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF218" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
@@ -18030,14 +18001,14 @@
       <c r="Z219" s="39"/>
       <c r="AA219" s="39"/>
       <c r="AB219" s="39"/>
-      <c r="AC219" s="118"/>
+      <c r="AC219" s="39"/>
       <c r="AD219" s="40"/>
       <c r="AE219" s="2">
-        <f>IF(SUM(Q219:AD219)&gt;0,SUM(Q219:AD219),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF219" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
@@ -18096,14 +18067,14 @@
       <c r="Z220" s="39"/>
       <c r="AA220" s="39"/>
       <c r="AB220" s="39"/>
-      <c r="AC220" s="118"/>
+      <c r="AC220" s="39"/>
       <c r="AD220" s="40"/>
       <c r="AE220" s="2">
-        <f>IF(SUM(Q220:AD220)&gt;0,SUM(Q220:AD220),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF220" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
@@ -18156,14 +18127,14 @@
       <c r="Z221" s="39"/>
       <c r="AA221" s="39"/>
       <c r="AB221" s="39"/>
-      <c r="AC221" s="118"/>
+      <c r="AC221" s="39"/>
       <c r="AD221" s="40"/>
       <c r="AE221" s="2">
-        <f>IF(SUM(Q221:AD221)&gt;0,SUM(Q221:AD221),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF221" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
@@ -18222,14 +18193,14 @@
       <c r="Z222" s="39"/>
       <c r="AA222" s="39"/>
       <c r="AB222" s="39"/>
-      <c r="AC222" s="118"/>
+      <c r="AC222" s="39"/>
       <c r="AD222" s="40"/>
       <c r="AE222" s="2">
-        <f>IF(SUM(Q222:AD222)&gt;0,SUM(Q222:AD222),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF222" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
@@ -18282,14 +18253,14 @@
       <c r="Z223" s="39"/>
       <c r="AA223" s="39"/>
       <c r="AB223" s="39"/>
-      <c r="AC223" s="118"/>
+      <c r="AC223" s="39"/>
       <c r="AD223" s="40"/>
       <c r="AE223" s="2">
-        <f>IF(SUM(Q223:AD223)&gt;0,SUM(Q223:AD223),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF223" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
@@ -18342,14 +18313,14 @@
       <c r="Z224" s="39"/>
       <c r="AA224" s="39"/>
       <c r="AB224" s="39"/>
-      <c r="AC224" s="118"/>
+      <c r="AC224" s="39"/>
       <c r="AD224" s="40"/>
       <c r="AE224" s="2">
-        <f>IF(SUM(Q224:AD224)&gt;0,SUM(Q224:AD224),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF224" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
@@ -18402,14 +18373,14 @@
       <c r="Z225" s="39"/>
       <c r="AA225" s="39"/>
       <c r="AB225" s="39"/>
-      <c r="AC225" s="118"/>
+      <c r="AC225" s="39"/>
       <c r="AD225" s="40"/>
       <c r="AE225" s="2">
-        <f>IF(SUM(Q225:AD225)&gt;0,SUM(Q225:AD225),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF225" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
@@ -18462,14 +18433,14 @@
       <c r="Z226" s="39"/>
       <c r="AA226" s="39"/>
       <c r="AB226" s="39"/>
-      <c r="AC226" s="118"/>
+      <c r="AC226" s="39"/>
       <c r="AD226" s="40"/>
       <c r="AE226" s="2">
-        <f>IF(SUM(Q226:AD226)&gt;0,SUM(Q226:AD226),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF226" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
@@ -18528,14 +18499,14 @@
       <c r="Z227" s="39"/>
       <c r="AA227" s="39"/>
       <c r="AB227" s="39"/>
-      <c r="AC227" s="118"/>
+      <c r="AC227" s="39"/>
       <c r="AD227" s="40"/>
       <c r="AE227" s="2">
-        <f>IF(SUM(Q227:AD227)&gt;0,SUM(Q227:AD227),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF227" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -18594,14 +18565,14 @@
       <c r="Z228" s="39"/>
       <c r="AA228" s="39"/>
       <c r="AB228" s="39"/>
-      <c r="AC228" s="118"/>
+      <c r="AC228" s="39"/>
       <c r="AD228" s="40"/>
       <c r="AE228" s="2">
-        <f>IF(SUM(Q228:AD228)&gt;0,SUM(Q228:AD228),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF228" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -18660,14 +18631,14 @@
       <c r="Z229" s="39"/>
       <c r="AA229" s="39"/>
       <c r="AB229" s="39"/>
-      <c r="AC229" s="118"/>
+      <c r="AC229" s="39"/>
       <c r="AD229" s="40"/>
       <c r="AE229" s="2">
-        <f>IF(SUM(Q229:AD229)&gt;0,SUM(Q229:AD229),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF229" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -18726,14 +18697,14 @@
       <c r="Z230" s="39"/>
       <c r="AA230" s="39"/>
       <c r="AB230" s="39"/>
-      <c r="AC230" s="118"/>
+      <c r="AC230" s="39"/>
       <c r="AD230" s="40"/>
       <c r="AE230" s="2">
-        <f>IF(SUM(Q230:AD230)&gt;0,SUM(Q230:AD230),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF230" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
     </row>
@@ -18792,14 +18763,14 @@
       <c r="Z231" s="39"/>
       <c r="AA231" s="39"/>
       <c r="AB231" s="39"/>
-      <c r="AC231" s="118"/>
+      <c r="AC231" s="39"/>
       <c r="AD231" s="40"/>
       <c r="AE231" s="2">
-        <f>IF(SUM(Q231:AD231)&gt;0,SUM(Q231:AD231),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF231" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
     </row>
@@ -18854,14 +18825,14 @@
       <c r="Z232" s="42"/>
       <c r="AA232" s="42"/>
       <c r="AB232" s="42"/>
-      <c r="AC232" s="119"/>
+      <c r="AC232" s="42"/>
       <c r="AD232" s="47"/>
       <c r="AE232" s="2">
-        <f>IF(SUM(Q232:AD232)&gt;0,SUM(Q232:AD232),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF232" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
     </row>
@@ -18920,14 +18891,14 @@
       <c r="Z233" s="39"/>
       <c r="AA233" s="39"/>
       <c r="AB233" s="39"/>
-      <c r="AC233" s="118"/>
+      <c r="AC233" s="39"/>
       <c r="AD233" s="40"/>
       <c r="AE233" s="2">
-        <f>IF(SUM(Q233:AD233)&gt;0,SUM(Q233:AD233),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF233" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
     </row>
@@ -18986,14 +18957,14 @@
       <c r="Z234" s="39"/>
       <c r="AA234" s="39"/>
       <c r="AB234" s="39"/>
-      <c r="AC234" s="118"/>
+      <c r="AC234" s="39"/>
       <c r="AD234" s="40"/>
       <c r="AE234" s="2">
-        <f>IF(SUM(Q234:AD234)&gt;0,SUM(Q234:AD234),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF234" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
     </row>
@@ -19052,14 +19023,14 @@
       <c r="Z235" s="39"/>
       <c r="AA235" s="39"/>
       <c r="AB235" s="39"/>
-      <c r="AC235" s="118"/>
+      <c r="AC235" s="39"/>
       <c r="AD235" s="40"/>
       <c r="AE235" s="2">
-        <f>IF(SUM(Q235:AD235)&gt;0,SUM(Q235:AD235),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF235" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
     </row>
@@ -19118,14 +19089,14 @@
       <c r="Z236" s="39"/>
       <c r="AA236" s="39"/>
       <c r="AB236" s="39"/>
-      <c r="AC236" s="118"/>
+      <c r="AC236" s="39"/>
       <c r="AD236" s="40"/>
       <c r="AE236" s="2">
-        <f>IF(SUM(Q236:AD236)&gt;0,SUM(Q236:AD236),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF236" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
     </row>
@@ -19184,14 +19155,14 @@
       <c r="Z237" s="39"/>
       <c r="AA237" s="39"/>
       <c r="AB237" s="39"/>
-      <c r="AC237" s="118"/>
+      <c r="AC237" s="39"/>
       <c r="AD237" s="40"/>
       <c r="AE237" s="2">
-        <f>IF(SUM(Q237:AD237)&gt;0,SUM(Q237:AD237),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF237" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
     </row>
@@ -19246,14 +19217,14 @@
       <c r="Z238" s="42"/>
       <c r="AA238" s="42"/>
       <c r="AB238" s="42"/>
-      <c r="AC238" s="119"/>
+      <c r="AC238" s="42"/>
       <c r="AD238" s="47"/>
       <c r="AE238" s="2">
-        <f>IF(SUM(Q238:AD238)&gt;0,SUM(Q238:AD238),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF238" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
     </row>
@@ -19308,14 +19279,14 @@
       <c r="Z239" s="42"/>
       <c r="AA239" s="42"/>
       <c r="AB239" s="42"/>
-      <c r="AC239" s="119"/>
+      <c r="AC239" s="42"/>
       <c r="AD239" s="47"/>
       <c r="AE239" s="2">
-        <f>IF(SUM(Q239:AD239)&gt;0,SUM(Q239:AD239),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF239" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
@@ -19370,14 +19341,14 @@
       <c r="Z240" s="42"/>
       <c r="AA240" s="42"/>
       <c r="AB240" s="42"/>
-      <c r="AC240" s="119"/>
+      <c r="AC240" s="42"/>
       <c r="AD240" s="47"/>
       <c r="AE240" s="2">
-        <f>IF(SUM(Q240:AD240)&gt;0,SUM(Q240:AD240),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF240" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
     </row>
@@ -19432,14 +19403,14 @@
       <c r="Z241" s="42"/>
       <c r="AA241" s="42"/>
       <c r="AB241" s="42"/>
-      <c r="AC241" s="119"/>
+      <c r="AC241" s="42"/>
       <c r="AD241" s="47"/>
       <c r="AE241" s="2">
-        <f>IF(SUM(Q241:AD241)&gt;0,SUM(Q241:AD241),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF241" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
     </row>
@@ -19498,14 +19469,14 @@
       <c r="Z242" s="39"/>
       <c r="AA242" s="39"/>
       <c r="AB242" s="39"/>
-      <c r="AC242" s="118"/>
+      <c r="AC242" s="39"/>
       <c r="AD242" s="40"/>
       <c r="AE242" s="2">
-        <f>IF(SUM(Q242:AD242)&gt;0,SUM(Q242:AD242),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF242" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
     </row>
@@ -19564,14 +19535,14 @@
       <c r="Z243" s="39"/>
       <c r="AA243" s="39"/>
       <c r="AB243" s="39"/>
-      <c r="AC243" s="118"/>
+      <c r="AC243" s="39"/>
       <c r="AD243" s="40"/>
       <c r="AE243" s="2">
-        <f>IF(SUM(Q243:AD243)&gt;0,SUM(Q243:AD243),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF243" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
     </row>
@@ -19630,14 +19601,14 @@
       <c r="Z244" s="39"/>
       <c r="AA244" s="39"/>
       <c r="AB244" s="39"/>
-      <c r="AC244" s="118"/>
+      <c r="AC244" s="39"/>
       <c r="AD244" s="40"/>
       <c r="AE244" s="2">
-        <f>IF(SUM(Q244:AD244)&gt;0,SUM(Q244:AD244),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF244" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
     </row>
@@ -19696,14 +19667,14 @@
       <c r="Z245" s="39"/>
       <c r="AA245" s="39"/>
       <c r="AB245" s="39"/>
-      <c r="AC245" s="118"/>
+      <c r="AC245" s="39"/>
       <c r="AD245" s="40"/>
       <c r="AE245" s="2">
-        <f>IF(SUM(Q245:AD245)&gt;0,SUM(Q245:AD245),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF245" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
@@ -19762,14 +19733,14 @@
       <c r="Z246" s="39"/>
       <c r="AA246" s="39"/>
       <c r="AB246" s="39"/>
-      <c r="AC246" s="118"/>
+      <c r="AC246" s="39"/>
       <c r="AD246" s="40"/>
       <c r="AE246" s="2">
-        <f>IF(SUM(Q246:AD246)&gt;0,SUM(Q246:AD246),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF246" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
     </row>
@@ -19828,14 +19799,14 @@
       <c r="Z247" s="39"/>
       <c r="AA247" s="39"/>
       <c r="AB247" s="39"/>
-      <c r="AC247" s="118"/>
+      <c r="AC247" s="39"/>
       <c r="AD247" s="40"/>
       <c r="AE247" s="2">
-        <f>IF(SUM(Q247:AD247)&gt;0,SUM(Q247:AD247),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF247" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
     </row>
@@ -19890,14 +19861,14 @@
       <c r="Z248" s="42"/>
       <c r="AA248" s="42"/>
       <c r="AB248" s="42"/>
-      <c r="AC248" s="119"/>
+      <c r="AC248" s="42"/>
       <c r="AD248" s="47"/>
       <c r="AE248" s="2">
-        <f>IF(SUM(Q248:AD248)&gt;0,SUM(Q248:AD248),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF248" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
     </row>
@@ -19956,14 +19927,14 @@
       <c r="Z249" s="39"/>
       <c r="AA249" s="39"/>
       <c r="AB249" s="39"/>
-      <c r="AC249" s="118"/>
+      <c r="AC249" s="39"/>
       <c r="AD249" s="40"/>
       <c r="AE249" s="2">
-        <f>IF(SUM(Q249:AD249)&gt;0,SUM(Q249:AD249),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF249" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
     </row>
@@ -20022,14 +19993,14 @@
       <c r="Z250" s="39"/>
       <c r="AA250" s="39"/>
       <c r="AB250" s="39"/>
-      <c r="AC250" s="118"/>
+      <c r="AC250" s="39"/>
       <c r="AD250" s="40"/>
       <c r="AE250" s="2">
-        <f>IF(SUM(Q250:AD250)&gt;0,SUM(Q250:AD250),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF250" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
     </row>
@@ -20088,14 +20059,14 @@
       <c r="Z251" s="39"/>
       <c r="AA251" s="39"/>
       <c r="AB251" s="39"/>
-      <c r="AC251" s="118"/>
+      <c r="AC251" s="39"/>
       <c r="AD251" s="40"/>
       <c r="AE251" s="2">
-        <f>IF(SUM(Q251:AD251)&gt;0,SUM(Q251:AD251),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF251" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
     </row>
@@ -20150,14 +20121,14 @@
       <c r="Z252" s="42"/>
       <c r="AA252" s="42"/>
       <c r="AB252" s="42"/>
-      <c r="AC252" s="119"/>
+      <c r="AC252" s="42"/>
       <c r="AD252" s="47"/>
       <c r="AE252" s="2">
-        <f>IF(SUM(Q252:AD252)&gt;0,SUM(Q252:AD252),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF252" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
     </row>
@@ -20212,14 +20183,14 @@
       <c r="Z253" s="42"/>
       <c r="AA253" s="42"/>
       <c r="AB253" s="42"/>
-      <c r="AC253" s="119"/>
+      <c r="AC253" s="42"/>
       <c r="AD253" s="47"/>
       <c r="AE253" s="2">
-        <f>IF(SUM(Q253:AD253)&gt;0,SUM(Q253:AD253),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF253" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
     </row>
@@ -20274,14 +20245,14 @@
       <c r="Z254" s="42"/>
       <c r="AA254" s="42"/>
       <c r="AB254" s="42"/>
-      <c r="AC254" s="119"/>
+      <c r="AC254" s="42"/>
       <c r="AD254" s="47"/>
       <c r="AE254" s="2">
-        <f>IF(SUM(Q254:AD254)&gt;0,SUM(Q254:AD254),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF254" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
     </row>
@@ -20336,14 +20307,14 @@
       <c r="Z255" s="42"/>
       <c r="AA255" s="42"/>
       <c r="AB255" s="42"/>
-      <c r="AC255" s="119"/>
+      <c r="AC255" s="42"/>
       <c r="AD255" s="47"/>
       <c r="AE255" s="2">
-        <f>IF(SUM(Q255:AD255)&gt;0,SUM(Q255:AD255),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF255" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
     </row>
@@ -20402,14 +20373,14 @@
       <c r="Z256" s="39"/>
       <c r="AA256" s="39"/>
       <c r="AB256" s="39"/>
-      <c r="AC256" s="118"/>
+      <c r="AC256" s="39"/>
       <c r="AD256" s="40"/>
       <c r="AE256" s="2">
-        <f>IF(SUM(Q256:AD256)&gt;0,SUM(Q256:AD256),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF256" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
     </row>
@@ -20464,14 +20435,14 @@
       <c r="Z257" s="42"/>
       <c r="AA257" s="42"/>
       <c r="AB257" s="42"/>
-      <c r="AC257" s="119"/>
+      <c r="AC257" s="42"/>
       <c r="AD257" s="47"/>
       <c r="AE257" s="2">
-        <f>IF(SUM(Q257:AD257)&gt;0,SUM(Q257:AD257),"")</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="AF257" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
     </row>
@@ -20526,14 +20497,14 @@
       <c r="Z258" s="42"/>
       <c r="AA258" s="42"/>
       <c r="AB258" s="42"/>
-      <c r="AC258" s="119"/>
+      <c r="AC258" s="42"/>
       <c r="AD258" s="47"/>
       <c r="AE258" s="2">
-        <f>IF(SUM(Q258:AD258)&gt;0,SUM(Q258:AD258),"")</f>
+        <f t="shared" ref="AE258:AE321" si="8">IF(SUM(Q258:AD258)&gt;0,SUM(Q258:AD258),"")</f>
         <v>1</v>
       </c>
       <c r="AF258" s="77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
     </row>
@@ -20592,14 +20563,14 @@
       <c r="Z259" s="39"/>
       <c r="AA259" s="39"/>
       <c r="AB259" s="39"/>
-      <c r="AC259" s="118"/>
+      <c r="AC259" s="39"/>
       <c r="AD259" s="40"/>
       <c r="AE259" s="2">
-        <f>IF(SUM(Q259:AD259)&gt;0,SUM(Q259:AD259),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF259" s="77">
-        <f t="shared" ref="AF259:AF322" si="4">IF(SUM(Q259:AD259)&lt;1,"",Q259*1+R259*2+S259*3+T259*4+U259*5+V259*6+W259*7+X259*8+Y259*9+Z259*10+AA259*11+AB259*12+AC259*13+AD259*14)</f>
+        <f t="shared" ref="AF259:AF322" si="9">IF(SUM(Q259:AD259)&lt;1,"",Q259*1+R259*2+S259*3+T259*4+U259*5+V259*6+W259*7+X259*8+Y259*9+Z259*10+AA259*11+AB259*12+AC259*13+AD259*14)</f>
         <v>2</v>
       </c>
     </row>
@@ -20658,14 +20629,14 @@
       <c r="Z260" s="39"/>
       <c r="AA260" s="39"/>
       <c r="AB260" s="39"/>
-      <c r="AC260" s="118"/>
+      <c r="AC260" s="39"/>
       <c r="AD260" s="40"/>
       <c r="AE260" s="2">
-        <f>IF(SUM(Q260:AD260)&gt;0,SUM(Q260:AD260),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF260" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
     </row>
@@ -20724,14 +20695,14 @@
       <c r="Z261" s="39"/>
       <c r="AA261" s="39"/>
       <c r="AB261" s="39"/>
-      <c r="AC261" s="118"/>
+      <c r="AC261" s="39"/>
       <c r="AD261" s="40"/>
       <c r="AE261" s="2">
-        <f>IF(SUM(Q261:AD261)&gt;0,SUM(Q261:AD261),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF261" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
     </row>
@@ -20790,14 +20761,14 @@
       <c r="Z262" s="39"/>
       <c r="AA262" s="39"/>
       <c r="AB262" s="39"/>
-      <c r="AC262" s="118"/>
+      <c r="AC262" s="39"/>
       <c r="AD262" s="40"/>
       <c r="AE262" s="2">
-        <f>IF(SUM(Q262:AD262)&gt;0,SUM(Q262:AD262),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF262" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
     </row>
@@ -20856,14 +20827,14 @@
       <c r="Z263" s="39"/>
       <c r="AA263" s="39"/>
       <c r="AB263" s="39"/>
-      <c r="AC263" s="118"/>
+      <c r="AC263" s="39"/>
       <c r="AD263" s="40"/>
       <c r="AE263" s="2">
-        <f>IF(SUM(Q263:AD263)&gt;0,SUM(Q263:AD263),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF263" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
     </row>
@@ -20918,14 +20889,14 @@
       <c r="Z264" s="39"/>
       <c r="AA264" s="39"/>
       <c r="AB264" s="39"/>
-      <c r="AC264" s="118"/>
+      <c r="AC264" s="39"/>
       <c r="AD264" s="40"/>
       <c r="AE264" s="2">
-        <f>IF(SUM(Q264:AD264)&gt;0,SUM(Q264:AD264),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF264" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
     </row>
@@ -20980,14 +20951,14 @@
       <c r="Z265" s="42"/>
       <c r="AA265" s="42"/>
       <c r="AB265" s="42"/>
-      <c r="AC265" s="119"/>
+      <c r="AC265" s="42"/>
       <c r="AD265" s="47"/>
       <c r="AE265" s="2">
-        <f>IF(SUM(Q265:AD265)&gt;0,SUM(Q265:AD265),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF265" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
     </row>
@@ -21042,14 +21013,14 @@
       <c r="Z266" s="42"/>
       <c r="AA266" s="42"/>
       <c r="AB266" s="42"/>
-      <c r="AC266" s="119"/>
+      <c r="AC266" s="42"/>
       <c r="AD266" s="47"/>
       <c r="AE266" s="2">
-        <f>IF(SUM(Q266:AD266)&gt;0,SUM(Q266:AD266),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF266" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
     </row>
@@ -21106,14 +21077,14 @@
       <c r="Z267" s="42"/>
       <c r="AA267" s="42"/>
       <c r="AB267" s="42"/>
-      <c r="AC267" s="119"/>
+      <c r="AC267" s="42"/>
       <c r="AD267" s="47"/>
       <c r="AE267" s="2">
-        <f>IF(SUM(Q267:AD267)&gt;0,SUM(Q267:AD267),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF267" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
     </row>
@@ -21168,14 +21139,14 @@
       <c r="Z268" s="42"/>
       <c r="AA268" s="42"/>
       <c r="AB268" s="42"/>
-      <c r="AC268" s="119"/>
+      <c r="AC268" s="42"/>
       <c r="AD268" s="47"/>
       <c r="AE268" s="2">
-        <f>IF(SUM(Q268:AD268)&gt;0,SUM(Q268:AD268),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF268" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
     </row>
@@ -21230,14 +21201,14 @@
       <c r="Z269" s="42"/>
       <c r="AA269" s="42"/>
       <c r="AB269" s="42"/>
-      <c r="AC269" s="119"/>
+      <c r="AC269" s="42"/>
       <c r="AD269" s="47"/>
       <c r="AE269" s="2">
-        <f>IF(SUM(Q269:AD269)&gt;0,SUM(Q269:AD269),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF269" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
     </row>
@@ -21296,14 +21267,14 @@
       <c r="Z270" s="39"/>
       <c r="AA270" s="39"/>
       <c r="AB270" s="39"/>
-      <c r="AC270" s="118"/>
+      <c r="AC270" s="39"/>
       <c r="AD270" s="40"/>
       <c r="AE270" s="2">
-        <f>IF(SUM(Q270:AD270)&gt;0,SUM(Q270:AD270),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF270" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
     </row>
@@ -21362,14 +21333,14 @@
       <c r="Z271" s="39"/>
       <c r="AA271" s="39"/>
       <c r="AB271" s="39"/>
-      <c r="AC271" s="118"/>
+      <c r="AC271" s="39"/>
       <c r="AD271" s="40"/>
       <c r="AE271" s="2">
-        <f>IF(SUM(Q271:AD271)&gt;0,SUM(Q271:AD271),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF271" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
     </row>
@@ -21428,14 +21399,14 @@
       <c r="Z272" s="39"/>
       <c r="AA272" s="39"/>
       <c r="AB272" s="39"/>
-      <c r="AC272" s="118"/>
+      <c r="AC272" s="39"/>
       <c r="AD272" s="40"/>
       <c r="AE272" s="2">
-        <f>IF(SUM(Q272:AD272)&gt;0,SUM(Q272:AD272),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF272" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
@@ -21494,14 +21465,14 @@
       <c r="Z273" s="39"/>
       <c r="AA273" s="39"/>
       <c r="AB273" s="39"/>
-      <c r="AC273" s="118"/>
+      <c r="AC273" s="39"/>
       <c r="AD273" s="40"/>
       <c r="AE273" s="2">
-        <f>IF(SUM(Q273:AD273)&gt;0,SUM(Q273:AD273),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF273" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
     </row>
@@ -21556,14 +21527,14 @@
       <c r="Z274" s="42"/>
       <c r="AA274" s="42"/>
       <c r="AB274" s="42"/>
-      <c r="AC274" s="119"/>
+      <c r="AC274" s="42"/>
       <c r="AD274" s="47"/>
       <c r="AE274" s="2">
-        <f>IF(SUM(Q274:AD274)&gt;0,SUM(Q274:AD274),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF274" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
     </row>
@@ -21618,14 +21589,14 @@
       <c r="Z275" s="42"/>
       <c r="AA275" s="42"/>
       <c r="AB275" s="42"/>
-      <c r="AC275" s="119"/>
+      <c r="AC275" s="42"/>
       <c r="AD275" s="47"/>
       <c r="AE275" s="2">
-        <f>IF(SUM(Q275:AD275)&gt;0,SUM(Q275:AD275),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF275" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
     </row>
@@ -21682,14 +21653,14 @@
       <c r="Z276" s="42"/>
       <c r="AA276" s="42"/>
       <c r="AB276" s="42"/>
-      <c r="AC276" s="119"/>
+      <c r="AC276" s="42"/>
       <c r="AD276" s="47"/>
       <c r="AE276" s="2">
-        <f>IF(SUM(Q276:AD276)&gt;0,SUM(Q276:AD276),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF276" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
     </row>
@@ -21746,14 +21717,14 @@
       <c r="Z277" s="42"/>
       <c r="AA277" s="42"/>
       <c r="AB277" s="42"/>
-      <c r="AC277" s="119"/>
+      <c r="AC277" s="42"/>
       <c r="AD277" s="47"/>
       <c r="AE277" s="2">
-        <f>IF(SUM(Q277:AD277)&gt;0,SUM(Q277:AD277),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF277" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
     </row>
@@ -21804,14 +21775,14 @@
       <c r="Z278" s="39"/>
       <c r="AA278" s="39"/>
       <c r="AB278" s="39"/>
-      <c r="AC278" s="118"/>
+      <c r="AC278" s="39"/>
       <c r="AD278" s="40"/>
       <c r="AE278" s="2">
-        <f>IF(SUM(Q278:AD278)&gt;0,SUM(Q278:AD278),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF278" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
@@ -21862,14 +21833,14 @@
       <c r="Z279" s="39"/>
       <c r="AA279" s="39"/>
       <c r="AB279" s="39"/>
-      <c r="AC279" s="118"/>
+      <c r="AC279" s="39"/>
       <c r="AD279" s="40"/>
       <c r="AE279" s="2">
-        <f>IF(SUM(Q279:AD279)&gt;0,SUM(Q279:AD279),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF279" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
@@ -21916,14 +21887,14 @@
       <c r="Z280" s="42"/>
       <c r="AA280" s="42"/>
       <c r="AB280" s="42"/>
-      <c r="AC280" s="119"/>
+      <c r="AC280" s="42"/>
       <c r="AD280" s="47"/>
       <c r="AE280" s="2">
-        <f>IF(SUM(Q280:AD280)&gt;0,SUM(Q280:AD280),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF280" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
@@ -21970,14 +21941,14 @@
       <c r="Z281" s="42"/>
       <c r="AA281" s="42"/>
       <c r="AB281" s="42"/>
-      <c r="AC281" s="119"/>
+      <c r="AC281" s="42"/>
       <c r="AD281" s="47"/>
       <c r="AE281" s="2">
-        <f>IF(SUM(Q281:AD281)&gt;0,SUM(Q281:AD281),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF281" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
@@ -22024,14 +21995,14 @@
       <c r="Z282" s="42"/>
       <c r="AA282" s="42"/>
       <c r="AB282" s="42"/>
-      <c r="AC282" s="119"/>
+      <c r="AC282" s="42"/>
       <c r="AD282" s="47"/>
       <c r="AE282" s="2">
-        <f>IF(SUM(Q282:AD282)&gt;0,SUM(Q282:AD282),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF282" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
@@ -22078,14 +22049,14 @@
       <c r="Z283" s="42"/>
       <c r="AA283" s="42"/>
       <c r="AB283" s="42"/>
-      <c r="AC283" s="119"/>
+      <c r="AC283" s="42"/>
       <c r="AD283" s="47"/>
       <c r="AE283" s="2">
-        <f>IF(SUM(Q283:AD283)&gt;0,SUM(Q283:AD283),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF283" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
@@ -22136,14 +22107,14 @@
       <c r="Z284" s="39"/>
       <c r="AA284" s="39"/>
       <c r="AB284" s="39"/>
-      <c r="AC284" s="118"/>
+      <c r="AC284" s="39"/>
       <c r="AD284" s="40"/>
       <c r="AE284" s="2">
-        <f>IF(SUM(Q284:AD284)&gt;0,SUM(Q284:AD284),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF284" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
     </row>
@@ -22194,14 +22165,14 @@
       <c r="Z285" s="39"/>
       <c r="AA285" s="39"/>
       <c r="AB285" s="39"/>
-      <c r="AC285" s="118"/>
+      <c r="AC285" s="39"/>
       <c r="AD285" s="40"/>
       <c r="AE285" s="2">
-        <f>IF(SUM(Q285:AD285)&gt;0,SUM(Q285:AD285),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF285" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
     </row>
@@ -22252,14 +22223,14 @@
       <c r="Z286" s="39"/>
       <c r="AA286" s="39"/>
       <c r="AB286" s="39"/>
-      <c r="AC286" s="118"/>
+      <c r="AC286" s="39"/>
       <c r="AD286" s="40"/>
       <c r="AE286" s="2">
-        <f>IF(SUM(Q286:AD286)&gt;0,SUM(Q286:AD286),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF286" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
     </row>
@@ -22310,14 +22281,14 @@
       <c r="Z287" s="39"/>
       <c r="AA287" s="39"/>
       <c r="AB287" s="39"/>
-      <c r="AC287" s="118"/>
+      <c r="AC287" s="39"/>
       <c r="AD287" s="40"/>
       <c r="AE287" s="2">
-        <f>IF(SUM(Q287:AD287)&gt;0,SUM(Q287:AD287),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF287" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
     </row>
@@ -22364,14 +22335,14 @@
       <c r="Z288" s="42"/>
       <c r="AA288" s="42"/>
       <c r="AB288" s="42"/>
-      <c r="AC288" s="119"/>
+      <c r="AC288" s="42"/>
       <c r="AD288" s="47"/>
       <c r="AE288" s="2">
-        <f>IF(SUM(Q288:AD288)&gt;0,SUM(Q288:AD288),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF288" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
     </row>
@@ -22420,14 +22391,14 @@
       <c r="Z289" s="42"/>
       <c r="AA289" s="42"/>
       <c r="AB289" s="42"/>
-      <c r="AC289" s="119"/>
+      <c r="AC289" s="42"/>
       <c r="AD289" s="47"/>
       <c r="AE289" s="2">
-        <f>IF(SUM(Q289:AD289)&gt;0,SUM(Q289:AD289),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF289" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
     </row>
@@ -22478,14 +22449,14 @@
       <c r="Z290" s="39"/>
       <c r="AA290" s="39"/>
       <c r="AB290" s="39"/>
-      <c r="AC290" s="118"/>
+      <c r="AC290" s="39"/>
       <c r="AD290" s="40"/>
       <c r="AE290" s="2">
-        <f>IF(SUM(Q290:AD290)&gt;0,SUM(Q290:AD290),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF290" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>8</v>
       </c>
     </row>
@@ -22536,14 +22507,14 @@
       <c r="Z291" s="39"/>
       <c r="AA291" s="39"/>
       <c r="AB291" s="39"/>
-      <c r="AC291" s="118"/>
+      <c r="AC291" s="39"/>
       <c r="AD291" s="40"/>
       <c r="AE291" s="2">
-        <f>IF(SUM(Q291:AD291)&gt;0,SUM(Q291:AD291),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF291" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>8</v>
       </c>
     </row>
@@ -22594,14 +22565,14 @@
       <c r="Z292" s="39"/>
       <c r="AA292" s="39"/>
       <c r="AB292" s="39"/>
-      <c r="AC292" s="118"/>
+      <c r="AC292" s="39"/>
       <c r="AD292" s="40"/>
       <c r="AE292" s="2">
-        <f>IF(SUM(Q292:AD292)&gt;0,SUM(Q292:AD292),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF292" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>8</v>
       </c>
     </row>
@@ -22660,14 +22631,14 @@
       <c r="Z293" s="39"/>
       <c r="AA293" s="39"/>
       <c r="AB293" s="39"/>
-      <c r="AC293" s="118"/>
+      <c r="AC293" s="39"/>
       <c r="AD293" s="40"/>
       <c r="AE293" s="2">
-        <f>IF(SUM(Q293:AD293)&gt;0,SUM(Q293:AD293),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF293" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>8</v>
       </c>
     </row>
@@ -22714,14 +22685,14 @@
       <c r="Z294" s="42"/>
       <c r="AA294" s="42"/>
       <c r="AB294" s="42"/>
-      <c r="AC294" s="119"/>
+      <c r="AC294" s="42"/>
       <c r="AD294" s="47"/>
       <c r="AE294" s="2">
-        <f>IF(SUM(Q294:AD294)&gt;0,SUM(Q294:AD294),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF294" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>8</v>
       </c>
     </row>
@@ -22776,14 +22747,14 @@
       <c r="Z295" s="42"/>
       <c r="AA295" s="42"/>
       <c r="AB295" s="42"/>
-      <c r="AC295" s="119"/>
+      <c r="AC295" s="42"/>
       <c r="AD295" s="47"/>
       <c r="AE295" s="2">
-        <f>IF(SUM(Q295:AD295)&gt;0,SUM(Q295:AD295),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF295" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>8</v>
       </c>
     </row>
@@ -22840,14 +22811,14 @@
       <c r="Z296" s="42"/>
       <c r="AA296" s="42"/>
       <c r="AB296" s="42"/>
-      <c r="AC296" s="119"/>
+      <c r="AC296" s="42"/>
       <c r="AD296" s="47"/>
       <c r="AE296" s="2">
-        <f>IF(SUM(Q296:AD296)&gt;0,SUM(Q296:AD296),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF296" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>8</v>
       </c>
     </row>
@@ -22904,14 +22875,14 @@
       <c r="Z297" s="42"/>
       <c r="AA297" s="42"/>
       <c r="AB297" s="42"/>
-      <c r="AC297" s="119"/>
+      <c r="AC297" s="42"/>
       <c r="AD297" s="47"/>
       <c r="AE297" s="2">
-        <f>IF(SUM(Q297:AD297)&gt;0,SUM(Q297:AD297),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF297" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>8</v>
       </c>
     </row>
@@ -22964,14 +22935,14 @@
       <c r="Z298" s="42"/>
       <c r="AA298" s="42"/>
       <c r="AB298" s="42"/>
-      <c r="AC298" s="119"/>
+      <c r="AC298" s="42"/>
       <c r="AD298" s="47"/>
       <c r="AE298" s="2">
-        <f>IF(SUM(Q298:AD298)&gt;0,SUM(Q298:AD298),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF298" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>8</v>
       </c>
     </row>
@@ -23009,14 +22980,14 @@
       <c r="Z299" s="39"/>
       <c r="AA299" s="39"/>
       <c r="AB299" s="39"/>
-      <c r="AC299" s="118"/>
+      <c r="AC299" s="39"/>
       <c r="AD299" s="40"/>
       <c r="AE299" s="2" t="str">
-        <f>IF(SUM(Q299:AD299)&gt;0,SUM(Q299:AD299),"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AF299" s="77" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -23077,14 +23048,14 @@
       <c r="Z300" s="39"/>
       <c r="AA300" s="39"/>
       <c r="AB300" s="39"/>
-      <c r="AC300" s="118"/>
+      <c r="AC300" s="39"/>
       <c r="AD300" s="40"/>
       <c r="AE300" s="2">
-        <f>IF(SUM(Q300:AD300)&gt;0,SUM(Q300:AD300),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF300" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
@@ -23145,14 +23116,14 @@
       <c r="Z301" s="45"/>
       <c r="AA301" s="45"/>
       <c r="AB301" s="45"/>
-      <c r="AC301" s="120"/>
+      <c r="AC301" s="45"/>
       <c r="AD301" s="51"/>
       <c r="AE301" s="2">
-        <f>IF(SUM(Q301:AD301)&gt;0,SUM(Q301:AD301),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF301" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
@@ -23199,14 +23170,14 @@
       <c r="Z302" s="39"/>
       <c r="AA302" s="39"/>
       <c r="AB302" s="39"/>
-      <c r="AC302" s="118"/>
+      <c r="AC302" s="39"/>
       <c r="AD302" s="40"/>
       <c r="AE302" s="2">
-        <f>IF(SUM(Q302:AD302)&gt;0,SUM(Q302:AD302),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF302" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
     </row>
@@ -23251,14 +23222,14 @@
       <c r="Z303" s="39"/>
       <c r="AA303" s="39"/>
       <c r="AB303" s="39"/>
-      <c r="AC303" s="118"/>
+      <c r="AC303" s="39"/>
       <c r="AD303" s="40"/>
       <c r="AE303" s="2">
-        <f>IF(SUM(Q303:AD303)&gt;0,SUM(Q303:AD303),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF303" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
     </row>
@@ -23307,14 +23278,14 @@
       <c r="AB304" s="41">
         <v>1</v>
       </c>
-      <c r="AC304" s="118"/>
+      <c r="AC304" s="39"/>
       <c r="AD304" s="40"/>
       <c r="AE304" s="2">
-        <f>IF(SUM(Q304:AD304)&gt;0,SUM(Q304:AD304),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF304" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
     </row>
@@ -23372,14 +23343,14 @@
       <c r="Z305" s="9"/>
       <c r="AA305" s="9"/>
       <c r="AB305" s="9"/>
-      <c r="AC305" s="116"/>
+      <c r="AC305" s="115"/>
       <c r="AD305" s="7"/>
       <c r="AE305" s="2">
-        <f>IF(SUM(Q305:AD305)&gt;0,SUM(Q305:AD305),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF305" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
     </row>
@@ -23415,14 +23386,14 @@
       <c r="Z306" s="9"/>
       <c r="AA306" s="9"/>
       <c r="AB306" s="9"/>
-      <c r="AC306" s="116"/>
+      <c r="AC306" s="115"/>
       <c r="AD306" s="7"/>
       <c r="AE306" s="2" t="str">
-        <f>IF(SUM(Q306:AD306)&gt;0,SUM(Q306:AD306),"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AF306" s="77" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -23480,14 +23451,14 @@
       <c r="Z307" s="9"/>
       <c r="AA307" s="9"/>
       <c r="AB307" s="9"/>
-      <c r="AC307" s="116"/>
+      <c r="AC307" s="115"/>
       <c r="AD307" s="7"/>
       <c r="AE307" s="2">
-        <f>IF(SUM(Q307:AD307)&gt;0,SUM(Q307:AD307),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF307" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
     </row>
@@ -23523,14 +23494,14 @@
       <c r="Z308" s="9"/>
       <c r="AA308" s="9"/>
       <c r="AB308" s="9"/>
-      <c r="AC308" s="116"/>
+      <c r="AC308" s="115"/>
       <c r="AD308" s="7"/>
       <c r="AE308" s="2" t="str">
-        <f>IF(SUM(Q308:AD308)&gt;0,SUM(Q308:AD308),"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AF308" s="77" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -23566,14 +23537,14 @@
       <c r="Z309" s="9"/>
       <c r="AA309" s="9"/>
       <c r="AB309" s="9"/>
-      <c r="AC309" s="116"/>
+      <c r="AC309" s="115"/>
       <c r="AD309" s="7"/>
       <c r="AE309" s="2" t="str">
-        <f>IF(SUM(Q309:AD309)&gt;0,SUM(Q309:AD309),"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AF309" s="77" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -23629,14 +23600,14 @@
       <c r="Z310" s="9"/>
       <c r="AA310" s="9"/>
       <c r="AB310" s="9"/>
-      <c r="AC310" s="116"/>
+      <c r="AC310" s="115"/>
       <c r="AD310" s="7"/>
       <c r="AE310" s="2">
-        <f>IF(SUM(Q310:AD310)&gt;0,SUM(Q310:AD310),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF310" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
     </row>
@@ -23694,14 +23665,14 @@
       <c r="Z311" s="9"/>
       <c r="AA311" s="9"/>
       <c r="AB311" s="9"/>
-      <c r="AC311" s="116"/>
+      <c r="AC311" s="115"/>
       <c r="AD311" s="7"/>
       <c r="AE311" s="2">
-        <f>IF(SUM(Q311:AD311)&gt;0,SUM(Q311:AD311),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF311" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
     </row>
@@ -23737,14 +23708,14 @@
       <c r="Z312" s="9"/>
       <c r="AA312" s="9"/>
       <c r="AB312" s="9"/>
-      <c r="AC312" s="116"/>
+      <c r="AC312" s="115"/>
       <c r="AD312" s="7"/>
       <c r="AE312" s="2" t="str">
-        <f>IF(SUM(Q312:AD312)&gt;0,SUM(Q312:AD312),"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AF312" s="77" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -23798,14 +23769,14 @@
       <c r="Z313" s="9"/>
       <c r="AA313" s="9"/>
       <c r="AB313" s="9"/>
-      <c r="AC313" s="116"/>
+      <c r="AC313" s="115"/>
       <c r="AD313" s="7"/>
       <c r="AE313" s="2">
-        <f>IF(SUM(Q313:AD313)&gt;0,SUM(Q313:AD313),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF313" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
     </row>
@@ -23861,14 +23832,14 @@
       <c r="Z314" s="9"/>
       <c r="AA314" s="9"/>
       <c r="AB314" s="9"/>
-      <c r="AC314" s="116"/>
+      <c r="AC314" s="115"/>
       <c r="AD314" s="7"/>
       <c r="AE314" s="2">
-        <f>IF(SUM(Q314:AD314)&gt;0,SUM(Q314:AD314),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF314" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
     </row>
@@ -23922,14 +23893,14 @@
       <c r="Z315" s="9"/>
       <c r="AA315" s="9"/>
       <c r="AB315" s="9"/>
-      <c r="AC315" s="116"/>
+      <c r="AC315" s="115"/>
       <c r="AD315" s="7"/>
       <c r="AE315" s="2">
-        <f>IF(SUM(Q315:AD315)&gt;0,SUM(Q315:AD315),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF315" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
     </row>
@@ -23983,14 +23954,14 @@
       <c r="Z316" s="9"/>
       <c r="AA316" s="9"/>
       <c r="AB316" s="9"/>
-      <c r="AC316" s="116"/>
+      <c r="AC316" s="115"/>
       <c r="AD316" s="7"/>
       <c r="AE316" s="2">
-        <f>IF(SUM(Q316:AD316)&gt;0,SUM(Q316:AD316),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF316" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
     </row>
@@ -24044,14 +24015,14 @@
       <c r="Z317" s="9"/>
       <c r="AA317" s="9"/>
       <c r="AB317" s="9"/>
-      <c r="AC317" s="116"/>
+      <c r="AC317" s="115"/>
       <c r="AD317" s="7"/>
       <c r="AE317" s="2">
-        <f>IF(SUM(Q317:AD317)&gt;0,SUM(Q317:AD317),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF317" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
     </row>
@@ -24105,14 +24076,14 @@
       <c r="Z318" s="9"/>
       <c r="AA318" s="9"/>
       <c r="AB318" s="9"/>
-      <c r="AC318" s="116"/>
+      <c r="AC318" s="115"/>
       <c r="AD318" s="7"/>
       <c r="AE318" s="2">
-        <f>IF(SUM(Q318:AD318)&gt;0,SUM(Q318:AD318),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF318" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
     </row>
@@ -24170,14 +24141,14 @@
       <c r="Z319" s="9"/>
       <c r="AA319" s="9"/>
       <c r="AB319" s="9"/>
-      <c r="AC319" s="116"/>
+      <c r="AC319" s="115"/>
       <c r="AD319" s="7"/>
       <c r="AE319" s="2">
-        <f>IF(SUM(Q319:AD319)&gt;0,SUM(Q319:AD319),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF319" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
@@ -24213,14 +24184,14 @@
       <c r="Z320" s="9"/>
       <c r="AA320" s="9"/>
       <c r="AB320" s="9"/>
-      <c r="AC320" s="116"/>
+      <c r="AC320" s="115"/>
       <c r="AD320" s="7"/>
       <c r="AE320" s="2" t="str">
-        <f>IF(SUM(Q320:AD320)&gt;0,SUM(Q320:AD320),"")</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="AF320" s="77" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24278,14 +24249,14 @@
       <c r="Z321" s="9"/>
       <c r="AA321" s="9"/>
       <c r="AB321" s="9"/>
-      <c r="AC321" s="116"/>
+      <c r="AC321" s="115"/>
       <c r="AD321" s="7"/>
       <c r="AE321" s="2">
-        <f>IF(SUM(Q321:AD321)&gt;0,SUM(Q321:AD321),"")</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AF321" s="77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
     </row>
@@ -24321,14 +24292,14 @@
       <c r="Z322" s="9"/>
       <c r="AA322" s="9"/>
       <c r="AB322" s="9"/>
-      <c r="AC322" s="116"/>
+      <c r="AC322" s="115"/>
       <c r="AD322" s="7"/>
       <c r="AE322" s="2" t="str">
-        <f>IF(SUM(Q322:AD322)&gt;0,SUM(Q322:AD322),"")</f>
+        <f t="shared" ref="AE322:AE385" si="10">IF(SUM(Q322:AD322)&gt;0,SUM(Q322:AD322),"")</f>
         <v/>
       </c>
       <c r="AF322" s="77" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
     </row>
@@ -24384,14 +24355,14 @@
       <c r="Z323" s="9"/>
       <c r="AA323" s="9"/>
       <c r="AB323" s="9"/>
-      <c r="AC323" s="116"/>
+      <c r="AC323" s="115"/>
       <c r="AD323" s="7"/>
       <c r="AE323" s="2">
-        <f>IF(SUM(Q323:AD323)&gt;0,SUM(Q323:AD323),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF323" s="77">
-        <f t="shared" ref="AF323:AF386" si="5">IF(SUM(Q323:AD323)&lt;1,"",Q323*1+R323*2+S323*3+T323*4+U323*5+V323*6+W323*7+X323*8+Y323*9+Z323*10+AA323*11+AB323*12+AC323*13+AD323*14)</f>
+        <f t="shared" ref="AF323:AF386" si="11">IF(SUM(Q323:AD323)&lt;1,"",Q323*1+R323*2+S323*3+T323*4+U323*5+V323*6+W323*7+X323*8+Y323*9+Z323*10+AA323*11+AB323*12+AC323*13+AD323*14)</f>
         <v>1</v>
       </c>
     </row>
@@ -24447,14 +24418,14 @@
       <c r="Z324" s="9"/>
       <c r="AA324" s="9"/>
       <c r="AB324" s="9"/>
-      <c r="AC324" s="116"/>
+      <c r="AC324" s="115"/>
       <c r="AD324" s="7"/>
       <c r="AE324" s="2">
-        <f>IF(SUM(Q324:AD324)&gt;0,SUM(Q324:AD324),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF324" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>9</v>
       </c>
     </row>
@@ -24512,14 +24483,14 @@
       <c r="Z325" s="9"/>
       <c r="AA325" s="9"/>
       <c r="AB325" s="9"/>
-      <c r="AC325" s="116"/>
+      <c r="AC325" s="115"/>
       <c r="AD325" s="7"/>
       <c r="AE325" s="2">
-        <f>IF(SUM(Q325:AD325)&gt;0,SUM(Q325:AD325),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF325" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>8</v>
       </c>
     </row>
@@ -24555,14 +24526,14 @@
       <c r="Z326" s="9"/>
       <c r="AA326" s="9"/>
       <c r="AB326" s="9"/>
-      <c r="AC326" s="116"/>
+      <c r="AC326" s="115"/>
       <c r="AD326" s="7"/>
       <c r="AE326" s="2" t="str">
-        <f>IF(SUM(Q326:AD326)&gt;0,SUM(Q326:AD326),"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AF326" s="77" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -24616,14 +24587,14 @@
       <c r="Z327" s="9"/>
       <c r="AA327" s="9"/>
       <c r="AB327" s="9"/>
-      <c r="AC327" s="116"/>
+      <c r="AC327" s="115"/>
       <c r="AD327" s="7"/>
       <c r="AE327" s="2">
-        <f>IF(SUM(Q327:AD327)&gt;0,SUM(Q327:AD327),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF327" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>8</v>
       </c>
     </row>
@@ -24680,14 +24651,14 @@
       <c r="Z328" s="9"/>
       <c r="AA328" s="9"/>
       <c r="AB328" s="9"/>
-      <c r="AC328" s="116"/>
+      <c r="AC328" s="115"/>
       <c r="AD328" s="7"/>
       <c r="AE328" s="2">
-        <f>IF(SUM(Q328:AD328)&gt;0,SUM(Q328:AD328),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF328" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>6</v>
       </c>
     </row>
@@ -24744,14 +24715,14 @@
       <c r="Z329" s="9"/>
       <c r="AA329" s="9"/>
       <c r="AB329" s="9"/>
-      <c r="AC329" s="116"/>
+      <c r="AC329" s="115"/>
       <c r="AD329" s="7"/>
       <c r="AE329" s="2">
-        <f>IF(SUM(Q329:AD329)&gt;0,SUM(Q329:AD329),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF329" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>7</v>
       </c>
     </row>
@@ -24808,14 +24779,14 @@
       <c r="Z330" s="9"/>
       <c r="AA330" s="9"/>
       <c r="AB330" s="9"/>
-      <c r="AC330" s="116"/>
+      <c r="AC330" s="115"/>
       <c r="AD330" s="7"/>
       <c r="AE330" s="2">
-        <f>IF(SUM(Q330:AD330)&gt;0,SUM(Q330:AD330),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF330" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>6</v>
       </c>
     </row>
@@ -24874,14 +24845,14 @@
       <c r="Z331" s="9"/>
       <c r="AA331" s="9"/>
       <c r="AB331" s="9"/>
-      <c r="AC331" s="116"/>
+      <c r="AC331" s="115"/>
       <c r="AD331" s="7"/>
       <c r="AE331" s="2">
-        <f>IF(SUM(Q331:AD331)&gt;0,SUM(Q331:AD331),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF331" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>6</v>
       </c>
     </row>
@@ -24916,14 +24887,14 @@
       <c r="Z332" s="9"/>
       <c r="AA332" s="9"/>
       <c r="AB332" s="9"/>
-      <c r="AC332" s="116"/>
+      <c r="AC332" s="115"/>
       <c r="AD332" s="7"/>
       <c r="AE332" s="2" t="str">
-        <f>IF(SUM(Q332:AD332)&gt;0,SUM(Q332:AD332),"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AF332" s="77" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -24982,14 +24953,14 @@
       <c r="Z333" s="9"/>
       <c r="AA333" s="9"/>
       <c r="AB333" s="9"/>
-      <c r="AC333" s="116"/>
+      <c r="AC333" s="115"/>
       <c r="AD333" s="7"/>
       <c r="AE333" s="2">
-        <f>IF(SUM(Q333:AD333)&gt;0,SUM(Q333:AD333),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF333" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>6</v>
       </c>
     </row>
@@ -25025,14 +24996,14 @@
       <c r="Z334" s="9"/>
       <c r="AA334" s="9"/>
       <c r="AB334" s="9"/>
-      <c r="AC334" s="116"/>
+      <c r="AC334" s="115"/>
       <c r="AD334" s="7"/>
       <c r="AE334" s="2" t="str">
-        <f>IF(SUM(Q334:AD334)&gt;0,SUM(Q334:AD334),"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AF334" s="77" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -25087,14 +25058,14 @@
       <c r="Z335" s="9"/>
       <c r="AA335" s="9"/>
       <c r="AB335" s="9"/>
-      <c r="AC335" s="116"/>
+      <c r="AC335" s="115"/>
       <c r="AD335" s="7"/>
       <c r="AE335" s="2">
-        <f>IF(SUM(Q335:AD335)&gt;0,SUM(Q335:AD335),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF335" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>6</v>
       </c>
     </row>
@@ -25149,14 +25120,14 @@
       <c r="Z336" s="9"/>
       <c r="AA336" s="9"/>
       <c r="AB336" s="9"/>
-      <c r="AC336" s="116"/>
+      <c r="AC336" s="115"/>
       <c r="AD336" s="7"/>
       <c r="AE336" s="2">
-        <f>IF(SUM(Q336:AD336)&gt;0,SUM(Q336:AD336),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF336" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
     </row>
@@ -25211,14 +25182,14 @@
       <c r="Z337" s="9"/>
       <c r="AA337" s="9"/>
       <c r="AB337" s="9"/>
-      <c r="AC337" s="116"/>
+      <c r="AC337" s="115"/>
       <c r="AD337" s="7"/>
       <c r="AE337" s="2">
-        <f>IF(SUM(Q337:AD337)&gt;0,SUM(Q337:AD337),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF337" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>6</v>
       </c>
     </row>
@@ -25273,14 +25244,14 @@
       <c r="Z338" s="9"/>
       <c r="AA338" s="9"/>
       <c r="AB338" s="9"/>
-      <c r="AC338" s="116"/>
+      <c r="AC338" s="115"/>
       <c r="AD338" s="7"/>
       <c r="AE338" s="2">
-        <f>IF(SUM(Q338:AD338)&gt;0,SUM(Q338:AD338),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF338" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>6</v>
       </c>
     </row>
@@ -25337,14 +25308,14 @@
       <c r="Z339" s="9"/>
       <c r="AA339" s="9"/>
       <c r="AB339" s="9"/>
-      <c r="AC339" s="116"/>
+      <c r="AC339" s="115"/>
       <c r="AD339" s="7"/>
       <c r="AE339" s="2">
-        <f>IF(SUM(Q339:AD339)&gt;0,SUM(Q339:AD339),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF339" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>6</v>
       </c>
     </row>
@@ -25401,14 +25372,14 @@
       <c r="Z340" s="9"/>
       <c r="AA340" s="9"/>
       <c r="AB340" s="9"/>
-      <c r="AC340" s="116"/>
+      <c r="AC340" s="115"/>
       <c r="AD340" s="7"/>
       <c r="AE340" s="2">
-        <f>IF(SUM(Q340:AD340)&gt;0,SUM(Q340:AD340),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF340" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>6</v>
       </c>
     </row>
@@ -25465,14 +25436,14 @@
       <c r="Z341" s="9"/>
       <c r="AA341" s="9"/>
       <c r="AB341" s="9"/>
-      <c r="AC341" s="116"/>
+      <c r="AC341" s="115"/>
       <c r="AD341" s="7"/>
       <c r="AE341" s="2">
-        <f>IF(SUM(Q341:AD341)&gt;0,SUM(Q341:AD341),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF341" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>6</v>
       </c>
     </row>
@@ -25529,14 +25500,14 @@
       <c r="Z342" s="9"/>
       <c r="AA342" s="9"/>
       <c r="AB342" s="9"/>
-      <c r="AC342" s="116"/>
+      <c r="AC342" s="115"/>
       <c r="AD342" s="7"/>
       <c r="AE342" s="2">
-        <f>IF(SUM(Q342:AD342)&gt;0,SUM(Q342:AD342),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF342" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
     </row>
@@ -25593,14 +25564,14 @@
       <c r="Z343" s="9"/>
       <c r="AA343" s="9"/>
       <c r="AB343" s="9"/>
-      <c r="AC343" s="116"/>
+      <c r="AC343" s="115"/>
       <c r="AD343" s="7"/>
       <c r="AE343" s="2">
-        <f>IF(SUM(Q343:AD343)&gt;0,SUM(Q343:AD343),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF343" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
     </row>
@@ -25636,14 +25607,14 @@
       <c r="Z344" s="9"/>
       <c r="AA344" s="9"/>
       <c r="AB344" s="9"/>
-      <c r="AC344" s="116"/>
+      <c r="AC344" s="115"/>
       <c r="AD344" s="7"/>
       <c r="AE344" s="2" t="str">
-        <f>IF(SUM(Q344:AD344)&gt;0,SUM(Q344:AD344),"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AF344" s="77" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -25699,14 +25670,14 @@
       <c r="Z345" s="9"/>
       <c r="AA345" s="9"/>
       <c r="AB345" s="9"/>
-      <c r="AC345" s="116"/>
+      <c r="AC345" s="115"/>
       <c r="AD345" s="7"/>
       <c r="AE345" s="2">
-        <f>IF(SUM(Q345:AD345)&gt;0,SUM(Q345:AD345),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF345" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
     </row>
@@ -25760,14 +25731,14 @@
       <c r="Z346" s="9"/>
       <c r="AA346" s="9"/>
       <c r="AB346" s="9"/>
-      <c r="AC346" s="116"/>
+      <c r="AC346" s="115"/>
       <c r="AD346" s="7"/>
       <c r="AE346" s="2">
-        <f>IF(SUM(Q346:AD346)&gt;0,SUM(Q346:AD346),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF346" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
     </row>
@@ -25823,14 +25794,14 @@
       <c r="Z347" s="9"/>
       <c r="AA347" s="9"/>
       <c r="AB347" s="9"/>
-      <c r="AC347" s="116"/>
+      <c r="AC347" s="115"/>
       <c r="AD347" s="7"/>
       <c r="AE347" s="2">
-        <f>IF(SUM(Q347:AD347)&gt;0,SUM(Q347:AD347),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF347" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
     </row>
@@ -25866,14 +25837,14 @@
       <c r="Z348" s="9"/>
       <c r="AA348" s="9"/>
       <c r="AB348" s="9"/>
-      <c r="AC348" s="116"/>
+      <c r="AC348" s="115"/>
       <c r="AD348" s="7"/>
       <c r="AE348" s="2" t="str">
-        <f>IF(SUM(Q348:AD348)&gt;0,SUM(Q348:AD348),"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AF348" s="77" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -25930,14 +25901,14 @@
       <c r="Z349" s="9"/>
       <c r="AA349" s="9"/>
       <c r="AB349" s="9"/>
-      <c r="AC349" s="116"/>
+      <c r="AC349" s="115"/>
       <c r="AD349" s="7"/>
       <c r="AE349" s="2">
-        <f>IF(SUM(Q349:AD349)&gt;0,SUM(Q349:AD349),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF349" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>7</v>
       </c>
     </row>
@@ -25994,14 +25965,14 @@
       <c r="Z350" s="9"/>
       <c r="AA350" s="9"/>
       <c r="AB350" s="9"/>
-      <c r="AC350" s="116"/>
+      <c r="AC350" s="115"/>
       <c r="AD350" s="7"/>
       <c r="AE350" s="2">
-        <f>IF(SUM(Q350:AD350)&gt;0,SUM(Q350:AD350),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF350" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>7</v>
       </c>
     </row>
@@ -26056,14 +26027,14 @@
       <c r="Z351" s="9"/>
       <c r="AA351" s="9"/>
       <c r="AB351" s="9"/>
-      <c r="AC351" s="116"/>
+      <c r="AC351" s="115"/>
       <c r="AD351" s="7"/>
       <c r="AE351" s="2">
-        <f>IF(SUM(Q351:AD351)&gt;0,SUM(Q351:AD351),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF351" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>7</v>
       </c>
     </row>
@@ -26118,14 +26089,14 @@
       <c r="Z352" s="9"/>
       <c r="AA352" s="9"/>
       <c r="AB352" s="9"/>
-      <c r="AC352" s="116"/>
+      <c r="AC352" s="115"/>
       <c r="AD352" s="7"/>
       <c r="AE352" s="2">
-        <f>IF(SUM(Q352:AD352)&gt;0,SUM(Q352:AD352),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF352" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>7</v>
       </c>
     </row>
@@ -26180,14 +26151,14 @@
       <c r="Z353" s="9"/>
       <c r="AA353" s="9"/>
       <c r="AB353" s="9"/>
-      <c r="AC353" s="116"/>
+      <c r="AC353" s="115"/>
       <c r="AD353" s="7"/>
       <c r="AE353" s="2">
-        <f>IF(SUM(Q353:AD353)&gt;0,SUM(Q353:AD353),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF353" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>8</v>
       </c>
     </row>
@@ -26242,14 +26213,14 @@
       <c r="Z354" s="9"/>
       <c r="AA354" s="9"/>
       <c r="AB354" s="9"/>
-      <c r="AC354" s="116"/>
+      <c r="AC354" s="115"/>
       <c r="AD354" s="7"/>
       <c r="AE354" s="2">
-        <f>IF(SUM(Q354:AD354)&gt;0,SUM(Q354:AD354),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF354" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>7</v>
       </c>
     </row>
@@ -26306,14 +26277,14 @@
       <c r="Z355" s="9"/>
       <c r="AA355" s="9"/>
       <c r="AB355" s="9"/>
-      <c r="AC355" s="116"/>
+      <c r="AC355" s="115"/>
       <c r="AD355" s="7"/>
       <c r="AE355" s="2">
-        <f>IF(SUM(Q355:AD355)&gt;0,SUM(Q355:AD355),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF355" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>7</v>
       </c>
     </row>
@@ -26368,14 +26339,14 @@
       <c r="Z356" s="9"/>
       <c r="AA356" s="9"/>
       <c r="AB356" s="9"/>
-      <c r="AC356" s="116"/>
+      <c r="AC356" s="115"/>
       <c r="AD356" s="7"/>
       <c r="AE356" s="2">
-        <f>IF(SUM(Q356:AD356)&gt;0,SUM(Q356:AD356),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF356" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>7</v>
       </c>
     </row>
@@ -26430,14 +26401,14 @@
       <c r="Z357" s="9"/>
       <c r="AA357" s="9"/>
       <c r="AB357" s="9"/>
-      <c r="AC357" s="116"/>
+      <c r="AC357" s="115"/>
       <c r="AD357" s="7"/>
       <c r="AE357" s="2">
-        <f>IF(SUM(Q357:AD357)&gt;0,SUM(Q357:AD357),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF357" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>7</v>
       </c>
     </row>
@@ -26493,14 +26464,14 @@
       <c r="Z358" s="9"/>
       <c r="AA358" s="9"/>
       <c r="AB358" s="9"/>
-      <c r="AC358" s="116"/>
+      <c r="AC358" s="115"/>
       <c r="AD358" s="7"/>
       <c r="AE358" s="2">
-        <f>IF(SUM(Q358:AD358)&gt;0,SUM(Q358:AD358),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF358" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
     </row>
@@ -26556,14 +26527,14 @@
       <c r="Z359" s="9"/>
       <c r="AA359" s="9"/>
       <c r="AB359" s="9"/>
-      <c r="AC359" s="116"/>
+      <c r="AC359" s="115"/>
       <c r="AD359" s="7"/>
       <c r="AE359" s="2">
-        <f>IF(SUM(Q359:AD359)&gt;0,SUM(Q359:AD359),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF359" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
     </row>
@@ -26619,14 +26590,14 @@
       <c r="Z360" s="9"/>
       <c r="AA360" s="9"/>
       <c r="AB360" s="9"/>
-      <c r="AC360" s="116"/>
+      <c r="AC360" s="115"/>
       <c r="AD360" s="7"/>
       <c r="AE360" s="2">
-        <f>IF(SUM(Q360:AD360)&gt;0,SUM(Q360:AD360),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF360" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
     </row>
@@ -26682,14 +26653,14 @@
       <c r="Z361" s="9"/>
       <c r="AA361" s="9"/>
       <c r="AB361" s="9"/>
-      <c r="AC361" s="116"/>
+      <c r="AC361" s="115"/>
       <c r="AD361" s="7"/>
       <c r="AE361" s="2">
-        <f>IF(SUM(Q361:AD361)&gt;0,SUM(Q361:AD361),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF361" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
     </row>
@@ -26745,14 +26716,14 @@
       <c r="Z362" s="9"/>
       <c r="AA362" s="9"/>
       <c r="AB362" s="9"/>
-      <c r="AC362" s="116"/>
+      <c r="AC362" s="115"/>
       <c r="AD362" s="7"/>
       <c r="AE362" s="2">
-        <f>IF(SUM(Q362:AD362)&gt;0,SUM(Q362:AD362),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF362" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
     </row>
@@ -26804,14 +26775,14 @@
       <c r="Z363" s="9"/>
       <c r="AA363" s="9"/>
       <c r="AB363" s="9"/>
-      <c r="AC363" s="116"/>
+      <c r="AC363" s="115"/>
       <c r="AD363" s="7"/>
       <c r="AE363" s="2">
-        <f>IF(SUM(Q363:AD363)&gt;0,SUM(Q363:AD363),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF363" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
     </row>
@@ -26863,14 +26834,14 @@
       <c r="Z364" s="9"/>
       <c r="AA364" s="9"/>
       <c r="AB364" s="9"/>
-      <c r="AC364" s="116"/>
+      <c r="AC364" s="115"/>
       <c r="AD364" s="7"/>
       <c r="AE364" s="2">
-        <f>IF(SUM(Q364:AD364)&gt;0,SUM(Q364:AD364),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF364" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
     </row>
@@ -26922,14 +26893,14 @@
       <c r="Z365" s="9"/>
       <c r="AA365" s="9"/>
       <c r="AB365" s="9"/>
-      <c r="AC365" s="116"/>
+      <c r="AC365" s="115"/>
       <c r="AD365" s="7"/>
       <c r="AE365" s="2">
-        <f>IF(SUM(Q365:AD365)&gt;0,SUM(Q365:AD365),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF365" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
     </row>
@@ -26983,14 +26954,14 @@
       <c r="Z366" s="9"/>
       <c r="AA366" s="9"/>
       <c r="AB366" s="9"/>
-      <c r="AC366" s="116"/>
+      <c r="AC366" s="115"/>
       <c r="AD366" s="7"/>
       <c r="AE366" s="2">
-        <f>IF(SUM(Q366:AD366)&gt;0,SUM(Q366:AD366),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF366" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
     </row>
@@ -27040,14 +27011,14 @@
       <c r="Z367" s="9"/>
       <c r="AA367" s="9"/>
       <c r="AB367" s="9"/>
-      <c r="AC367" s="116"/>
+      <c r="AC367" s="115"/>
       <c r="AD367" s="7"/>
       <c r="AE367" s="2">
-        <f>IF(SUM(Q367:AD367)&gt;0,SUM(Q367:AD367),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF367" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
     </row>
@@ -27097,14 +27068,14 @@
       <c r="Z368" s="9"/>
       <c r="AA368" s="9"/>
       <c r="AB368" s="9"/>
-      <c r="AC368" s="116"/>
+      <c r="AC368" s="115"/>
       <c r="AD368" s="7"/>
       <c r="AE368" s="2">
-        <f>IF(SUM(Q368:AD368)&gt;0,SUM(Q368:AD368),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF368" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
     </row>
@@ -27161,14 +27132,14 @@
       <c r="Z369" s="9"/>
       <c r="AA369" s="9"/>
       <c r="AB369" s="9"/>
-      <c r="AC369" s="116"/>
+      <c r="AC369" s="115"/>
       <c r="AD369" s="7"/>
       <c r="AE369" s="2">
-        <f>IF(SUM(Q369:AD369)&gt;0,SUM(Q369:AD369),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF369" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>9</v>
       </c>
     </row>
@@ -27225,14 +27196,14 @@
       <c r="Z370" s="9"/>
       <c r="AA370" s="9"/>
       <c r="AB370" s="9"/>
-      <c r="AC370" s="116"/>
+      <c r="AC370" s="115"/>
       <c r="AD370" s="7"/>
       <c r="AE370" s="2">
-        <f>IF(SUM(Q370:AD370)&gt;0,SUM(Q370:AD370),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF370" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>9</v>
       </c>
     </row>
@@ -27289,14 +27260,14 @@
       <c r="Z371" s="9"/>
       <c r="AA371" s="9"/>
       <c r="AB371" s="9"/>
-      <c r="AC371" s="116"/>
+      <c r="AC371" s="115"/>
       <c r="AD371" s="7"/>
       <c r="AE371" s="2">
-        <f>IF(SUM(Q371:AD371)&gt;0,SUM(Q371:AD371),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF371" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -27332,14 +27303,14 @@
       <c r="Z372" s="9"/>
       <c r="AA372" s="9"/>
       <c r="AB372" s="9"/>
-      <c r="AC372" s="116"/>
+      <c r="AC372" s="115"/>
       <c r="AD372" s="7"/>
       <c r="AE372" s="2" t="str">
-        <f>IF(SUM(Q372:AD372)&gt;0,SUM(Q372:AD372),"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AF372" s="77" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27396,14 +27367,14 @@
       <c r="Z373" s="9"/>
       <c r="AA373" s="9"/>
       <c r="AB373" s="9"/>
-      <c r="AC373" s="116"/>
+      <c r="AC373" s="115"/>
       <c r="AD373" s="7"/>
       <c r="AE373" s="2">
-        <f>IF(SUM(Q373:AD373)&gt;0,SUM(Q373:AD373),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF373" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>9</v>
       </c>
     </row>
@@ -27454,14 +27425,14 @@
       <c r="Z374" s="9"/>
       <c r="AA374" s="9"/>
       <c r="AB374" s="9"/>
-      <c r="AC374" s="116"/>
+      <c r="AC374" s="115"/>
       <c r="AD374" s="7"/>
       <c r="AE374" s="2">
-        <f>IF(SUM(Q374:AD374)&gt;0,SUM(Q374:AD374),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF374" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>9</v>
       </c>
     </row>
@@ -27512,14 +27483,14 @@
       <c r="Z375" s="9"/>
       <c r="AA375" s="9"/>
       <c r="AB375" s="9"/>
-      <c r="AC375" s="116"/>
+      <c r="AC375" s="115"/>
       <c r="AD375" s="7"/>
       <c r="AE375" s="2">
-        <f>IF(SUM(Q375:AD375)&gt;0,SUM(Q375:AD375),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF375" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>9</v>
       </c>
     </row>
@@ -27574,14 +27545,14 @@
       <c r="Z376" s="9"/>
       <c r="AA376" s="9"/>
       <c r="AB376" s="9"/>
-      <c r="AC376" s="116"/>
+      <c r="AC376" s="115"/>
       <c r="AD376" s="7"/>
       <c r="AE376" s="2">
-        <f>IF(SUM(Q376:AD376)&gt;0,SUM(Q376:AD376),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF376" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>9</v>
       </c>
     </row>
@@ -27636,14 +27607,14 @@
       <c r="Z377" s="9"/>
       <c r="AA377" s="9"/>
       <c r="AB377" s="9"/>
-      <c r="AC377" s="116"/>
+      <c r="AC377" s="115"/>
       <c r="AD377" s="7"/>
       <c r="AE377" s="2">
-        <f>IF(SUM(Q377:AD377)&gt;0,SUM(Q377:AD377),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF377" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>9</v>
       </c>
     </row>
@@ -27691,14 +27662,14 @@
       <c r="Z378" s="9"/>
       <c r="AA378" s="9"/>
       <c r="AB378" s="9"/>
-      <c r="AC378" s="116"/>
+      <c r="AC378" s="115"/>
       <c r="AD378" s="7"/>
       <c r="AE378" s="2">
-        <f>IF(SUM(Q378:AD378)&gt;0,SUM(Q378:AD378),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF378" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
     </row>
@@ -27734,14 +27705,14 @@
       <c r="Z379" s="9"/>
       <c r="AA379" s="9"/>
       <c r="AB379" s="9"/>
-      <c r="AC379" s="116"/>
+      <c r="AC379" s="115"/>
       <c r="AD379" s="7"/>
       <c r="AE379" s="2" t="str">
-        <f>IF(SUM(Q379:AD379)&gt;0,SUM(Q379:AD379),"")</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="AF379" s="77" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
     </row>
@@ -27788,14 +27759,14 @@
       <c r="Z380" s="9"/>
       <c r="AA380" s="9"/>
       <c r="AB380" s="9"/>
-      <c r="AC380" s="116"/>
+      <c r="AC380" s="115"/>
       <c r="AD380" s="7"/>
       <c r="AE380" s="2">
-        <f>IF(SUM(Q380:AD380)&gt;0,SUM(Q380:AD380),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF380" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>6</v>
       </c>
     </row>
@@ -27842,14 +27813,14 @@
       <c r="Z381" s="9"/>
       <c r="AA381" s="9"/>
       <c r="AB381" s="9"/>
-      <c r="AC381" s="116"/>
+      <c r="AC381" s="115"/>
       <c r="AD381" s="7"/>
       <c r="AE381" s="2">
-        <f>IF(SUM(Q381:AD381)&gt;0,SUM(Q381:AD381),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF381" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>6</v>
       </c>
     </row>
@@ -27896,14 +27867,14 @@
       <c r="Z382" s="9"/>
       <c r="AA382" s="9"/>
       <c r="AB382" s="9"/>
-      <c r="AC382" s="116"/>
+      <c r="AC382" s="115"/>
       <c r="AD382" s="7"/>
       <c r="AE382" s="2">
-        <f>IF(SUM(Q382:AD382)&gt;0,SUM(Q382:AD382),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF382" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>6</v>
       </c>
     </row>
@@ -27950,14 +27921,14 @@
       <c r="Z383" s="9"/>
       <c r="AA383" s="9"/>
       <c r="AB383" s="9"/>
-      <c r="AC383" s="116"/>
+      <c r="AC383" s="115"/>
       <c r="AD383" s="7"/>
       <c r="AE383" s="2">
-        <f>IF(SUM(Q383:AD383)&gt;0,SUM(Q383:AD383),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF383" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>6</v>
       </c>
     </row>
@@ -28005,14 +27976,14 @@
       <c r="Z384" s="9"/>
       <c r="AA384" s="9"/>
       <c r="AB384" s="9"/>
-      <c r="AC384" s="116"/>
+      <c r="AC384" s="115"/>
       <c r="AD384" s="7"/>
       <c r="AE384" s="2">
-        <f>IF(SUM(Q384:AD384)&gt;0,SUM(Q384:AD384),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF384" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
     </row>
@@ -28060,14 +28031,14 @@
       <c r="Z385" s="9"/>
       <c r="AA385" s="9"/>
       <c r="AB385" s="9"/>
-      <c r="AC385" s="116"/>
+      <c r="AC385" s="115"/>
       <c r="AD385" s="7"/>
       <c r="AE385" s="2">
-        <f>IF(SUM(Q385:AD385)&gt;0,SUM(Q385:AD385),"")</f>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="AF385" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
     </row>
@@ -28117,14 +28088,14 @@
       <c r="Z386" s="9"/>
       <c r="AA386" s="9"/>
       <c r="AB386" s="9"/>
-      <c r="AC386" s="116"/>
+      <c r="AC386" s="115"/>
       <c r="AD386" s="7"/>
       <c r="AE386" s="2">
-        <f>IF(SUM(Q386:AD386)&gt;0,SUM(Q386:AD386),"")</f>
+        <f t="shared" ref="AE386:AE449" si="12">IF(SUM(Q386:AD386)&gt;0,SUM(Q386:AD386),"")</f>
         <v>1</v>
       </c>
       <c r="AF386" s="77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="11"/>
         <v>2</v>
       </c>
     </row>
@@ -28170,14 +28141,14 @@
       <c r="Z387" s="9"/>
       <c r="AA387" s="9"/>
       <c r="AB387" s="9"/>
-      <c r="AC387" s="116"/>
+      <c r="AC387" s="115"/>
       <c r="AD387" s="7"/>
       <c r="AE387" s="2">
-        <f>IF(SUM(Q387:AD387)&gt;0,SUM(Q387:AD387),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF387" s="77">
-        <f t="shared" ref="AF387:AF448" si="6">IF(SUM(Q387:AD387)&lt;1,"",Q387*1+R387*2+S387*3+T387*4+U387*5+V387*6+W387*7+X387*8+Y387*9+Z387*10+AA387*11+AB387*12+AC387*13+AD387*14)</f>
+        <f t="shared" ref="AF387:AF448" si="13">IF(SUM(Q387:AD387)&lt;1,"",Q387*1+R387*2+S387*3+T387*4+U387*5+V387*6+W387*7+X387*8+Y387*9+Z387*10+AA387*11+AB387*12+AC387*13+AD387*14)</f>
         <v>3</v>
       </c>
     </row>
@@ -28225,14 +28196,14 @@
       <c r="Z388" s="9"/>
       <c r="AA388" s="9"/>
       <c r="AB388" s="9"/>
-      <c r="AC388" s="116"/>
+      <c r="AC388" s="115"/>
       <c r="AD388" s="7"/>
       <c r="AE388" s="2">
-        <f>IF(SUM(Q388:AD388)&gt;0,SUM(Q388:AD388),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF388" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
     </row>
@@ -28268,14 +28239,14 @@
       <c r="Z389" s="9"/>
       <c r="AA389" s="9"/>
       <c r="AB389" s="9"/>
-      <c r="AC389" s="116"/>
+      <c r="AC389" s="115"/>
       <c r="AD389" s="7"/>
       <c r="AE389" s="2" t="str">
-        <f>IF(SUM(Q389:AD389)&gt;0,SUM(Q389:AD389),"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AF389" s="77" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -28324,14 +28295,14 @@
       <c r="Z390" s="9"/>
       <c r="AA390" s="9"/>
       <c r="AB390" s="9"/>
-      <c r="AC390" s="116"/>
+      <c r="AC390" s="115"/>
       <c r="AD390" s="7"/>
       <c r="AE390" s="2">
-        <f>IF(SUM(Q390:AD390)&gt;0,SUM(Q390:AD390),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF390" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>8</v>
       </c>
     </row>
@@ -28380,14 +28351,14 @@
       <c r="Z391" s="9"/>
       <c r="AA391" s="9"/>
       <c r="AB391" s="9"/>
-      <c r="AC391" s="116"/>
+      <c r="AC391" s="115"/>
       <c r="AD391" s="7"/>
       <c r="AE391" s="2">
-        <f>IF(SUM(Q391:AD391)&gt;0,SUM(Q391:AD391),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF391" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>8</v>
       </c>
     </row>
@@ -28444,14 +28415,14 @@
       <c r="Z392" s="9"/>
       <c r="AA392" s="9"/>
       <c r="AB392" s="9"/>
-      <c r="AC392" s="116"/>
+      <c r="AC392" s="115"/>
       <c r="AD392" s="7"/>
       <c r="AE392" s="2">
-        <f>IF(SUM(Q392:AD392)&gt;0,SUM(Q392:AD392),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF392" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>8</v>
       </c>
     </row>
@@ -28498,14 +28469,14 @@
       <c r="Z393" s="9"/>
       <c r="AA393" s="9"/>
       <c r="AB393" s="9"/>
-      <c r="AC393" s="116"/>
+      <c r="AC393" s="115"/>
       <c r="AD393" s="7"/>
       <c r="AE393" s="2">
-        <f>IF(SUM(Q393:AD393)&gt;0,SUM(Q393:AD393),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF393" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>8</v>
       </c>
     </row>
@@ -28560,14 +28531,14 @@
       <c r="Z394" s="9"/>
       <c r="AA394" s="9"/>
       <c r="AB394" s="9"/>
-      <c r="AC394" s="116"/>
+      <c r="AC394" s="115"/>
       <c r="AD394" s="7"/>
       <c r="AE394" s="2">
-        <f>IF(SUM(Q394:AD394)&gt;0,SUM(Q394:AD394),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF394" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>8</v>
       </c>
     </row>
@@ -28622,14 +28593,14 @@
       <c r="Z395" s="9"/>
       <c r="AA395" s="9"/>
       <c r="AB395" s="9"/>
-      <c r="AC395" s="116"/>
+      <c r="AC395" s="115"/>
       <c r="AD395" s="7"/>
       <c r="AE395" s="2">
-        <f>IF(SUM(Q395:AD395)&gt;0,SUM(Q395:AD395),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF395" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>8</v>
       </c>
     </row>
@@ -28684,14 +28655,14 @@
       <c r="Z396" s="9"/>
       <c r="AA396" s="9"/>
       <c r="AB396" s="9"/>
-      <c r="AC396" s="116"/>
+      <c r="AC396" s="115"/>
       <c r="AD396" s="7"/>
       <c r="AE396" s="2">
-        <f>IF(SUM(Q396:AD396)&gt;0,SUM(Q396:AD396),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF396" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>8</v>
       </c>
     </row>
@@ -28742,14 +28713,14 @@
       <c r="Z397" s="9"/>
       <c r="AA397" s="9"/>
       <c r="AB397" s="9"/>
-      <c r="AC397" s="116"/>
+      <c r="AC397" s="115"/>
       <c r="AD397" s="7"/>
       <c r="AE397" s="2">
-        <f>IF(SUM(Q397:AD397)&gt;0,SUM(Q397:AD397),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF397" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>8</v>
       </c>
     </row>
@@ -28785,14 +28756,14 @@
       <c r="Z398" s="9"/>
       <c r="AA398" s="9"/>
       <c r="AB398" s="9"/>
-      <c r="AC398" s="116"/>
+      <c r="AC398" s="115"/>
       <c r="AD398" s="7"/>
       <c r="AE398" s="2" t="str">
-        <f>IF(SUM(Q398:AD398)&gt;0,SUM(Q398:AD398),"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AF398" s="77" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -28850,14 +28821,14 @@
       <c r="Z399" s="9"/>
       <c r="AA399" s="9"/>
       <c r="AB399" s="9"/>
-      <c r="AC399" s="116"/>
+      <c r="AC399" s="115"/>
       <c r="AD399" s="7"/>
       <c r="AE399" s="2">
-        <f>IF(SUM(Q399:AD399)&gt;0,SUM(Q399:AD399),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF399" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -28915,14 +28886,14 @@
       <c r="Z400" s="9"/>
       <c r="AA400" s="9"/>
       <c r="AB400" s="9"/>
-      <c r="AC400" s="116"/>
+      <c r="AC400" s="115"/>
       <c r="AD400" s="7"/>
       <c r="AE400" s="2">
-        <f>IF(SUM(Q400:AD400)&gt;0,SUM(Q400:AD400),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF400" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
     </row>
@@ -28958,14 +28929,14 @@
       <c r="Z401" s="9"/>
       <c r="AA401" s="9"/>
       <c r="AB401" s="9"/>
-      <c r="AC401" s="116"/>
+      <c r="AC401" s="115"/>
       <c r="AD401" s="7"/>
       <c r="AE401" s="2" t="str">
-        <f>IF(SUM(Q401:AD401)&gt;0,SUM(Q401:AD401),"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AF401" s="77" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -29021,14 +28992,14 @@
       <c r="AB402" s="63">
         <v>1</v>
       </c>
-      <c r="AC402" s="116"/>
+      <c r="AC402" s="115"/>
       <c r="AD402" s="7"/>
       <c r="AE402" s="2">
-        <f>IF(SUM(Q402:AD402)&gt;0,SUM(Q402:AD402),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF402" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>12</v>
       </c>
     </row>
@@ -29063,14 +29034,14 @@
       <c r="Z403" s="9"/>
       <c r="AA403" s="9"/>
       <c r="AB403" s="9"/>
-      <c r="AC403" s="116"/>
+      <c r="AC403" s="115"/>
       <c r="AD403" s="7"/>
       <c r="AE403" s="2" t="str">
-        <f>IF(SUM(Q403:AD403)&gt;0,SUM(Q403:AD403),"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AF403" s="77" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -29124,14 +29095,14 @@
       <c r="AB404" s="63">
         <v>1</v>
       </c>
-      <c r="AC404" s="116"/>
+      <c r="AC404" s="115"/>
       <c r="AD404" s="7"/>
       <c r="AE404" s="2">
-        <f>IF(SUM(Q404:AD404)&gt;0,SUM(Q404:AD404),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF404" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>12</v>
       </c>
     </row>
@@ -29189,14 +29160,14 @@
       <c r="AB405" s="63">
         <v>1</v>
       </c>
-      <c r="AC405" s="116"/>
+      <c r="AC405" s="115"/>
       <c r="AD405" s="7"/>
       <c r="AE405" s="2">
-        <f>IF(SUM(Q405:AD405)&gt;0,SUM(Q405:AD405),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF405" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>12</v>
       </c>
     </row>
@@ -29254,14 +29225,14 @@
       <c r="AB406" s="63">
         <v>1</v>
       </c>
-      <c r="AC406" s="116"/>
+      <c r="AC406" s="115"/>
       <c r="AD406" s="7"/>
       <c r="AE406" s="2">
-        <f>IF(SUM(Q406:AD406)&gt;0,SUM(Q406:AD406),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF406" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>12</v>
       </c>
     </row>
@@ -29319,14 +29290,14 @@
       <c r="AB407" s="63">
         <v>1</v>
       </c>
-      <c r="AC407" s="116"/>
+      <c r="AC407" s="115"/>
       <c r="AD407" s="7"/>
       <c r="AE407" s="2">
-        <f>IF(SUM(Q407:AD407)&gt;0,SUM(Q407:AD407),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF407" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>12</v>
       </c>
     </row>
@@ -29384,14 +29355,14 @@
       <c r="AB408" s="63">
         <v>1</v>
       </c>
-      <c r="AC408" s="116"/>
+      <c r="AC408" s="115"/>
       <c r="AD408" s="7"/>
       <c r="AE408" s="2">
-        <f>IF(SUM(Q408:AD408)&gt;0,SUM(Q408:AD408),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF408" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>12</v>
       </c>
     </row>
@@ -29449,14 +29420,14 @@
       <c r="AB409" s="63">
         <v>1</v>
       </c>
-      <c r="AC409" s="116"/>
+      <c r="AC409" s="115"/>
       <c r="AD409" s="7"/>
       <c r="AE409" s="2">
-        <f>IF(SUM(Q409:AD409)&gt;0,SUM(Q409:AD409),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF409" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>12</v>
       </c>
     </row>
@@ -29514,14 +29485,14 @@
       <c r="AB410" s="63">
         <v>1</v>
       </c>
-      <c r="AC410" s="116"/>
+      <c r="AC410" s="115"/>
       <c r="AD410" s="7"/>
       <c r="AE410" s="2">
-        <f>IF(SUM(Q410:AD410)&gt;0,SUM(Q410:AD410),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF410" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>12</v>
       </c>
     </row>
@@ -29579,14 +29550,14 @@
       <c r="AB411" s="63">
         <v>1</v>
       </c>
-      <c r="AC411" s="116"/>
+      <c r="AC411" s="115"/>
       <c r="AD411" s="7"/>
       <c r="AE411" s="2">
-        <f>IF(SUM(Q411:AD411)&gt;0,SUM(Q411:AD411),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF411" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>12</v>
       </c>
     </row>
@@ -29644,14 +29615,14 @@
       <c r="AB412" s="63">
         <v>1</v>
       </c>
-      <c r="AC412" s="116"/>
+      <c r="AC412" s="115"/>
       <c r="AD412" s="7"/>
       <c r="AE412" s="2">
-        <f>IF(SUM(Q412:AD412)&gt;0,SUM(Q412:AD412),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF412" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>12</v>
       </c>
     </row>
@@ -29709,14 +29680,14 @@
       <c r="AB413" s="63">
         <v>1</v>
       </c>
-      <c r="AC413" s="116"/>
+      <c r="AC413" s="115"/>
       <c r="AD413" s="7"/>
       <c r="AE413" s="2">
-        <f>IF(SUM(Q413:AD413)&gt;0,SUM(Q413:AD413),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF413" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>12</v>
       </c>
     </row>
@@ -29774,14 +29745,14 @@
       <c r="AB414" s="63">
         <v>1</v>
       </c>
-      <c r="AC414" s="116"/>
+      <c r="AC414" s="115"/>
       <c r="AD414" s="7"/>
       <c r="AE414" s="2">
-        <f>IF(SUM(Q414:AD414)&gt;0,SUM(Q414:AD414),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF414" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>12</v>
       </c>
     </row>
@@ -29839,14 +29810,14 @@
       <c r="AB415" s="63">
         <v>1</v>
       </c>
-      <c r="AC415" s="116"/>
+      <c r="AC415" s="115"/>
       <c r="AD415" s="7"/>
       <c r="AE415" s="2">
-        <f>IF(SUM(Q415:AD415)&gt;0,SUM(Q415:AD415),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF415" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>12</v>
       </c>
     </row>
@@ -29904,14 +29875,14 @@
       <c r="AB416" s="63">
         <v>1</v>
       </c>
-      <c r="AC416" s="116"/>
+      <c r="AC416" s="115"/>
       <c r="AD416" s="7"/>
       <c r="AE416" s="2">
-        <f>IF(SUM(Q416:AD416)&gt;0,SUM(Q416:AD416),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF416" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>12</v>
       </c>
     </row>
@@ -29969,14 +29940,14 @@
       <c r="AB417" s="63">
         <v>1</v>
       </c>
-      <c r="AC417" s="116"/>
+      <c r="AC417" s="115"/>
       <c r="AD417" s="7"/>
       <c r="AE417" s="2">
-        <f>IF(SUM(Q417:AD417)&gt;0,SUM(Q417:AD417),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF417" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>12</v>
       </c>
     </row>
@@ -30034,14 +30005,14 @@
       <c r="AB418" s="63">
         <v>1</v>
       </c>
-      <c r="AC418" s="116"/>
+      <c r="AC418" s="115"/>
       <c r="AD418" s="7"/>
       <c r="AE418" s="2">
-        <f>IF(SUM(Q418:AD418)&gt;0,SUM(Q418:AD418),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF418" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>12</v>
       </c>
     </row>
@@ -30089,14 +30060,14 @@
       <c r="AB419" s="63">
         <v>1</v>
       </c>
-      <c r="AC419" s="116"/>
+      <c r="AC419" s="115"/>
       <c r="AD419" s="7"/>
       <c r="AE419" s="2">
-        <f>IF(SUM(Q419:AD419)&gt;0,SUM(Q419:AD419),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF419" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>12</v>
       </c>
     </row>
@@ -30144,14 +30115,14 @@
       <c r="AB420" s="63">
         <v>1</v>
       </c>
-      <c r="AC420" s="116"/>
+      <c r="AC420" s="115"/>
       <c r="AD420" s="7"/>
       <c r="AE420" s="2">
-        <f>IF(SUM(Q420:AD420)&gt;0,SUM(Q420:AD420),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF420" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>12</v>
       </c>
     </row>
@@ -30207,14 +30178,14 @@
       <c r="AB421" s="63">
         <v>1</v>
       </c>
-      <c r="AC421" s="116"/>
+      <c r="AC421" s="115"/>
       <c r="AD421" s="7"/>
       <c r="AE421" s="2">
-        <f>IF(SUM(Q421:AD421)&gt;0,SUM(Q421:AD421),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF421" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>12</v>
       </c>
     </row>
@@ -30274,14 +30245,14 @@
         <v>1</v>
       </c>
       <c r="AB422" s="9"/>
-      <c r="AC422" s="116"/>
+      <c r="AC422" s="115"/>
       <c r="AD422" s="7"/>
       <c r="AE422" s="2">
-        <f>IF(SUM(Q422:AD422)&gt;0,SUM(Q422:AD422),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF422" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>11</v>
       </c>
     </row>
@@ -30316,14 +30287,14 @@
       <c r="Z423" s="9"/>
       <c r="AA423" s="9"/>
       <c r="AB423" s="9"/>
-      <c r="AC423" s="116"/>
+      <c r="AC423" s="115"/>
       <c r="AD423" s="7"/>
       <c r="AE423" s="2" t="str">
-        <f>IF(SUM(Q423:AD423)&gt;0,SUM(Q423:AD423),"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AF423" s="77" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30377,14 +30348,14 @@
         <v>1</v>
       </c>
       <c r="AB424" s="9"/>
-      <c r="AC424" s="116"/>
+      <c r="AC424" s="115"/>
       <c r="AD424" s="7"/>
       <c r="AE424" s="2">
-        <f>IF(SUM(Q424:AD424)&gt;0,SUM(Q424:AD424),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF424" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>11</v>
       </c>
     </row>
@@ -30446,14 +30417,14 @@
         <v>1</v>
       </c>
       <c r="AB425" s="9"/>
-      <c r="AC425" s="116"/>
+      <c r="AC425" s="115"/>
       <c r="AD425" s="7"/>
       <c r="AE425" s="2">
-        <f>IF(SUM(Q425:AD425)&gt;0,SUM(Q425:AD425),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF425" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>11</v>
       </c>
     </row>
@@ -30489,14 +30460,14 @@
       <c r="Z426" s="9"/>
       <c r="AA426" s="9"/>
       <c r="AB426" s="9"/>
-      <c r="AC426" s="116"/>
+      <c r="AC426" s="115"/>
       <c r="AD426" s="7"/>
       <c r="AE426" s="2" t="str">
-        <f>IF(SUM(Q426:AD426)&gt;0,SUM(Q426:AD426),"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AF426" s="77" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30543,16 +30514,16 @@
       <c r="Z427" s="9"/>
       <c r="AA427" s="9"/>
       <c r="AB427" s="9"/>
-      <c r="AC427" s="121">
+      <c r="AC427" s="63">
         <v>1</v>
       </c>
       <c r="AD427" s="7"/>
       <c r="AE427" s="2">
-        <f>IF(SUM(Q427:AD427)&gt;0,SUM(Q427:AD427),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF427" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>13</v>
       </c>
     </row>
@@ -30599,16 +30570,16 @@
       <c r="Z428" s="9"/>
       <c r="AA428" s="9"/>
       <c r="AB428" s="9"/>
-      <c r="AC428" s="121">
+      <c r="AC428" s="63">
         <v>1</v>
       </c>
       <c r="AD428" s="7"/>
       <c r="AE428" s="2">
-        <f>IF(SUM(Q428:AD428)&gt;0,SUM(Q428:AD428),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF428" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>13</v>
       </c>
     </row>
@@ -30645,14 +30616,14 @@
       <c r="Z429" s="9"/>
       <c r="AA429" s="9"/>
       <c r="AB429" s="9"/>
-      <c r="AC429" s="116"/>
+      <c r="AC429" s="115"/>
       <c r="AD429" s="7"/>
       <c r="AE429" s="2" t="str">
-        <f>IF(SUM(Q429:AD429)&gt;0,SUM(Q429:AD429),"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AF429" s="77" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30689,14 +30660,14 @@
       <c r="Z430" s="9"/>
       <c r="AA430" s="9"/>
       <c r="AB430" s="9"/>
-      <c r="AC430" s="116"/>
+      <c r="AC430" s="115"/>
       <c r="AD430" s="7"/>
       <c r="AE430" s="2" t="str">
-        <f>IF(SUM(Q430:AD430)&gt;0,SUM(Q430:AD430),"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AF430" s="77" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30733,14 +30704,14 @@
       <c r="Z431" s="9"/>
       <c r="AA431" s="9"/>
       <c r="AB431" s="9"/>
-      <c r="AC431" s="116"/>
+      <c r="AC431" s="115"/>
       <c r="AD431" s="7"/>
       <c r="AE431" s="2" t="str">
-        <f>IF(SUM(Q431:AD431)&gt;0,SUM(Q431:AD431),"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AF431" s="77" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30777,14 +30748,14 @@
       <c r="Z432" s="9"/>
       <c r="AA432" s="9"/>
       <c r="AB432" s="9"/>
-      <c r="AC432" s="116"/>
+      <c r="AC432" s="115"/>
       <c r="AD432" s="7"/>
       <c r="AE432" s="2" t="str">
-        <f>IF(SUM(Q432:AD432)&gt;0,SUM(Q432:AD432),"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AF432" s="77" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30821,14 +30792,14 @@
       <c r="Z433" s="9"/>
       <c r="AA433" s="9"/>
       <c r="AB433" s="9"/>
-      <c r="AC433" s="116"/>
+      <c r="AC433" s="115"/>
       <c r="AD433" s="7"/>
       <c r="AE433" s="2" t="str">
-        <f>IF(SUM(Q433:AD433)&gt;0,SUM(Q433:AD433),"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AF433" s="77" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -30879,14 +30850,14 @@
       </c>
       <c r="AA434" s="9"/>
       <c r="AB434" s="9"/>
-      <c r="AC434" s="116"/>
+      <c r="AC434" s="115"/>
       <c r="AD434" s="7"/>
       <c r="AE434" s="2">
-        <f>IF(SUM(Q434:AD434)&gt;0,SUM(Q434:AD434),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF434" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>10</v>
       </c>
     </row>
@@ -30938,14 +30909,14 @@
       </c>
       <c r="AA435" s="9"/>
       <c r="AB435" s="9"/>
-      <c r="AC435" s="116"/>
+      <c r="AC435" s="115"/>
       <c r="AD435" s="7"/>
       <c r="AE435" s="2">
-        <f>IF(SUM(Q435:AD435)&gt;0,SUM(Q435:AD435),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF435" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>10</v>
       </c>
     </row>
@@ -30996,14 +30967,14 @@
       </c>
       <c r="AA436" s="9"/>
       <c r="AB436" s="9"/>
-      <c r="AC436" s="116"/>
+      <c r="AC436" s="115"/>
       <c r="AD436" s="7"/>
       <c r="AE436" s="2">
-        <f>IF(SUM(Q436:AD436)&gt;0,SUM(Q436:AD436),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF436" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>10</v>
       </c>
     </row>
@@ -31054,14 +31025,14 @@
       </c>
       <c r="AA437" s="9"/>
       <c r="AB437" s="9"/>
-      <c r="AC437" s="116"/>
+      <c r="AC437" s="115"/>
       <c r="AD437" s="7"/>
       <c r="AE437" s="2">
-        <f>IF(SUM(Q437:AD437)&gt;0,SUM(Q437:AD437),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF437" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>10</v>
       </c>
     </row>
@@ -31112,14 +31083,14 @@
       </c>
       <c r="AA438" s="9"/>
       <c r="AB438" s="9"/>
-      <c r="AC438" s="116"/>
+      <c r="AC438" s="115"/>
       <c r="AD438" s="7"/>
       <c r="AE438" s="2">
-        <f>IF(SUM(Q438:AD438)&gt;0,SUM(Q438:AD438),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF438" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>10</v>
       </c>
     </row>
@@ -31171,14 +31142,14 @@
       </c>
       <c r="AA439" s="9"/>
       <c r="AB439" s="9"/>
-      <c r="AC439" s="116"/>
+      <c r="AC439" s="115"/>
       <c r="AD439" s="7"/>
       <c r="AE439" s="2">
-        <f>IF(SUM(Q439:AD439)&gt;0,SUM(Q439:AD439),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF439" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>10</v>
       </c>
     </row>
@@ -31230,14 +31201,14 @@
       </c>
       <c r="AA440" s="9"/>
       <c r="AB440" s="9"/>
-      <c r="AC440" s="116"/>
+      <c r="AC440" s="115"/>
       <c r="AD440" s="7"/>
       <c r="AE440" s="2">
-        <f>IF(SUM(Q440:AD440)&gt;0,SUM(Q440:AD440),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF440" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>10</v>
       </c>
     </row>
@@ -31289,14 +31260,14 @@
       </c>
       <c r="AA441" s="9"/>
       <c r="AB441" s="9"/>
-      <c r="AC441" s="116"/>
+      <c r="AC441" s="115"/>
       <c r="AD441" s="7"/>
       <c r="AE441" s="2">
-        <f>IF(SUM(Q441:AD441)&gt;0,SUM(Q441:AD441),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF441" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>10</v>
       </c>
     </row>
@@ -31348,14 +31319,14 @@
       </c>
       <c r="AA442" s="9"/>
       <c r="AB442" s="9"/>
-      <c r="AC442" s="116"/>
+      <c r="AC442" s="115"/>
       <c r="AD442" s="7"/>
       <c r="AE442" s="2">
-        <f>IF(SUM(Q442:AD442)&gt;0,SUM(Q442:AD442),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF442" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>10</v>
       </c>
     </row>
@@ -31392,14 +31363,14 @@
       <c r="Z443" s="9"/>
       <c r="AA443" s="9"/>
       <c r="AB443" s="9"/>
-      <c r="AC443" s="116"/>
+      <c r="AC443" s="115"/>
       <c r="AD443" s="7"/>
       <c r="AE443" s="2" t="str">
-        <f>IF(SUM(Q443:AD443)&gt;0,SUM(Q443:AD443),"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AF443" s="77" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31417,14 +31388,14 @@
       <c r="P444" s="58">
         <v>1</v>
       </c>
-      <c r="AC444" s="116"/>
+      <c r="AC444" s="115"/>
       <c r="AD444" s="7"/>
       <c r="AE444" s="2" t="str">
-        <f>IF(SUM(Q444:AD444)&gt;0,SUM(Q444:AD444),"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AF444" s="77" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31451,14 +31422,14 @@
       <c r="P445" s="58">
         <v>1</v>
       </c>
-      <c r="AC445" s="116"/>
+      <c r="AC445" s="115"/>
       <c r="AD445" s="7"/>
       <c r="AE445" s="2" t="str">
-        <f>IF(SUM(Q445:AD445)&gt;0,SUM(Q445:AD445),"")</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AF445" s="77" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
     </row>
@@ -31485,16 +31456,16 @@
       <c r="Z446" s="2"/>
       <c r="AA446" s="2"/>
       <c r="AB446" s="2"/>
-      <c r="AC446" s="121">
+      <c r="AC446" s="63">
         <v>1</v>
       </c>
       <c r="AD446" s="7"/>
       <c r="AE446" s="2">
-        <f>IF(SUM(Q446:AD446)&gt;0,SUM(Q446:AD446),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF446" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>13</v>
       </c>
     </row>
@@ -31521,16 +31492,16 @@
       <c r="Z447" s="2"/>
       <c r="AA447" s="2"/>
       <c r="AB447" s="2"/>
-      <c r="AC447" s="121">
+      <c r="AC447" s="63">
         <v>1</v>
       </c>
       <c r="AD447" s="7"/>
       <c r="AE447" s="2">
-        <f>IF(SUM(Q447:AD447)&gt;0,SUM(Q447:AD447),"")</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="AF447" s="77">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>13</v>
       </c>
     </row>
@@ -31577,16 +31548,16 @@
       <c r="Z448" s="81"/>
       <c r="AA448" s="81"/>
       <c r="AB448" s="81"/>
-      <c r="AC448" s="122">
-        <v>1</v>
-      </c>
-      <c r="AD448" s="127"/>
+      <c r="AC448" s="116">
+        <v>1</v>
+      </c>
+      <c r="AD448" s="119"/>
       <c r="AE448" s="81">
-        <f>IF(SUM(Q448:AD448)&gt;0,SUM(Q448:AD448),"")</f>
-        <v>1</v>
-      </c>
-      <c r="AF448" s="136">
-        <f t="shared" si="6"/>
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="AF448" s="127">
+        <f t="shared" si="13"/>
         <v>13</v>
       </c>
     </row>
@@ -31609,107 +31580,107 @@
         <v>0</v>
       </c>
       <c r="F449" s="1">
-        <f t="shared" ref="F449:O453" si="7">SUMIFS(F$4:F$448,$D$4:$D$448,$C449)</f>
+        <f t="shared" ref="F449:O453" si="14">SUMIFS(F$4:F$448,$D$4:$D$448,$C449)</f>
         <v>61</v>
       </c>
       <c r="G449" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>59</v>
       </c>
       <c r="H449" s="74">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>61</v>
       </c>
       <c r="I449" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>59</v>
       </c>
       <c r="J449" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>73</v>
       </c>
       <c r="K449" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>25</v>
       </c>
       <c r="L449" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>73</v>
       </c>
       <c r="M449" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>73</v>
       </c>
       <c r="N449" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>73</v>
       </c>
       <c r="O449" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
       <c r="P449" s="58">
-        <f t="shared" ref="P449:AD453" si="8">SUMIFS(P$4:P$448,$D$4:$D$448,$C449)</f>
+        <f t="shared" ref="P449:AD453" si="15">SUMIFS(P$4:P$448,$D$4:$D$448,$C449)</f>
         <v>90</v>
       </c>
       <c r="Q449" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>18</v>
       </c>
       <c r="R449" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>9</v>
       </c>
       <c r="S449" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>19</v>
       </c>
       <c r="T449" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>3</v>
       </c>
       <c r="U449" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>9</v>
       </c>
       <c r="V449" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>3</v>
       </c>
       <c r="W449" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>12</v>
       </c>
       <c r="X449" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>8</v>
       </c>
       <c r="Y449" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>9</v>
       </c>
       <c r="Z449" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AA449" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AB449" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC449" s="123">
+      <c r="AC449" s="1">
         <f>SUMIFS(AC$4:AC$448,$D$4:$D$448,$C449)</f>
         <v>0</v>
       </c>
       <c r="AD449" s="58">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE449" s="2">
-        <f>SUM(Q449:AD449)</f>
+        <f t="shared" ref="AE449:AE456" si="16">SUM(Q449:AD449)</f>
         <v>90</v>
       </c>
       <c r="AF449" s="60"/>
@@ -31733,107 +31704,107 @@
         <v>0</v>
       </c>
       <c r="F450" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>45</v>
       </c>
       <c r="G450" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>42</v>
       </c>
       <c r="H450" s="74">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>47</v>
       </c>
       <c r="I450" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>43</v>
       </c>
       <c r="J450" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>63</v>
       </c>
       <c r="K450" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="L450" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>58</v>
       </c>
       <c r="M450" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>58</v>
       </c>
       <c r="N450" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>58</v>
       </c>
       <c r="O450" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
       <c r="P450" s="58">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>68</v>
       </c>
       <c r="Q450" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>5</v>
       </c>
       <c r="R450" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>12</v>
       </c>
       <c r="S450" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>6</v>
       </c>
       <c r="T450" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="U450" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>6</v>
       </c>
       <c r="V450" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>18</v>
       </c>
       <c r="W450" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="X450" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>12</v>
       </c>
       <c r="Y450" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>9</v>
       </c>
       <c r="Z450" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AA450" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AB450" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC450" s="123">
+      <c r="AC450" s="1">
         <f>SUMIFS(AC$4:AC$448,$D$4:$D$448,$C450)</f>
         <v>0</v>
       </c>
       <c r="AD450" s="58">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE450" s="2">
-        <f>SUM(Q450:AD450)</f>
+        <f t="shared" si="16"/>
         <v>68</v>
       </c>
       <c r="AF450" s="60"/>
@@ -31854,107 +31825,107 @@
       </c>
       <c r="E451" s="9"/>
       <c r="F451" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="G451" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="H451" s="75">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>61</v>
       </c>
       <c r="I451" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>50</v>
       </c>
       <c r="J451" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>75</v>
       </c>
       <c r="K451" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>31</v>
       </c>
       <c r="L451" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>75</v>
       </c>
       <c r="M451" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>75</v>
       </c>
       <c r="N451" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>75</v>
       </c>
       <c r="O451" s="65">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="P451" s="76">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>93</v>
       </c>
       <c r="Q451" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>4</v>
       </c>
       <c r="R451" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>9</v>
       </c>
       <c r="S451" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>12</v>
       </c>
       <c r="T451" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="U451" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>15</v>
       </c>
       <c r="V451" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>17</v>
       </c>
       <c r="W451" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>15</v>
       </c>
       <c r="X451" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>15</v>
       </c>
       <c r="Y451" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>6</v>
       </c>
       <c r="Z451" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AA451" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AB451" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AC451" s="124">
+      <c r="AC451" s="65">
         <f>SUMIFS(AC$4:AC$448,$D$4:$D$448,$C451)</f>
         <v>0</v>
       </c>
       <c r="AD451" s="76">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE451" s="65">
-        <f>SUM(Q451:AD451)</f>
+        <f t="shared" si="16"/>
         <v>93</v>
       </c>
       <c r="AF451" s="60"/>
@@ -31975,107 +31946,107 @@
       </c>
       <c r="E452" s="2"/>
       <c r="F452" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>74</v>
       </c>
       <c r="G452" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>113</v>
       </c>
       <c r="H452" s="74">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>75</v>
       </c>
       <c r="I452" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>113</v>
       </c>
       <c r="J452" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>103</v>
       </c>
       <c r="K452" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>68</v>
       </c>
       <c r="L452" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>101</v>
       </c>
       <c r="M452" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>115</v>
       </c>
       <c r="N452" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>104</v>
       </c>
       <c r="O452" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>26</v>
       </c>
       <c r="P452" s="58">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>143</v>
       </c>
       <c r="Q452" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>2</v>
       </c>
       <c r="R452" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="S452" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>9</v>
       </c>
       <c r="T452" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>14</v>
       </c>
       <c r="U452" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>11</v>
       </c>
       <c r="V452" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>3</v>
       </c>
       <c r="W452" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="X452" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="Y452" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>3</v>
       </c>
       <c r="Z452" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>45</v>
       </c>
       <c r="AA452" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>10</v>
       </c>
       <c r="AB452" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>22</v>
       </c>
-      <c r="AC452" s="123">
+      <c r="AC452" s="1">
         <f>SUMIFS(AC$4:AC$448,$D$4:$D$448,$C452)</f>
         <v>3</v>
       </c>
       <c r="AD452" s="58">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>16</v>
       </c>
       <c r="AE452" s="2">
-        <f>SUM(Q452:AD452)</f>
+        <f t="shared" si="16"/>
         <v>141</v>
       </c>
       <c r="AF452" s="60"/>
@@ -32096,107 +32067,107 @@
       </c>
       <c r="E453" s="9"/>
       <c r="F453" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="G453" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="H453" s="74">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>5</v>
       </c>
       <c r="I453" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>4</v>
       </c>
       <c r="J453" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
       <c r="K453" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="L453" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
       <c r="M453" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>4</v>
       </c>
       <c r="N453" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>3</v>
       </c>
       <c r="O453" s="1">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="P453" s="58">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>6</v>
       </c>
       <c r="Q453" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R453" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="S453" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="T453" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="U453" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>2</v>
       </c>
       <c r="V453" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="W453" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="X453" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="Y453" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="Z453" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>3</v>
       </c>
       <c r="AA453" s="65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AB453" s="65">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="AC453" s="124">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="AC453" s="65">
         <f>SUMIFS(AC$4:AC$448,$D$4:$D$448,$C453)</f>
         <v>0</v>
       </c>
       <c r="AD453" s="76">
-        <f t="shared" si="8"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AE453" s="65">
-        <f>SUM(Q453:AD453)</f>
+        <f t="shared" si="16"/>
         <v>6</v>
       </c>
       <c r="AF453" s="60"/>
@@ -32218,95 +32189,95 @@
         <v>396</v>
       </c>
       <c r="F454" s="83">
-        <f t="shared" ref="F454:AD454" si="9">SUMIFS(F$4:F$448,$D$4:$D$448,"")</f>
+        <f t="shared" ref="F454:AD454" si="17">SUMIFS(F$4:F$448,$D$4:$D$448,"")</f>
         <v>0</v>
       </c>
       <c r="G454" s="83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="H454" s="84">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="I454" s="83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="J454" s="83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="K454" s="83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="L454" s="83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M454" s="83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>5</v>
       </c>
       <c r="N454" s="83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="O454" s="83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P454" s="85">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>6</v>
       </c>
       <c r="Q454" s="83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="R454" s="83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="S454" s="83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="T454" s="83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="U454" s="83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="V454" s="83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="W454" s="83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="X454" s="83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Y454" s="83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="Z454" s="83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AA454" s="83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AB454" s="83">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AC454" s="83">
@@ -32314,11 +32285,11 @@
         <v>0</v>
       </c>
       <c r="AD454" s="85">
-        <f t="shared" si="9"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AE454" s="83">
-        <f>SUM(Q454:AD454)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AF454" s="85"/>
@@ -32350,63 +32321,63 @@
         <v>215</v>
       </c>
       <c r="H455" s="1">
-        <f t="shared" ref="H455" si="10">SUM(H449:H454)</f>
+        <f t="shared" ref="H455" si="18">SUM(H449:H454)</f>
         <v>249</v>
       </c>
       <c r="I455" s="1">
-        <f t="shared" ref="I455:K455" si="11">SUM(I449:I454)</f>
+        <f t="shared" ref="I455:K455" si="19">SUM(I449:I454)</f>
         <v>269</v>
       </c>
       <c r="J455" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>317</v>
       </c>
       <c r="K455" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="19"/>
         <v>145</v>
       </c>
       <c r="L455" s="1">
-        <f t="shared" ref="L455:M455" si="12">SUM(L449:L454)</f>
+        <f t="shared" ref="L455:M455" si="20">SUM(L449:L454)</f>
         <v>310</v>
       </c>
       <c r="M455" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" si="20"/>
         <v>330</v>
       </c>
       <c r="N455" s="1">
-        <f t="shared" ref="N455:O455" si="13">SUM(N449:N454)</f>
+        <f t="shared" ref="N455:O455" si="21">SUM(N449:N454)</f>
         <v>313</v>
       </c>
       <c r="O455" s="1">
-        <f t="shared" si="13"/>
+        <f t="shared" si="21"/>
         <v>33</v>
       </c>
       <c r="P455" s="58">
-        <f t="shared" ref="P455" si="14">SUM(P449:P454)</f>
+        <f t="shared" ref="P455" si="22">SUM(P449:P454)</f>
         <v>406</v>
       </c>
       <c r="Q455" s="1">
-        <f t="shared" ref="Q455:AB455" si="15">SUM(Q449:Q454)</f>
+        <f t="shared" ref="Q455:AB455" si="23">SUM(Q449:Q454)</f>
         <v>29</v>
       </c>
       <c r="R455" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>31</v>
       </c>
       <c r="S455" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>46</v>
       </c>
       <c r="T455" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>17</v>
       </c>
       <c r="U455" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>43</v>
       </c>
       <c r="V455" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>41</v>
       </c>
       <c r="W455" s="1">
@@ -32430,10 +32401,10 @@
         <v>10</v>
       </c>
       <c r="AB455" s="1">
-        <f t="shared" si="15"/>
+        <f t="shared" si="23"/>
         <v>23</v>
       </c>
-      <c r="AC455" s="125">
+      <c r="AC455" s="117">
         <f>SUM(AC449:AC454)</f>
         <v>3</v>
       </c>
@@ -32442,7 +32413,7 @@
         <v>16</v>
       </c>
       <c r="AE455" s="2">
-        <f>SUM(Q455:AD455)</f>
+        <f t="shared" si="16"/>
         <v>398</v>
       </c>
       <c r="AF455" s="60"/>
@@ -32454,113 +32425,113 @@
       <c r="B456" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C456" s="128" t="s">
+      <c r="C456" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="D456" s="129">
-        <f t="shared" ref="D456" si="16">D455-D451-D454</f>
+      <c r="D456" s="121">
+        <f t="shared" ref="D456" si="24">D455-D451-D454</f>
         <v>307</v>
       </c>
-      <c r="E456" s="129"/>
-      <c r="F456" s="129"/>
-      <c r="G456" s="130"/>
-      <c r="H456" s="129">
-        <f t="shared" ref="H456:K456" si="17">H455-H451-H454</f>
+      <c r="E456" s="121"/>
+      <c r="F456" s="121"/>
+      <c r="G456" s="122"/>
+      <c r="H456" s="121">
+        <f t="shared" ref="H456:K456" si="25">H455-H451-H454</f>
         <v>188</v>
       </c>
-      <c r="I456" s="129">
-        <f t="shared" si="17"/>
+      <c r="I456" s="121">
+        <f t="shared" si="25"/>
         <v>219</v>
       </c>
-      <c r="J456" s="129">
-        <f t="shared" si="17"/>
+      <c r="J456" s="121">
+        <f t="shared" si="25"/>
         <v>242</v>
       </c>
-      <c r="K456" s="129">
-        <f t="shared" si="17"/>
+      <c r="K456" s="121">
+        <f t="shared" si="25"/>
         <v>113</v>
       </c>
-      <c r="L456" s="129">
-        <f t="shared" ref="L456:M456" si="18">L455-L451-L454</f>
+      <c r="L456" s="121">
+        <f t="shared" ref="L456:M456" si="26">L455-L451-L454</f>
         <v>235</v>
       </c>
-      <c r="M456" s="129">
-        <f t="shared" si="18"/>
+      <c r="M456" s="121">
+        <f t="shared" si="26"/>
         <v>250</v>
       </c>
-      <c r="N456" s="129">
-        <f t="shared" ref="N456:O456" si="19">N455-N451-N454</f>
+      <c r="N456" s="121">
+        <f t="shared" ref="N456:O456" si="27">N455-N451-N454</f>
         <v>238</v>
       </c>
-      <c r="O456" s="129">
-        <f t="shared" si="19"/>
+      <c r="O456" s="121">
+        <f t="shared" si="27"/>
         <v>33</v>
       </c>
-      <c r="P456" s="130">
-        <f t="shared" ref="P456" si="20">P455-P451-P454</f>
+      <c r="P456" s="122">
+        <f t="shared" ref="P456" si="28">P455-P451-P454</f>
         <v>307</v>
       </c>
-      <c r="Q456" s="129">
-        <f t="shared" ref="Q456:AB456" si="21">Q$449+Q$450+Q452</f>
+      <c r="Q456" s="121">
+        <f t="shared" ref="Q456:AB456" si="29">Q$449+Q$450+Q452</f>
         <v>25</v>
       </c>
-      <c r="R456" s="129">
-        <f t="shared" si="21"/>
+      <c r="R456" s="121">
+        <f t="shared" si="29"/>
         <v>22</v>
       </c>
-      <c r="S456" s="129">
-        <f t="shared" si="21"/>
+      <c r="S456" s="121">
+        <f t="shared" si="29"/>
         <v>34</v>
       </c>
-      <c r="T456" s="129">
-        <f t="shared" si="21"/>
+      <c r="T456" s="121">
+        <f t="shared" si="29"/>
         <v>17</v>
       </c>
-      <c r="U456" s="129">
-        <f t="shared" si="21"/>
+      <c r="U456" s="121">
+        <f t="shared" si="29"/>
         <v>26</v>
       </c>
-      <c r="V456" s="129">
-        <f t="shared" si="21"/>
+      <c r="V456" s="121">
+        <f t="shared" si="29"/>
         <v>24</v>
       </c>
-      <c r="W456" s="129">
-        <f t="shared" si="21"/>
+      <c r="W456" s="121">
+        <f t="shared" si="29"/>
         <v>13</v>
       </c>
-      <c r="X456" s="129">
-        <f t="shared" si="21"/>
+      <c r="X456" s="121">
+        <f t="shared" si="29"/>
         <v>21</v>
       </c>
-      <c r="Y456" s="129">
-        <f t="shared" si="21"/>
+      <c r="Y456" s="121">
+        <f t="shared" si="29"/>
         <v>21</v>
       </c>
-      <c r="Z456" s="129">
-        <f t="shared" si="21"/>
+      <c r="Z456" s="121">
+        <f t="shared" si="29"/>
         <v>45</v>
       </c>
-      <c r="AA456" s="129">
-        <f t="shared" si="21"/>
+      <c r="AA456" s="121">
+        <f t="shared" si="29"/>
         <v>10</v>
       </c>
-      <c r="AB456" s="129">
-        <f t="shared" si="21"/>
+      <c r="AB456" s="121">
+        <f t="shared" si="29"/>
         <v>22</v>
       </c>
-      <c r="AC456" s="131">
+      <c r="AC456" s="123">
         <f>AC$449+AC$450+AC452</f>
         <v>3</v>
       </c>
-      <c r="AD456" s="132">
+      <c r="AD456" s="124">
         <f>AD$449+AD$450+AD452</f>
         <v>16</v>
       </c>
-      <c r="AE456" s="133">
-        <f>SUM(Q456:AD456)</f>
+      <c r="AE456" s="125">
+        <f t="shared" si="16"/>
         <v>299</v>
       </c>
-      <c r="AF456" s="134"/>
+      <c r="AF456" s="126"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AF456" xr:uid="{5C1FF91F-9CCE-4A6C-8D63-17223F279B13}"/>
